--- a/DataSphere/Encuestas Satisfaccion/Clasificacion Columnas por area.xlsx
+++ b/DataSphere/Encuestas Satisfaccion/Clasificacion Columnas por area.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\degonzalez\Documents\2026\Backup_2026\DataSphere\Encuestas Satisfaccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E161F460-50ED-450E-9500-0D3F571CB6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966E154B-7755-4C65-92F0-47DAD68ACEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2DBDEDD0-140B-4193-A25A-54F1E8F4D7F4}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2DBDEDD0-140B-4193-A25A-54F1E8F4D7F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -4644,7 +4644,7 @@
         <v>"ID_2019" As "ID_2019",</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2019</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>"Correo" As "Correo",</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2019</v>
       </c>
@@ -4704,7 +4704,7 @@
         <v>"Nivel Formacion" As "Nivel Formacion",</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>"Modalidad" As "Modalidad",</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2019</v>
       </c>
@@ -4764,7 +4764,7 @@
         <v>"cedula" As "cedula",</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2019</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>"Ciudad" As "Ciudad",</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2019</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>"AC1" As "¿Qué tan satisfecho te encuentras con el programa más reciente que estás cursando en la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2019</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>"AC2" As "¿Qué tan cumplida ha sido la Universidad Ean en relación con el proceso de formación basado en competencias?",</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2019</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>"AC3" As "En general, ¿cómo percibes la calidad docente de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -4914,7 +4914,7 @@
         <v>"AC4" As "¿Qué tan fácil han hecho los docentes el proceso de aprendizaje en el que te encuentras?",</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2019</v>
       </c>
@@ -4944,7 +4944,7 @@
         <v>"AC5" As "¿Qué tan oportuna es la entrega de evaluaciones por parte de los docentes?",</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2019</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>"AC6" As "¿Qué tan competente es el personal de tu facultad?",</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2019</v>
       </c>
@@ -5004,7 +5004,7 @@
         <v>"AC7" As "¿Qué tan competentes son los responsables de tu programa académico (directores o coordinadores)?",</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2019</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>"AC8" As "En general, ¿cómo calificas los mecanismos de interacción y comunicación de los colaboradores de tu facultad?",</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2019</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>"AC9" As "¿Qué tan satisfecho te encuentras con la oferta académica de unidades de estudio?",</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2019</v>
       </c>
@@ -5094,7 +5094,7 @@
         <v>"AC10" As "¿Qué tan satisfecho te encuentras con el soporte brindado en temas de notas en Blackboard o SAP?",</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2019</v>
       </c>
@@ -8994,7 +8994,7 @@
         <v>"Network ID" As "Network ID",</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2020</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>"Cedula" As "Cedula",</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2020</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>"AC1" As "¿Qué tan satisfecho(a) te encuentras con la calidad académica del programa que cursas en la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2020</v>
       </c>
@@ -9084,7 +9084,7 @@
         <v>"AC2" As "¿Qué tan cumplida ha sido la Universidad Ean respecto a la promesa de valor académica ofrecida?",</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2020</v>
       </c>
@@ -9114,7 +9114,7 @@
         <v>"AC3" As "En general, ¿Cómo percibes la calidad de los docentes de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2020</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>"AC4" As "¿Qué tan oportuna es la entrega de calificaciones por parte de los docentes?",</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2020</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>"AC5" As "¿Qué tan cercanos percibes a los responsables de tu programa académico (decano(a), director(a) o coordinador(a)?",</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2020</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>"AC6" As "En general ¿Cómo calificas el soporte administrativo que brinda la Unidad Académica Administrativa?",</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2020</v>
       </c>
@@ -9234,7 +9234,7 @@
         <v>"AC7" As "¿Cómo percibes la atención y el servicio por parte de los colaboradores de la Unidad Académica Administrativa?",</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2020</v>
       </c>
@@ -9264,7 +9264,7 @@
         <v>"AC8" As "Si eres estudiante presencial ¿Cómo evalúas el modelo PAT implementado durante la pandemia?",</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2020</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>"AC9" As "¿Consideras que la Universidad Ean te ha brindado el acompañamiento y soporte necesario para dar continuidad a tus actividades académicas durante la pandemia?",</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2020</v>
       </c>
@@ -9324,7 +9324,7 @@
         <v>"AC10" As "¿Qué tan probable es que recomiendes tu programa académico con familiares y amigos?",</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2020</v>
       </c>
@@ -9354,7 +9354,7 @@
         <v>"IES1" As "¿Conoces los servicios y beneficios que dispone el Instituto de Emprendimiento Sostenible para todos sus estudiantes?",</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2020</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>"IES2" As "¿Qué tanto impacta el enfoque del emprendimiento sostenible en tu proceso formativo?",</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2020</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>"IES3" As "Innovación",</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2020</v>
       </c>
@@ -9444,7 +9444,7 @@
         <v>"IES4" As "Emprendimiento",</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2020</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v>"IES5" As "Sostenibilidad",</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2020</v>
       </c>
@@ -9504,7 +9504,7 @@
         <v>"IES6" As "Calidad",</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2020</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>"IES7" As "Diversidad",</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2020</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>"IES8" As "Ética y valores",</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2020</v>
       </c>
@@ -9594,7 +9594,7 @@
         <v>"IES9" As "¿Qué tan probable es que recomiendes la formación en emprendimiento sostenible de la Universidad Ean con tus compañeros y conocidos?",</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2020</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>"B1" As "¿Qué tan satisfecho(a) te encuentras con los servicios que presta la biblioteca de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2020</v>
       </c>
@@ -9654,7 +9654,7 @@
         <v>"B2" As "¿Qué tan completas consideras las colecciones físicas y electrónicas en la biblioteca de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2020</v>
       </c>
@@ -9684,7 +9684,7 @@
         <v>"B3" As "¿Qué tan fácil ha sido el acceso a las colecciones electrónicas en la biblioteca de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2020</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>"B4" As "¿Cómo percibes la atención y el servicio por parte de los colaboradores de la biblioteca?",</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2020</v>
       </c>
@@ -9744,7 +9744,7 @@
         <v>"B5" As "¿Qué tan probable es que recomiendes el uso de la biblioteca de la Universidad Ean con tus compañeros?",</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2020</v>
       </c>
@@ -9774,7 +9774,7 @@
         <v>"INT1" As "Intercambios académicos",</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2020</v>
       </c>
@@ -9804,7 +9804,7 @@
         <v>"INT2" As "Misiones académicas",</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2020</v>
       </c>
@@ -9834,7 +9834,7 @@
         <v>"INT3" As "Semana Ean Internacional",</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2020</v>
       </c>
@@ -9864,7 +9864,7 @@
         <v>"INT4" As "Sesiones Ean Internacional",</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2020</v>
       </c>
@@ -9894,7 +9894,7 @@
         <v>"INT5" As "Escuela Internacional de Verano/Invierno",</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2020</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>"INT6" As "Visión Global, con Brigitte Baptiste",</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2020</v>
       </c>
@@ -9954,7 +9954,7 @@
         <v>"INT7" As "Global Classroom",</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2020</v>
       </c>
@@ -9984,7 +9984,7 @@
         <v>"INT8" As "Doble Titulación",</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2020</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>"INT9" As "Consultoría de investigación internacional",</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>2020</v>
       </c>
@@ -10044,7 +10044,7 @@
         <v>"GEE00" As "No conozco ninguno",</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2020</v>
       </c>
@@ -10074,7 +10074,7 @@
         <v>"INT11" As "¿Has participado en alguno de los programas mencionados anteriormente?",</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>2020</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>"INT12" As "¿Te interesaría participar en el futuro en alguno de los programas mencionados anteriormente?",</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>2020</v>
       </c>
@@ -10134,7 +10134,7 @@
         <v>"INT13" As "¿Conoces la oferta de convenios con universidades aliadas para hacer intercambios académicos?",</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>2020</v>
       </c>
@@ -10164,7 +10164,7 @@
         <v>"INT14" As "¿Qué tan relevante es para tu desarrollo académico y profesional participar en uno de los programas de movilidad y proyección global?",</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2020</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>"INT15" As "¿Qué tan satisfecho (a) te encuentras con la calidad de los servicios que brinda el equipo de Internacionalización y Relaciones Institucionales?",</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>2020</v>
       </c>
@@ -10224,7 +10224,7 @@
         <v>"PF1" As "¿Conoces los servicios, políticas y alcances de la oficina de Prácticas Profesionales?",</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2020</v>
       </c>
@@ -10254,7 +10254,7 @@
         <v>"PF2" As "¿Qué tan satisfecho (a) te encuentras con las opciones de Práctica Empresarial gestionadas por la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>2020</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>"PF3" As "¿Qué tan satisfecho(a) te encuentras con la calidad de los servicios que brinda el equipo de Prácticas Profesionales?",</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>2020</v>
       </c>
@@ -10314,7 +10314,7 @@
         <v>"TIC1" As "¿Qué tan satisfecho (a) te encuentras con la plataforma de correo electrónico en Outlook?",</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>2020</v>
       </c>
@@ -10344,7 +10344,7 @@
         <v>"TIC2" As "¿Qué tan satisfecho(a) te encuentras con la plataforma y la información que encuentras en SAP?",</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>2020</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>"TIC3" As "¿Qué tan satisfecho(a) te encuentras con el soporte técnico brindado para el correo electrónico y SAP?",</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>2020</v>
       </c>
@@ -10404,7 +10404,7 @@
         <v>"MD1" As "¿Qué tan satisfecho(a) te encuentras con la plataforma virtual Canvas?",</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>2020</v>
       </c>
@@ -10434,7 +10434,7 @@
         <v>"MD2" As "¿Qué tan satisfecho(a) te encuentras con Cisco Webex?",</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>2020</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>"MD3" As "¿Qué tan satisfecho(a) te encuentras con el soporte técnico brindado para la plataforma Canvas y Cisco Webex?",</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>2020</v>
       </c>
@@ -10494,7 +10494,7 @@
         <v>"TIC4" As "En general, ¿Cómo percibes la calidad de la tecnología de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>2020</v>
       </c>
@@ -10524,7 +10524,7 @@
         <v>"TIC5" As "¿Qué tan fácil ha sido el uso y acceso a los recursos tecnológicos de la Universidad Ean (Correo electrónico, Canvas, Cisco Webex, SAP)?",</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>2020</v>
       </c>
@@ -10554,7 +10554,7 @@
         <v>"TIC6" As "¿Qué tan probable es que recomiendes el uso de recursos tecnológicos de la Universidad Ean con tus compañeros?",</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>2020</v>
       </c>
@@ -10584,7 +10584,7 @@
         <v>"RA1" As "¿Qué tan satisfecho(a) te encuentras con los servicios ofrecidos por el área de registro académico de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>2020</v>
       </c>
@@ -10614,7 +10614,7 @@
         <v>"RA2" As "En relación con los tiempos de respuesta de registro académico ¿qué tan satisfecho(a) te encuentras?",</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>2020</v>
       </c>
@@ -10644,7 +10644,7 @@
         <v>"RA3" As "¿Qué tan satisfecho(a) te encuentras con la calidad de la atención que brinda el equipo de Registro Académico?",</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>2020</v>
       </c>
@@ -10674,7 +10674,7 @@
         <v>"APF1" As "¿Conoces los convenios y opciones de financiación dispuestos por la Universidad para la financiación de matrícula?",</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>2020</v>
       </c>
@@ -10704,7 +10704,7 @@
         <v>"APF2" As "¿Qué tan satisfecho(a) te encuentras con la calidad de los servicios ofrecidos por el área de Apoyo Financiero y Tesorería de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>2020</v>
       </c>
@@ -10734,7 +10734,7 @@
         <v>"APF3" As "¿Qué tan satisfecho(a) te encuentras con los procedimientos y tiempos de respuesta para aplicación de descuentos?",</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>2020</v>
       </c>
@@ -10764,7 +10764,7 @@
         <v>"APF4" As "¿Qué tan satisfecho(a) te encuentras con los canales dispuestos para el pago de matrícula y otros servicios académicos?",</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>2020</v>
       </c>
@@ -10794,7 +10794,7 @@
         <v>"APF5" As "¿Qué tan satisfecho(a) te sientes con la atención brindada por los colaboradores del proceso de Apoyo Financiero y Tesorería?",</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>2020</v>
       </c>
@@ -10824,7 +10824,7 @@
         <v>"MC1" As "¿Qué tan satisfecho(a) te encuentras con la atención telefónica cuando llamas al PBX de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>2020</v>
       </c>
@@ -10854,7 +10854,7 @@
         <v>"MC2" As "Facebook",</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>2020</v>
       </c>
@@ -10884,7 +10884,7 @@
         <v>"MC3" As "Instagram",</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>2020</v>
       </c>
@@ -10914,7 +10914,7 @@
         <v>"MC4" As "Twitter",</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>2020</v>
       </c>
@@ -10944,7 +10944,7 @@
         <v>"MC5" As "LinKedIn",</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>2020</v>
       </c>
@@ -10974,7 +10974,7 @@
         <v>"MC6" As "Youtube",</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>2020</v>
       </c>
@@ -11004,7 +11004,7 @@
         <v>"MC7" As "Ninguna",</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>2020</v>
       </c>
@@ -11034,7 +11034,7 @@
         <v>"MC8" As "¿Qué tan satisfecho (a) te encuentras con el contenido que se encuentra en la página web de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>2020</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>"MC9" As "¿Qué tan satisfecho (a) te encuentras con los contenidos y la funcionalidad de la app de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>2020</v>
       </c>
@@ -11094,7 +11094,7 @@
         <v>"MC10" As "¿Qué tan satisfecho(a) te encuentras el chat EVA de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>2020</v>
       </c>
@@ -11124,7 +11124,7 @@
         <v>"MC11" As "¿Qué tan satisfecho (a) te encuentras el soporte brindado a través de las Salas Webex de servicio?",</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>2020</v>
       </c>
@@ -11154,7 +11154,7 @@
         <v>"MC12" As "¿Qué tan satisfecho (a) te encuentras con la información que recibes de la Universidad Ean en tu correo electrónico institucional?",</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>2020</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>"MC13" As "¿Con qué frecuencia te gustaría recibir correos electrónicos de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>2020</v>
       </c>
@@ -11214,7 +11214,7 @@
         <v>"MC14" As "De los siguiente canales ¿Cuál consideras es el más efectivo para resolver tus inquietudes o requerimientos?",</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>2020</v>
       </c>
@@ -11244,7 +11244,7 @@
         <v>"GEE1" As "Admisiones",</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>2020</v>
       </c>
@@ -11274,7 +11274,7 @@
         <v>"GEE2" As "Bienestar Universitario",</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>2020</v>
       </c>
@@ -11304,7 +11304,7 @@
         <v>"GEE3" As "Permanencia Estudiantil",</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>2020</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>"GEE4" As "Servicios al Estudiante",</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>2020</v>
       </c>
@@ -11364,7 +11364,7 @@
         <v>"GEE5" As "Defensoría Universitaria",</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>2020</v>
       </c>
@@ -11394,7 +11394,7 @@
         <v>"GEE6" As "Graduados",</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>2020</v>
       </c>
@@ -11424,7 +11424,7 @@
         <v>"GEE07" As "Gimnasio y App Fitness Ean",</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>2020</v>
       </c>
@@ -11454,7 +11454,7 @@
         <v>"GEE08" As "Servicio de salud integral (médico y enfermería)",</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>2020</v>
       </c>
@@ -11484,7 +11484,7 @@
         <v>"GEE09" As "Servicio de atención psicosocial",</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>2020</v>
       </c>
@@ -11514,7 +11514,7 @@
         <v>"GEE10_2" As "Pedaleando a la U",</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>2020</v>
       </c>
@@ -11544,7 +11544,7 @@
         <v>"GEE11_2" As "Póliza de accidentes personales",</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>2020</v>
       </c>
@@ -11574,7 +11574,7 @@
         <v>"GEE12_2" As "Espacios de formación cultural (Grupos Culturales)",</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>2020</v>
       </c>
@@ -11604,7 +11604,7 @@
         <v>"GEE13_2" As "Espacios de formación deportiva (Grupos Deportivos)",</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>2020</v>
       </c>
@@ -11634,7 +11634,7 @@
         <v>"GEE14_2" As "Espacios de formación en actividad física",</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>2020</v>
       </c>
@@ -11664,7 +11664,7 @@
         <v>"GEE15_2" As "Espacios de formación en habilidades humanas (frEands, café de la diversidad, mindfulness y cyborg)",</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>2020</v>
       </c>
@@ -11694,7 +11694,7 @@
         <v>"GEE16_2" As "Eventos (Semana de la cultura, de la salud, del buen vivir, fitness, olimpiadas, jornadas de bienvenida, días especiales, etc...)",</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>2020</v>
       </c>
@@ -11724,7 +11724,7 @@
         <v>"GEE17" As "No conozco ninguno",</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>2020</v>
       </c>
@@ -11754,7 +11754,7 @@
         <v>"GEE7" As "Gimnasio y App Fitness Ean",</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>2020</v>
       </c>
@@ -11784,7 +11784,7 @@
         <v>"GEE8" As "Servicio de salud integral (médico y enfermería)",</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>2020</v>
       </c>
@@ -11814,7 +11814,7 @@
         <v>"GEE9" As "Servicio de atención psicosocial",</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>2020</v>
       </c>
@@ -11844,7 +11844,7 @@
         <v>"GEE10" As "Pedaleando a la U",</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>2020</v>
       </c>
@@ -11874,7 +11874,7 @@
         <v>"GEE11" As "Póliza de accidentes personales",</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>2020</v>
       </c>
@@ -11904,7 +11904,7 @@
         <v>"GEE12" As "Espacios de formación cultural (Grupos Culturales)",</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>2020</v>
       </c>
@@ -11934,7 +11934,7 @@
         <v>"GEE13" As "Espacios de formación deportiva (Grupos Deportivos)",</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>2020</v>
       </c>
@@ -11964,7 +11964,7 @@
         <v>"GEE14" As "Espacios de formación en actividad física",</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>2020</v>
       </c>
@@ -11994,7 +11994,7 @@
         <v>"GEE15" As "Espacios de formación en habilidades humanas (frEands, café de la diversidad, mindfulness y cyborg)",</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>2020</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>"GEE16" As "Eventos (Semana de la cultura, de la salud, del buen vivir, fitness, olimpiadas, jornadas de bienvenida, días especiales, etc...)",</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>2020</v>
       </c>
@@ -12054,7 +12054,7 @@
         <v>"GEE28" As "No los he usado",</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>2020</v>
       </c>
@@ -12084,7 +12084,7 @@
         <v>"GEE29" As "¿Qué tan satisfecho (a) te encuentras con la oferta de Bienestar Universitario?",</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>2020</v>
       </c>
@@ -12114,7 +12114,7 @@
         <v>"GEE30" As "¿Qué otra oferta te gustaría que se implementara para los estudiantes desde Bienestar Universitario?",</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>2020</v>
       </c>
@@ -12144,7 +12144,7 @@
         <v>"GEE31" As "¿Qué tan satisfecho (a) te encuentras con la actitud de servicio del equipo de Bienestar Universitario?",</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>2020</v>
       </c>
@@ -12174,7 +12174,7 @@
         <v>"GEE32" As "Programa Ean Contigo",</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>2020</v>
       </c>
@@ -12204,7 +12204,7 @@
         <v>"GEE33" As "Mentores Académicos",</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>2020</v>
       </c>
@@ -12234,7 +12234,7 @@
         <v>"GEE34" As "Los dos anteriores",</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>2020</v>
       </c>
@@ -12264,7 +12264,7 @@
         <v>"GEE35" As "Ninguno de los anteriores",</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>2020</v>
       </c>
@@ -12294,7 +12294,7 @@
         <v>"GEE36" As "¿Qué tan satisfecho (a) te encuentras con la calidad de los servicios que brinda el equipo de Permanencia Estudiantil?",</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>2020</v>
       </c>
@@ -12324,7 +12324,7 @@
         <v>"GEE37" As "¿Conoces el rol de los mentores académicos y su aporte a los estudiantes acompañados?",</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>2020</v>
       </c>
@@ -12354,7 +12354,7 @@
         <v>"GEE38" As "Talleres de empleabilidad",</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>2020</v>
       </c>
@@ -12384,7 +12384,7 @@
         <v>"GEE39" As "Asesoría en Hoja de Vida",</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>2020</v>
       </c>
@@ -12414,7 +12414,7 @@
         <v>"GEE40" As "Bolsa de Empleo",</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>2020</v>
       </c>
@@ -12444,7 +12444,7 @@
         <v>"GEE41" As "Seminario y talleres para el trabajo",</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>2020</v>
       </c>
@@ -12474,7 +12474,7 @@
         <v>"GEE42" As "¿Qué tan satisfecho (a) te encuentras con la calidad de los servicios que brinda el equipo del programa Empleabilidad?",</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>2020</v>
       </c>
@@ -12504,7 +12504,7 @@
         <v>"GEE43" As "¿Sabías que, en la Universidad Ean existe el rol de defensor universitario para prevenir y atender conflictos, cuya gestión es de acompañamiento, mediación e intervención?",</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>2020</v>
       </c>
@@ -12534,7 +12534,7 @@
         <v>"INST1" As "¿Qué tan satisfecho (a) te encuentras con los horarios en los cuales las áreas de la Universidad atienden a sus estudiantes?",</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>2020</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>"INST2" As "¿Consideras que la Universidad Ean desarrolla acciones para la sana convivencia y el respeto a la diferencia?",</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>2020</v>
       </c>
@@ -12594,7 +12594,7 @@
         <v>"INST3" As "¿Te sentiste acompañado o apoyado por la Universidad Ean durante la pandemia?",</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>2020</v>
       </c>
@@ -12624,7 +12624,7 @@
         <v>"INST4" As "¿Quieres destacar algo positivo de la Universidad Ean? ¿Crees que podemos mejorar en algún aspecto adicional?",</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>2020</v>
       </c>
@@ -12654,7 +12654,7 @@
         <v>"Start Date (UTC)" As "Start Date (UTC)",</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>2020</v>
       </c>
@@ -12684,7 +12684,7 @@
         <v>"Submit Date (UTC)" As "Submit Date (UTC)",</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>2020</v>
       </c>
@@ -36988,7 +36988,14 @@
   <autoFilter ref="A1:I1080" xr:uid="{CD622777-2061-4107-94CD-CCCFB7DE918A}">
     <filterColumn colId="0">
       <filters>
-        <filter val="2020"/>
+        <filter val="2019"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Academia"/>
+        <filter val="Datos Estudiante"/>
+        <filter val="Datos Programa"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/DataSphere/Encuestas Satisfaccion/Clasificacion Columnas por area.xlsx
+++ b/DataSphere/Encuestas Satisfaccion/Clasificacion Columnas por area.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\degonzalez\Documents\2026\Backup_2026\DataSphere\Encuestas Satisfaccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966E154B-7755-4C65-92F0-47DAD68ACEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED003F4-AE4F-4342-A40E-E570D9C60C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2DBDEDD0-140B-4193-A25A-54F1E8F4D7F4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2DBDEDD0-140B-4193-A25A-54F1E8F4D7F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -4575,7 +4575,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD622777-2061-4107-94CD-CCCFB7DE918A}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I1080"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4614,7 +4613,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2019</v>
       </c>
@@ -5124,7 +5123,7 @@
         <v>"AC11" As "¿Qué tan probable es que recomiendes tu programa académico con familiares y amigos?",</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2019</v>
       </c>
@@ -5154,7 +5153,7 @@
         <v>"IES1" As "¿Qué tan claro ha sido el concepto de sostenibilidad en tu proceso de formación con la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2019</v>
       </c>
@@ -5184,7 +5183,7 @@
         <v>"IES2" As "¿Qué tan interesado te encuentras en ser emprendedor, según el aprendizaje obtenido?",</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2019</v>
       </c>
@@ -5214,7 +5213,7 @@
         <v>"IES3" As "En general, ¿cómo percibes el enfoque de emprendimiento sostenible en los docentes con los que has interactuado?",</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2019</v>
       </c>
@@ -5244,7 +5243,7 @@
         <v>"IES4" As "¿Qué tan satisfecho te encuentras con el acompañamiento en tus proyectos de emprendimiento?",</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2019</v>
       </c>
@@ -5274,7 +5273,7 @@
         <v>"IES5" As "¿Qué tan satisfecho te encuentras con los espacios de conocimiento e intercambio de experiencias en emprendimiento sostenible?",</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2019</v>
       </c>
@@ -5304,7 +5303,7 @@
         <v>"IES6" As "¿Qué tan probable es que recomiendes la formación en emprendimiento sostenible de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2019</v>
       </c>
@@ -5334,7 +5333,7 @@
         <v>"TIC1" As "¿Qué tan satisfecho te encuentras con los recursos tecnológicos de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2019</v>
       </c>
@@ -5364,7 +5363,7 @@
         <v>"TIC2" As "En general, ¿cómo percibes la calidad de la tecnología de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2019</v>
       </c>
@@ -5394,7 +5393,7 @@
         <v>"TIC3" As "¿Qué tan fácil ha sido el uso y acceso a los recursos tecnológicos de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2019</v>
       </c>
@@ -5424,7 +5423,7 @@
         <v>"TIC4" As "¿Qué tan probable es que recomiendes el uso de los recursos tecnológicos de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2019</v>
       </c>
@@ -5454,7 +5453,7 @@
         <v>"B1" As "¿Qué tan satisfecho te encuentras con los servicios que presta la biblioteca de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2019</v>
       </c>
@@ -5484,7 +5483,7 @@
         <v>"B2" As "¿Qué tan satisfecho te encuentras con el horario que tiene la biblioteca?",</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2019</v>
       </c>
@@ -5514,7 +5513,7 @@
         <v>"B3" As "¿Qué tan completas consideras las colecciones físicas y electrónicas en la biblioteca?",</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2019</v>
       </c>
@@ -5544,7 +5543,7 @@
         <v>"B4" As "¿Qué tan fácil ha sido el uso de las colecciones físicas y electrónicas en la biblioteca?",</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2019</v>
       </c>
@@ -5574,7 +5573,7 @@
         <v>"B5" As "En general, ¿cómo percibes la atención de los colaboradores de la biblioteca?",</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2019</v>
       </c>
@@ -5604,7 +5603,7 @@
         <v>"B6" As "¿Qué tan probable es que recomiendes el uso de la biblioteca de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2019</v>
       </c>
@@ -5634,7 +5633,7 @@
         <v>"PFSL1" As "¿La Universidad Ean pone a disposición recursos para realizar el proceso de enseñanza-aprendizaje?",</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2019</v>
       </c>
@@ -5664,7 +5663,7 @@
         <v>"PFSL2" As "Accesibilidad",</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2019</v>
       </c>
@@ -5694,7 +5693,7 @@
         <v>"PFSL3" As "Capacidad (número de estudiantes máximo)",</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2019</v>
       </c>
@@ -5724,7 +5723,7 @@
         <v>"PFSL4" As "Ventilación",</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2019</v>
       </c>
@@ -5754,7 +5753,7 @@
         <v>"PFSL5" As "Condiciones de seguridad",</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2019</v>
       </c>
@@ -5784,7 +5783,7 @@
         <v>"PFSL6" As "Aseo",</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2019</v>
       </c>
@@ -5814,7 +5813,7 @@
         <v>"PFSL7" As "Disponibilidad de aulas",</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2019</v>
       </c>
@@ -5844,7 +5843,7 @@
         <v>"PFSL8" As "Acceso a internet",</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2019</v>
       </c>
@@ -5874,7 +5873,7 @@
         <v>"PFSL9" As "¿Qué tan satisfecho te encuentras con los servicios de Frutiice en la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2019</v>
       </c>
@@ -5904,7 +5903,7 @@
         <v>"PFSL10" As "¿Quieres hacer algún breve comentario acerca de Frutiice?",</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2019</v>
       </c>
@@ -5934,7 +5933,7 @@
         <v>"PFSL11" As "¿Qué tan probable es que recomiendes Frutiice con tus compañeros?",</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2019</v>
       </c>
@@ -5964,7 +5963,7 @@
         <v>"PFSL12" As "¿Qué tan satisfecho te encuentras con los servicios de fotocopiado de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2019</v>
       </c>
@@ -5994,7 +5993,7 @@
         <v>"PFSL13" As "¿Quieres hacer algún breve comentario acerca de los servicios de fotocopiado?",</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2019</v>
       </c>
@@ -6024,7 +6023,7 @@
         <v>"PFSL14" As "¿Qué tan probable es que recomiendes los servicios de fotocopiado con tus compañeros?",</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2019</v>
       </c>
@@ -6054,7 +6053,7 @@
         <v>"PFSL15" As "¿Qué tan satisfecho te encuentras con la atención del personal de seguridad de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2019</v>
       </c>
@@ -6084,7 +6083,7 @@
         <v>"PFSL16" As "¿Quieres hacer algún breve comentario acerca de la atención del personal de seguridad?",</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2019</v>
       </c>
@@ -6114,7 +6113,7 @@
         <v>"PFSL17" As "¿Qué tan probable es que recomiendes la atención del personal de seguridad con tus compañeros?",</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2019</v>
       </c>
@@ -6144,7 +6143,7 @@
         <v>"PFSL18" As "¿Qué tan satisfecho te encuentras con el servicio del personal de aseo de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2019</v>
       </c>
@@ -6174,7 +6173,7 @@
         <v>"PFSL19" As "¿Quieres hacer algún breve comentario acerca del servicio del personal de aseo?",</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2019</v>
       </c>
@@ -6204,7 +6203,7 @@
         <v>"PFSL20" As "¿Qué tan probable es que recomiendes el servicio del personal de aseo con tus compañeros?",</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2019</v>
       </c>
@@ -6234,7 +6233,7 @@
         <v>"PFSL21" As "¿Qué tan satisfecho te encuentras con el servicio de audiovisuales de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2019</v>
       </c>
@@ -6264,7 +6263,7 @@
         <v>"PFSL22" As "¿Quieres hacer algún breve comentario acerca del servicio de audiovisuales?",</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2019</v>
       </c>
@@ -6294,7 +6293,7 @@
         <v>"PFSL23" As "¿Qué tan probable es que recomiendes el servicio de audiovisuales con tus compañeros?",</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2019</v>
       </c>
@@ -6324,7 +6323,7 @@
         <v>"PFSL24" As "¿Qué tan satisfecho te encuentras con el servicio de parqueadero de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2019</v>
       </c>
@@ -6354,7 +6353,7 @@
         <v>"PFSL25" As "¿Quieres hacer algún breve comentario acerca del servicio de parqueadero?",</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2019</v>
       </c>
@@ -6384,7 +6383,7 @@
         <v>"PFSL26" As "¿Qué tan probable es que recomiendes el servicio de parqueadero con tus compañeros?",</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2019</v>
       </c>
@@ -6414,7 +6413,7 @@
         <v>"GEE1" As "¿Qué tan satisfecho te encuentras con el gimnasio de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2019</v>
       </c>
@@ -6444,7 +6443,7 @@
         <v>"GEE2" As "¿Quieres hacer algún breve comentario acerca del gimnasio?",</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2019</v>
       </c>
@@ -6474,7 +6473,7 @@
         <v>"GEE3" As "¿Qué tan probable es que recomiendes el gimnasio con tus compañeros?",</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2019</v>
       </c>
@@ -6504,7 +6503,7 @@
         <v>"GEE4" As "¿Qué tan satisfecho te encuentras con las actividades y grupos culturales de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2019</v>
       </c>
@@ -6534,7 +6533,7 @@
         <v>"GEE5" As "¿Quieres hacer algún breve comentario acerca de las actividades y grupos culturales?",</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2019</v>
       </c>
@@ -6564,7 +6563,7 @@
         <v>"GEE6" As "¿Qué tan probable es que recomiendes las actividades y grupos culturales con tus compañeros?",</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2019</v>
       </c>
@@ -6594,7 +6593,7 @@
         <v>"GEE7" As "¿Qué tan satisfecho te encuentras con las actividades y grupos deportivos de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2019</v>
       </c>
@@ -6624,7 +6623,7 @@
         <v>"GEE8" As "¿Quieres hacer algún breve comentario acerca de las actividades y grupos deportivos?",</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2019</v>
       </c>
@@ -6654,7 +6653,7 @@
         <v>"GEE9" As "¿Qué tan probable es que recomiendes las actividades y grupos deportivos con tus compañeros?",</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2019</v>
       </c>
@@ -6684,7 +6683,7 @@
         <v>"GEE10" As "¿Qué tan satisfecho te encuentras con los talleres y asesoría de empleabilidad que ofrece la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2019</v>
       </c>
@@ -6714,7 +6713,7 @@
         <v>"GEE11" As "¿Quieres hacer algún breve comentario acerca de los talleres y asesoría de empleabilidad?",</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2019</v>
       </c>
@@ -6744,7 +6743,7 @@
         <v>"GEE12" As "¿Qué tan probable es que recomiendes los talleres y asesoría de empleabilidad con tus compañeros?",</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2019</v>
       </c>
@@ -6774,7 +6773,7 @@
         <v>"GEE13" As "¿Qué tan satisfecho te encuentras con el servicio de consejería y atención psicosocial de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>2019</v>
       </c>
@@ -6804,7 +6803,7 @@
         <v>"GEE14" As "¿Quieres hacer algún breve comentario acerca del servicio de consejería y atención psicosocial?",</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2019</v>
       </c>
@@ -6834,7 +6833,7 @@
         <v>"GEE15" As "¿Qué tan probable es que recomiendes el servicio de consejería y atención psicosocial con tus compañeros?",</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>2019</v>
       </c>
@@ -6864,7 +6863,7 @@
         <v>"GEE16" As "¿Qué tan satisfecho te encuentras con las actividades de atención médica y prevención en salud?",</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>2019</v>
       </c>
@@ -6894,7 +6893,7 @@
         <v>"GEE17" As "¿Quieres hacer algún breve comentario acerca de las actividades de atención médica y prevención en salud?",</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2019</v>
       </c>
@@ -6924,7 +6923,7 @@
         <v>"GEE18" As "¿Qué tan probable es que recomiendes las actividades de atención médica y prevención en salud con tus compañeros?",</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2019</v>
       </c>
@@ -6954,7 +6953,7 @@
         <v>"GEE19" As "¿Conoces los servicios y beneficios de la póliza estudiantil que brinda la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2019</v>
       </c>
@@ -6984,7 +6983,7 @@
         <v>"GEE20" As "¿Qué tan satisfecho te encuentras con el programa de préstamo de bicicletas Pedaleando a la U?",</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2019</v>
       </c>
@@ -7014,7 +7013,7 @@
         <v>"GEE21" As "¿Quieres hacer algún breve comentario acerca del programa Pedaleando a la U?",</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2019</v>
       </c>
@@ -7044,7 +7043,7 @@
         <v>"GEE22" As "¿Qué tan probable es que recomiendes el programa de préstamo de bicicletas Pedaleando a la U con tus compañeros?",</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2019</v>
       </c>
@@ -7074,7 +7073,7 @@
         <v>"GEE23" As "¿Qué tan satisfecho te encuentras con la atención del personal de recepción?",</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>2019</v>
       </c>
@@ -7104,7 +7103,7 @@
         <v>"GEE24" As "¿Quieres hacer algún breve comentario acerca de la atención del personal de recepción?",</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2019</v>
       </c>
@@ -7134,7 +7133,7 @@
         <v>"GEE25" As "¿Qué tan probable es que recomiendes la atención del personal de recepción con tus compañeros?",</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>2019</v>
       </c>
@@ -7164,7 +7163,7 @@
         <v>"GEE26" As "¿Qué tan satisfecho te encuentras con la atención telefónica del PBX opción 1?",</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2019</v>
       </c>
@@ -7194,7 +7193,7 @@
         <v>"GEE27" As "¿Quieres hacer algún breve comentario acerca de la atención telefónica del PBX opción 1?",</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>2019</v>
       </c>
@@ -7224,7 +7223,7 @@
         <v>"GEE28" As "¿Qué tan probable es que recomiendes la atención telefónica del PBX opción 1 con tus compañeros?",</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>2019</v>
       </c>
@@ -7254,7 +7253,7 @@
         <v>"GEE29" As "¿Sabes que el carné de la Universidad Ean ahora es digital?",</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2019</v>
       </c>
@@ -7284,7 +7283,7 @@
         <v>"GEE30" As "¿Ya tienes tu carné digital?",</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2019</v>
       </c>
@@ -7314,7 +7313,7 @@
         <v>"GEE31" As "¿Quieres hacer algún breve comentario acerca del carné digital?",</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>2019</v>
       </c>
@@ -7344,7 +7343,7 @@
         <v>"GEE32" As "¿Qué tan probable es que recomiendes el carné digital con tus compañeros?",</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>2019</v>
       </c>
@@ -7374,7 +7373,7 @@
         <v>"GEE33" As "¿Conoces los servicios de Ean Contigo?",</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>2019</v>
       </c>
@@ -7404,7 +7403,7 @@
         <v>"GEE34" As "¿Qué tan satisfecho te encuentras con el servicio Ean Contigo?",</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>2019</v>
       </c>
@@ -7434,7 +7433,7 @@
         <v>"GEE35" As "¿Quieres hacer algún breve comentario acerca del servicio Ean Contigo?",</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>2019</v>
       </c>
@@ -7464,7 +7463,7 @@
         <v>"GEE36" As "¿Qué tan probable es que recomiendes el servicio Ean Contigo con tus compañeros?",</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2019</v>
       </c>
@@ -7494,7 +7493,7 @@
         <v>"GEE37" As "¿Conoces el rol de los mentores académicos y su aporte en el proceso formativo?",</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2019</v>
       </c>
@@ -7524,7 +7523,7 @@
         <v>"GEE38" As "¿Qué tan satisfecho te encuentras con los mentores académicos de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2019</v>
       </c>
@@ -7554,7 +7553,7 @@
         <v>"GEE39" As "¿Quieres hacer algún breve comentario acerca de los mentores académicos?",</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2019</v>
       </c>
@@ -7584,7 +7583,7 @@
         <v>"GEE40" As "¿Qué tan probable es que recomiendes a los mentores académicos con tus compañeros?",</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>2019</v>
       </c>
@@ -7614,7 +7613,7 @@
         <v>"GEE41" As "¿Qué tan satisfecho te encuentras con la oficina de servicios al estudiante?",</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>2019</v>
       </c>
@@ -7644,7 +7643,7 @@
         <v>"GEE42" As "¿Quieres hacer algún comentario acerca de la oficina de servicios al estudiante?",</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>2019</v>
       </c>
@@ -7674,7 +7673,7 @@
         <v>"GEE43" As "¿Qué tan probable es que recomiendes la oficina de servicios al estudiante con tus compañeros?",</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2019</v>
       </c>
@@ -7704,7 +7703,7 @@
         <v>"GEE44" As "¿Consideras que la Universidad Ean es incluyente?",</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2019</v>
       </c>
@@ -7734,7 +7733,7 @@
         <v>"GEE45" As "¿Consideras que la Universidad Ean desarrolla acciones para la sana convivencia y el respeto a la diferencia?",</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2019</v>
       </c>
@@ -7764,7 +7763,7 @@
         <v>"MC1" As "¿Qué tan satisfecho te encuentras con la página web de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2019</v>
       </c>
@@ -7794,7 +7793,7 @@
         <v>"MC2" As "¿Qué tan fácil te resulta navegar en la página web de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2019</v>
       </c>
@@ -7824,7 +7823,7 @@
         <v>"MC3" As "¿Qué tan probable es que recomiendes la página web con tus compañeros?",</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2019</v>
       </c>
@@ -7854,7 +7853,7 @@
         <v>"MC4" As "¿Conoces la app de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2019</v>
       </c>
@@ -7884,7 +7883,7 @@
         <v>"MC5" As "¿Qué tan útil te resulta la app de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2019</v>
       </c>
@@ -7914,7 +7913,7 @@
         <v>"MC6" As "¿Qué tan fácil te resulta interactuar con la app de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2019</v>
       </c>
@@ -7944,7 +7943,7 @@
         <v>"MC7" As "¿Qué tan probable es que recomiendes la app de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2019</v>
       </c>
@@ -7974,7 +7973,7 @@
         <v>"MC8" As "¿Conoces el chat EVA de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>2019</v>
       </c>
@@ -8004,7 +8003,7 @@
         <v>"MC9" As "¿Qué tan fácil te resulta interactuar con el chat EVA?",</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2019</v>
       </c>
@@ -8034,7 +8033,7 @@
         <v>"MC10" As "¿Qué tan probable es que recomiendes el chat EVA con tus compañeros?",</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2019</v>
       </c>
@@ -8064,7 +8063,7 @@
         <v>"MC11" As "¿Qué tan claro es el concepto de emprendimiento sostenible transmitido por las comunicaciones en la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2019</v>
       </c>
@@ -8094,7 +8093,7 @@
         <v>"INT1" As "¿Qué tan importantes son los convenios internacionales que te ofrece la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2019</v>
       </c>
@@ -8124,7 +8123,7 @@
         <v>"INT2" As "¿Qué tan satisfecho te encuentras con la divulgación de los convenios que ofrece internacionalización?",</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>2019</v>
       </c>
@@ -8154,7 +8153,7 @@
         <v>"INT3" As "¿Cómo percibes el servicio del área de internacionalización?",</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>2019</v>
       </c>
@@ -8184,7 +8183,7 @@
         <v>"INT4" As "¿Qué tan probable es que recomiendes los convenios de internacionalización con tus compañeros?",</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2019</v>
       </c>
@@ -8214,7 +8213,7 @@
         <v>"PF 1" As "¿Qué tan satisfecho te encuentras con el apoyo de Prácticas Profesionales de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2019</v>
       </c>
@@ -8244,7 +8243,7 @@
         <v>"PF 2" As "¿Quieres hacer algún breve comentario sobre Prácticas Profesionales?",</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2019</v>
       </c>
@@ -8274,7 +8273,7 @@
         <v>"PF 3" As "¿Qué tan probable es que recomiendes las Prácticas Profesionales con tus compañeros?",</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2019</v>
       </c>
@@ -8304,7 +8303,7 @@
         <v>"APF1" As "¿Qué tan satisfecho te encuentras con el servicio de apoyo financiero de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2019</v>
       </c>
@@ -8334,7 +8333,7 @@
         <v>"APF2" As "¿Qué tan satisfecho te encuentras con el horario que tiene apoyo financiero?",</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2019</v>
       </c>
@@ -8364,7 +8363,7 @@
         <v>"APF3" As "Y en relación con el servicio de facturación ¿qué tan satisfecho te encuentras?",</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2019</v>
       </c>
@@ -8394,7 +8393,7 @@
         <v>"APF4" As "¿Conoces los convenios y opciones de financiación para obtener crédito en la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2019</v>
       </c>
@@ -8424,7 +8423,7 @@
         <v>"APF5" As "¿Qué tan satisfecho te sientes con los convenios y opciones de financiación?",</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2019</v>
       </c>
@@ -8454,7 +8453,7 @@
         <v>"APF6" As "¿Quieres hacer algún breve comentario sobre apoyo financiero y facturación?",</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2019</v>
       </c>
@@ -8484,7 +8483,7 @@
         <v>"APF7" As "¿Qué tan probable es que recomiendes el servicio de apoyo financiero y facturación con tus compañeros?",</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2019</v>
       </c>
@@ -8514,7 +8513,7 @@
         <v>"RA1" As "¿Qué tan satisfecho te encuentras con los servicios de registro académico de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2019</v>
       </c>
@@ -8544,7 +8543,7 @@
         <v>"RA2" As "En relación con los tiempos de atención de registro académico ¿qué tan satisfecho te encuentras?",</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2019</v>
       </c>
@@ -8574,7 +8573,7 @@
         <v>"RA3" As "¿Quieres hacer algún breve comentario sobre registro académico de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2019</v>
       </c>
@@ -8604,7 +8603,7 @@
         <v>"RA4" As "¿Qué tan probable es que recomiendes el servicio de registro académico con tus compañeros?",</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2019</v>
       </c>
@@ -8634,7 +8633,7 @@
         <v>"MD1" As "¿Cuál es la experiencia de uso con la plataforma Blackboard para el desarrollo de tus actividades académicas?",</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2019</v>
       </c>
@@ -8664,7 +8663,7 @@
         <v>"MD2" As "¿Qué tan satisfecho te encuentras con el soporte técnico brindado para la plataforma de Blackboard?",</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2019</v>
       </c>
@@ -8694,7 +8693,7 @@
         <v>"MD3" As "En relación con los tiempos de atención para el soporte técnico de la plataforma de Blackboard ¿cómo es tu nivel de satisfacción?",</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2019</v>
       </c>
@@ -8724,7 +8723,7 @@
         <v>"MD4" As "¿Tienes algún comentario acerca de la plataforma Blackboard?",</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2019</v>
       </c>
@@ -8754,7 +8753,7 @@
         <v>"MD5" As "¿Qué tan probable es que recomiendes el servicio de soporte técnico y aulas virtuales en la plataforma Blackboard con tus compañeros?",</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2019</v>
       </c>
@@ -8784,7 +8783,7 @@
         <v>"ASSMC1" As "¿Qué tan satisfecho te encuentras con la medición de calidad que buscan las pruebas objetivas?",</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2019</v>
       </c>
@@ -8814,7 +8813,7 @@
         <v>"ASSMC2" As "¿Qué tan claras son las instrucciones para presentar las pruebas objetivas?",</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2019</v>
       </c>
@@ -8844,7 +8843,7 @@
         <v>"ASSMC3" As "¿Quieres hacer algún comentario sobre las pruebas objetivas?",</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2019</v>
       </c>
@@ -8874,7 +8873,7 @@
         <v>"ASSMC4" As "¿Qué tan probable es que recomiendes las pruebas objetivas con tus compañeros?",</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2019</v>
       </c>
@@ -8904,7 +8903,7 @@
         <v>"COMENT14" As "¿Quieres destacar algo positivo de la Universidad Ean o sugerir mejoras adicionales?",</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2019</v>
       </c>
@@ -8934,7 +8933,7 @@
         <v>"Start Date (UTC)" As "Start Date (UTC)",</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2019</v>
       </c>
@@ -8964,7 +8963,7 @@
         <v>"Submit Date (UTC)" As "Submit Date (UTC)",</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2019</v>
       </c>
@@ -8994,7 +8993,7 @@
         <v>"Network ID" As "Network ID",</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2020</v>
       </c>
@@ -9024,7 +9023,7 @@
         <v>"Cedula" As "Cedula",</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2020</v>
       </c>
@@ -9054,7 +9053,7 @@
         <v>"AC1" As "¿Qué tan satisfecho(a) te encuentras con la calidad académica del programa que cursas en la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2020</v>
       </c>
@@ -9084,7 +9083,7 @@
         <v>"AC2" As "¿Qué tan cumplida ha sido la Universidad Ean respecto a la promesa de valor académica ofrecida?",</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2020</v>
       </c>
@@ -9114,7 +9113,7 @@
         <v>"AC3" As "En general, ¿Cómo percibes la calidad de los docentes de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2020</v>
       </c>
@@ -9144,7 +9143,7 @@
         <v>"AC4" As "¿Qué tan oportuna es la entrega de calificaciones por parte de los docentes?",</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2020</v>
       </c>
@@ -9174,7 +9173,7 @@
         <v>"AC5" As "¿Qué tan cercanos percibes a los responsables de tu programa académico (decano(a), director(a) o coordinador(a)?",</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2020</v>
       </c>
@@ -9204,7 +9203,7 @@
         <v>"AC6" As "En general ¿Cómo calificas el soporte administrativo que brinda la Unidad Académica Administrativa?",</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2020</v>
       </c>
@@ -9234,7 +9233,7 @@
         <v>"AC7" As "¿Cómo percibes la atención y el servicio por parte de los colaboradores de la Unidad Académica Administrativa?",</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2020</v>
       </c>
@@ -9264,7 +9263,7 @@
         <v>"AC8" As "Si eres estudiante presencial ¿Cómo evalúas el modelo PAT implementado durante la pandemia?",</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2020</v>
       </c>
@@ -9294,7 +9293,7 @@
         <v>"AC9" As "¿Consideras que la Universidad Ean te ha brindado el acompañamiento y soporte necesario para dar continuidad a tus actividades académicas durante la pandemia?",</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2020</v>
       </c>
@@ -9324,7 +9323,7 @@
         <v>"AC10" As "¿Qué tan probable es que recomiendes tu programa académico con familiares y amigos?",</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2020</v>
       </c>
@@ -9354,7 +9353,7 @@
         <v>"IES1" As "¿Conoces los servicios y beneficios que dispone el Instituto de Emprendimiento Sostenible para todos sus estudiantes?",</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2020</v>
       </c>
@@ -9384,7 +9383,7 @@
         <v>"IES2" As "¿Qué tanto impacta el enfoque del emprendimiento sostenible en tu proceso formativo?",</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2020</v>
       </c>
@@ -9414,7 +9413,7 @@
         <v>"IES3" As "Innovación",</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2020</v>
       </c>
@@ -9444,7 +9443,7 @@
         <v>"IES4" As "Emprendimiento",</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2020</v>
       </c>
@@ -9474,7 +9473,7 @@
         <v>"IES5" As "Sostenibilidad",</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2020</v>
       </c>
@@ -9504,7 +9503,7 @@
         <v>"IES6" As "Calidad",</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2020</v>
       </c>
@@ -9534,7 +9533,7 @@
         <v>"IES7" As "Diversidad",</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2020</v>
       </c>
@@ -9564,7 +9563,7 @@
         <v>"IES8" As "Ética y valores",</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2020</v>
       </c>
@@ -9594,7 +9593,7 @@
         <v>"IES9" As "¿Qué tan probable es que recomiendes la formación en emprendimiento sostenible de la Universidad Ean con tus compañeros y conocidos?",</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2020</v>
       </c>
@@ -9624,7 +9623,7 @@
         <v>"B1" As "¿Qué tan satisfecho(a) te encuentras con los servicios que presta la biblioteca de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2020</v>
       </c>
@@ -9654,7 +9653,7 @@
         <v>"B2" As "¿Qué tan completas consideras las colecciones físicas y electrónicas en la biblioteca de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2020</v>
       </c>
@@ -9684,7 +9683,7 @@
         <v>"B3" As "¿Qué tan fácil ha sido el acceso a las colecciones electrónicas en la biblioteca de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2020</v>
       </c>
@@ -9714,7 +9713,7 @@
         <v>"B4" As "¿Cómo percibes la atención y el servicio por parte de los colaboradores de la biblioteca?",</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2020</v>
       </c>
@@ -9744,7 +9743,7 @@
         <v>"B5" As "¿Qué tan probable es que recomiendes el uso de la biblioteca de la Universidad Ean con tus compañeros?",</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2020</v>
       </c>
@@ -9774,7 +9773,7 @@
         <v>"INT1" As "Intercambios académicos",</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2020</v>
       </c>
@@ -9804,7 +9803,7 @@
         <v>"INT2" As "Misiones académicas",</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2020</v>
       </c>
@@ -9834,7 +9833,7 @@
         <v>"INT3" As "Semana Ean Internacional",</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2020</v>
       </c>
@@ -9864,7 +9863,7 @@
         <v>"INT4" As "Sesiones Ean Internacional",</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2020</v>
       </c>
@@ -9894,7 +9893,7 @@
         <v>"INT5" As "Escuela Internacional de Verano/Invierno",</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2020</v>
       </c>
@@ -9924,7 +9923,7 @@
         <v>"INT6" As "Visión Global, con Brigitte Baptiste",</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2020</v>
       </c>
@@ -9954,7 +9953,7 @@
         <v>"INT7" As "Global Classroom",</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2020</v>
       </c>
@@ -9984,7 +9983,7 @@
         <v>"INT8" As "Doble Titulación",</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2020</v>
       </c>
@@ -10014,7 +10013,7 @@
         <v>"INT9" As "Consultoría de investigación internacional",</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>2020</v>
       </c>
@@ -10044,7 +10043,7 @@
         <v>"GEE00" As "No conozco ninguno",</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2020</v>
       </c>
@@ -10074,7 +10073,7 @@
         <v>"INT11" As "¿Has participado en alguno de los programas mencionados anteriormente?",</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>2020</v>
       </c>
@@ -10104,7 +10103,7 @@
         <v>"INT12" As "¿Te interesaría participar en el futuro en alguno de los programas mencionados anteriormente?",</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>2020</v>
       </c>
@@ -10134,7 +10133,7 @@
         <v>"INT13" As "¿Conoces la oferta de convenios con universidades aliadas para hacer intercambios académicos?",</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>2020</v>
       </c>
@@ -10164,7 +10163,7 @@
         <v>"INT14" As "¿Qué tan relevante es para tu desarrollo académico y profesional participar en uno de los programas de movilidad y proyección global?",</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2020</v>
       </c>
@@ -10194,7 +10193,7 @@
         <v>"INT15" As "¿Qué tan satisfecho (a) te encuentras con la calidad de los servicios que brinda el equipo de Internacionalización y Relaciones Institucionales?",</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>2020</v>
       </c>
@@ -10224,7 +10223,7 @@
         <v>"PF1" As "¿Conoces los servicios, políticas y alcances de la oficina de Prácticas Profesionales?",</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2020</v>
       </c>
@@ -10254,7 +10253,7 @@
         <v>"PF2" As "¿Qué tan satisfecho (a) te encuentras con las opciones de Práctica Empresarial gestionadas por la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>2020</v>
       </c>
@@ -10284,7 +10283,7 @@
         <v>"PF3" As "¿Qué tan satisfecho(a) te encuentras con la calidad de los servicios que brinda el equipo de Prácticas Profesionales?",</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>2020</v>
       </c>
@@ -10314,7 +10313,7 @@
         <v>"TIC1" As "¿Qué tan satisfecho (a) te encuentras con la plataforma de correo electrónico en Outlook?",</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>2020</v>
       </c>
@@ -10344,7 +10343,7 @@
         <v>"TIC2" As "¿Qué tan satisfecho(a) te encuentras con la plataforma y la información que encuentras en SAP?",</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>2020</v>
       </c>
@@ -10374,7 +10373,7 @@
         <v>"TIC3" As "¿Qué tan satisfecho(a) te encuentras con el soporte técnico brindado para el correo electrónico y SAP?",</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>2020</v>
       </c>
@@ -10404,7 +10403,7 @@
         <v>"MD1" As "¿Qué tan satisfecho(a) te encuentras con la plataforma virtual Canvas?",</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>2020</v>
       </c>
@@ -10434,7 +10433,7 @@
         <v>"MD2" As "¿Qué tan satisfecho(a) te encuentras con Cisco Webex?",</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>2020</v>
       </c>
@@ -10464,7 +10463,7 @@
         <v>"MD3" As "¿Qué tan satisfecho(a) te encuentras con el soporte técnico brindado para la plataforma Canvas y Cisco Webex?",</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>2020</v>
       </c>
@@ -10494,7 +10493,7 @@
         <v>"TIC4" As "En general, ¿Cómo percibes la calidad de la tecnología de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>2020</v>
       </c>
@@ -10524,7 +10523,7 @@
         <v>"TIC5" As "¿Qué tan fácil ha sido el uso y acceso a los recursos tecnológicos de la Universidad Ean (Correo electrónico, Canvas, Cisco Webex, SAP)?",</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>2020</v>
       </c>
@@ -10554,7 +10553,7 @@
         <v>"TIC6" As "¿Qué tan probable es que recomiendes el uso de recursos tecnológicos de la Universidad Ean con tus compañeros?",</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>2020</v>
       </c>
@@ -10584,7 +10583,7 @@
         <v>"RA1" As "¿Qué tan satisfecho(a) te encuentras con los servicios ofrecidos por el área de registro académico de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>2020</v>
       </c>
@@ -10614,7 +10613,7 @@
         <v>"RA2" As "En relación con los tiempos de respuesta de registro académico ¿qué tan satisfecho(a) te encuentras?",</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>2020</v>
       </c>
@@ -10644,7 +10643,7 @@
         <v>"RA3" As "¿Qué tan satisfecho(a) te encuentras con la calidad de la atención que brinda el equipo de Registro Académico?",</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>2020</v>
       </c>
@@ -10674,7 +10673,7 @@
         <v>"APF1" As "¿Conoces los convenios y opciones de financiación dispuestos por la Universidad para la financiación de matrícula?",</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>2020</v>
       </c>
@@ -10704,7 +10703,7 @@
         <v>"APF2" As "¿Qué tan satisfecho(a) te encuentras con la calidad de los servicios ofrecidos por el área de Apoyo Financiero y Tesorería de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>2020</v>
       </c>
@@ -10734,7 +10733,7 @@
         <v>"APF3" As "¿Qué tan satisfecho(a) te encuentras con los procedimientos y tiempos de respuesta para aplicación de descuentos?",</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>2020</v>
       </c>
@@ -10764,7 +10763,7 @@
         <v>"APF4" As "¿Qué tan satisfecho(a) te encuentras con los canales dispuestos para el pago de matrícula y otros servicios académicos?",</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>2020</v>
       </c>
@@ -10794,7 +10793,7 @@
         <v>"APF5" As "¿Qué tan satisfecho(a) te sientes con la atención brindada por los colaboradores del proceso de Apoyo Financiero y Tesorería?",</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>2020</v>
       </c>
@@ -10824,7 +10823,7 @@
         <v>"MC1" As "¿Qué tan satisfecho(a) te encuentras con la atención telefónica cuando llamas al PBX de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>2020</v>
       </c>
@@ -10854,7 +10853,7 @@
         <v>"MC2" As "Facebook",</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>2020</v>
       </c>
@@ -10884,7 +10883,7 @@
         <v>"MC3" As "Instagram",</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>2020</v>
       </c>
@@ -10914,7 +10913,7 @@
         <v>"MC4" As "Twitter",</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>2020</v>
       </c>
@@ -10944,7 +10943,7 @@
         <v>"MC5" As "LinKedIn",</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>2020</v>
       </c>
@@ -10974,7 +10973,7 @@
         <v>"MC6" As "Youtube",</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>2020</v>
       </c>
@@ -11004,7 +11003,7 @@
         <v>"MC7" As "Ninguna",</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>2020</v>
       </c>
@@ -11034,7 +11033,7 @@
         <v>"MC8" As "¿Qué tan satisfecho (a) te encuentras con el contenido que se encuentra en la página web de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>2020</v>
       </c>
@@ -11064,7 +11063,7 @@
         <v>"MC9" As "¿Qué tan satisfecho (a) te encuentras con los contenidos y la funcionalidad de la app de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>2020</v>
       </c>
@@ -11094,7 +11093,7 @@
         <v>"MC10" As "¿Qué tan satisfecho(a) te encuentras el chat EVA de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>2020</v>
       </c>
@@ -11124,7 +11123,7 @@
         <v>"MC11" As "¿Qué tan satisfecho (a) te encuentras el soporte brindado a través de las Salas Webex de servicio?",</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>2020</v>
       </c>
@@ -11154,7 +11153,7 @@
         <v>"MC12" As "¿Qué tan satisfecho (a) te encuentras con la información que recibes de la Universidad Ean en tu correo electrónico institucional?",</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>2020</v>
       </c>
@@ -11184,7 +11183,7 @@
         <v>"MC13" As "¿Con qué frecuencia te gustaría recibir correos electrónicos de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>2020</v>
       </c>
@@ -11214,7 +11213,7 @@
         <v>"MC14" As "De los siguiente canales ¿Cuál consideras es el más efectivo para resolver tus inquietudes o requerimientos?",</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>2020</v>
       </c>
@@ -11244,7 +11243,7 @@
         <v>"GEE1" As "Admisiones",</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>2020</v>
       </c>
@@ -11274,7 +11273,7 @@
         <v>"GEE2" As "Bienestar Universitario",</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>2020</v>
       </c>
@@ -11304,7 +11303,7 @@
         <v>"GEE3" As "Permanencia Estudiantil",</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>2020</v>
       </c>
@@ -11334,7 +11333,7 @@
         <v>"GEE4" As "Servicios al Estudiante",</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>2020</v>
       </c>
@@ -11364,7 +11363,7 @@
         <v>"GEE5" As "Defensoría Universitaria",</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>2020</v>
       </c>
@@ -11394,7 +11393,7 @@
         <v>"GEE6" As "Graduados",</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>2020</v>
       </c>
@@ -11424,7 +11423,7 @@
         <v>"GEE07" As "Gimnasio y App Fitness Ean",</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>2020</v>
       </c>
@@ -11454,7 +11453,7 @@
         <v>"GEE08" As "Servicio de salud integral (médico y enfermería)",</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>2020</v>
       </c>
@@ -11484,7 +11483,7 @@
         <v>"GEE09" As "Servicio de atención psicosocial",</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>2020</v>
       </c>
@@ -11514,7 +11513,7 @@
         <v>"GEE10_2" As "Pedaleando a la U",</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>2020</v>
       </c>
@@ -11544,7 +11543,7 @@
         <v>"GEE11_2" As "Póliza de accidentes personales",</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>2020</v>
       </c>
@@ -11574,7 +11573,7 @@
         <v>"GEE12_2" As "Espacios de formación cultural (Grupos Culturales)",</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>2020</v>
       </c>
@@ -11604,7 +11603,7 @@
         <v>"GEE13_2" As "Espacios de formación deportiva (Grupos Deportivos)",</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>2020</v>
       </c>
@@ -11634,7 +11633,7 @@
         <v>"GEE14_2" As "Espacios de formación en actividad física",</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>2020</v>
       </c>
@@ -11664,7 +11663,7 @@
         <v>"GEE15_2" As "Espacios de formación en habilidades humanas (frEands, café de la diversidad, mindfulness y cyborg)",</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>2020</v>
       </c>
@@ -11694,7 +11693,7 @@
         <v>"GEE16_2" As "Eventos (Semana de la cultura, de la salud, del buen vivir, fitness, olimpiadas, jornadas de bienvenida, días especiales, etc...)",</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>2020</v>
       </c>
@@ -11724,7 +11723,7 @@
         <v>"GEE17" As "No conozco ninguno",</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>2020</v>
       </c>
@@ -11754,7 +11753,7 @@
         <v>"GEE7" As "Gimnasio y App Fitness Ean",</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>2020</v>
       </c>
@@ -11784,7 +11783,7 @@
         <v>"GEE8" As "Servicio de salud integral (médico y enfermería)",</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>2020</v>
       </c>
@@ -11814,7 +11813,7 @@
         <v>"GEE9" As "Servicio de atención psicosocial",</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>2020</v>
       </c>
@@ -11844,7 +11843,7 @@
         <v>"GEE10" As "Pedaleando a la U",</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>2020</v>
       </c>
@@ -11874,7 +11873,7 @@
         <v>"GEE11" As "Póliza de accidentes personales",</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>2020</v>
       </c>
@@ -11904,7 +11903,7 @@
         <v>"GEE12" As "Espacios de formación cultural (Grupos Culturales)",</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>2020</v>
       </c>
@@ -11934,7 +11933,7 @@
         <v>"GEE13" As "Espacios de formación deportiva (Grupos Deportivos)",</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>2020</v>
       </c>
@@ -11964,7 +11963,7 @@
         <v>"GEE14" As "Espacios de formación en actividad física",</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>2020</v>
       </c>
@@ -11994,7 +11993,7 @@
         <v>"GEE15" As "Espacios de formación en habilidades humanas (frEands, café de la diversidad, mindfulness y cyborg)",</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>2020</v>
       </c>
@@ -12024,7 +12023,7 @@
         <v>"GEE16" As "Eventos (Semana de la cultura, de la salud, del buen vivir, fitness, olimpiadas, jornadas de bienvenida, días especiales, etc...)",</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>2020</v>
       </c>
@@ -12054,7 +12053,7 @@
         <v>"GEE28" As "No los he usado",</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>2020</v>
       </c>
@@ -12084,7 +12083,7 @@
         <v>"GEE29" As "¿Qué tan satisfecho (a) te encuentras con la oferta de Bienestar Universitario?",</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>2020</v>
       </c>
@@ -12114,7 +12113,7 @@
         <v>"GEE30" As "¿Qué otra oferta te gustaría que se implementara para los estudiantes desde Bienestar Universitario?",</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>2020</v>
       </c>
@@ -12144,7 +12143,7 @@
         <v>"GEE31" As "¿Qué tan satisfecho (a) te encuentras con la actitud de servicio del equipo de Bienestar Universitario?",</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>2020</v>
       </c>
@@ -12174,7 +12173,7 @@
         <v>"GEE32" As "Programa Ean Contigo",</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>2020</v>
       </c>
@@ -12204,7 +12203,7 @@
         <v>"GEE33" As "Mentores Académicos",</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>2020</v>
       </c>
@@ -12234,7 +12233,7 @@
         <v>"GEE34" As "Los dos anteriores",</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>2020</v>
       </c>
@@ -12264,7 +12263,7 @@
         <v>"GEE35" As "Ninguno de los anteriores",</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>2020</v>
       </c>
@@ -12294,7 +12293,7 @@
         <v>"GEE36" As "¿Qué tan satisfecho (a) te encuentras con la calidad de los servicios que brinda el equipo de Permanencia Estudiantil?",</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>2020</v>
       </c>
@@ -12324,7 +12323,7 @@
         <v>"GEE37" As "¿Conoces el rol de los mentores académicos y su aporte a los estudiantes acompañados?",</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>2020</v>
       </c>
@@ -12354,7 +12353,7 @@
         <v>"GEE38" As "Talleres de empleabilidad",</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>2020</v>
       </c>
@@ -12384,7 +12383,7 @@
         <v>"GEE39" As "Asesoría en Hoja de Vida",</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>2020</v>
       </c>
@@ -12414,7 +12413,7 @@
         <v>"GEE40" As "Bolsa de Empleo",</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>2020</v>
       </c>
@@ -12444,7 +12443,7 @@
         <v>"GEE41" As "Seminario y talleres para el trabajo",</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>2020</v>
       </c>
@@ -12474,7 +12473,7 @@
         <v>"GEE42" As "¿Qué tan satisfecho (a) te encuentras con la calidad de los servicios que brinda el equipo del programa Empleabilidad?",</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>2020</v>
       </c>
@@ -12504,7 +12503,7 @@
         <v>"GEE43" As "¿Sabías que, en la Universidad Ean existe el rol de defensor universitario para prevenir y atender conflictos, cuya gestión es de acompañamiento, mediación e intervención?",</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>2020</v>
       </c>
@@ -12534,7 +12533,7 @@
         <v>"INST1" As "¿Qué tan satisfecho (a) te encuentras con los horarios en los cuales las áreas de la Universidad atienden a sus estudiantes?",</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>2020</v>
       </c>
@@ -12564,7 +12563,7 @@
         <v>"INST2" As "¿Consideras que la Universidad Ean desarrolla acciones para la sana convivencia y el respeto a la diferencia?",</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>2020</v>
       </c>
@@ -12594,7 +12593,7 @@
         <v>"INST3" As "¿Te sentiste acompañado o apoyado por la Universidad Ean durante la pandemia?",</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>2020</v>
       </c>
@@ -12624,7 +12623,7 @@
         <v>"INST4" As "¿Quieres destacar algo positivo de la Universidad Ean? ¿Crees que podemos mejorar en algún aspecto adicional?",</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>2020</v>
       </c>
@@ -12654,7 +12653,7 @@
         <v>"Start Date (UTC)" As "Start Date (UTC)",</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>2020</v>
       </c>
@@ -12684,7 +12683,7 @@
         <v>"Submit Date (UTC)" As "Submit Date (UTC)",</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>2020</v>
       </c>
@@ -12714,7 +12713,7 @@
         <v>"Network ID" As "Network ID",</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>2021</v>
       </c>
@@ -12744,7 +12743,7 @@
         <v>"ID_2021" As "ID_2021",</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>2021</v>
       </c>
@@ -12774,7 +12773,7 @@
         <v>"CC" As "CC",</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>2021</v>
       </c>
@@ -12804,7 +12803,7 @@
         <v>"Programa " As "Programa ",</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>2021</v>
       </c>
@@ -12834,7 +12833,7 @@
         <v>"Metodologia " As "Metodologia ",</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>2021</v>
       </c>
@@ -12864,7 +12863,7 @@
         <v>"AC1" As "Plan de estudios de tu programa",</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>2021</v>
       </c>
@@ -12894,7 +12893,7 @@
         <v>"AC2" As "Las competencias propuestas en las unidades cursadas hasta el momento",</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>2021</v>
       </c>
@@ -12924,7 +12923,7 @@
         <v>"AC3" As "¿Qué tan cumplida ha sido la Universidad Ean respecto a la promesa de valor académica ofrecida por el programa que cursas actualmente?",</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>2021</v>
       </c>
@@ -12954,7 +12953,7 @@
         <v>"AC4" As "Conocimiento disciplinar",</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>2021</v>
       </c>
@@ -12984,7 +12983,7 @@
         <v>"AC5" As "Competencias para la enseñanza y la formación",</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>2021</v>
       </c>
@@ -13014,7 +13013,7 @@
         <v>"AC6" As "Cumplimiento del Syllabus y plan de estudios del programa",</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>2021</v>
       </c>
@@ -13044,7 +13043,7 @@
         <v>"AC7" As "Evaluación y acompañamiento del proceso de aprendizaje",</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>2021</v>
       </c>
@@ -13074,7 +13073,7 @@
         <v>"AC8" As "Entrega de calificaciones y feedback",</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>2021</v>
       </c>
@@ -13104,7 +13103,7 @@
         <v>"AC9" As "Decano(a)",</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>2021</v>
       </c>
@@ -13134,7 +13133,7 @@
         <v>"AC10" As "Director (a) o Coordinador (a)",</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>2021</v>
       </c>
@@ -13164,7 +13163,7 @@
         <v>"AC11" As "En general ¿cómo calificas el soporte que presta el equipo de la Unidad Académico administrativa.",</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>2021</v>
       </c>
@@ -13194,7 +13193,7 @@
         <v>"AC12" As "En general ¿Cómo calificas el soporte administrativo que brindan los asistentes de tu Facultad?",</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>2021</v>
       </c>
@@ -13224,7 +13223,7 @@
         <v>"AC13" As "¿En qué modalidad de estudio estas cursando tu semestre?",</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>2021</v>
       </c>
@@ -13254,7 +13253,7 @@
         <v>"AC14" As "¿Cómo evalúas el regreso voluntario a la presencialidad?",</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>2021</v>
       </c>
@@ -13284,7 +13283,7 @@
         <v>"PFSL1" As "Disponibilidad y funcionamiento de los equipos",</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>2021</v>
       </c>
@@ -13314,7 +13313,7 @@
         <v>"PFSL2" As "Disponibilidad de materiales y/o reactivos",</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>2021</v>
       </c>
@@ -13344,7 +13343,7 @@
         <v>"PFSL3" As "Instalaciones",</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>2021</v>
       </c>
@@ -13374,7 +13373,7 @@
         <v>"PFSL4" As "Higiene y limpieza las Instalaciones y Equipos",</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>2021</v>
       </c>
@@ -13404,7 +13403,7 @@
         <v>"AC15" As "¿Qué tan probable es que recomiendes tu programa académico con familiares y amigos?",</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>2021</v>
       </c>
@@ -13434,7 +13433,7 @@
         <v>"AC16" As "¿Qué tan probable es que en el futuro vuelvas a estudiar un programa académico en la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>2021</v>
       </c>
@@ -13464,7 +13463,7 @@
         <v>"IES1" As "¿Conoces los servicios y beneficios que dispone el Instituto de Emprendimiento Sostenible para todos sus estudiantes?",</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>2021</v>
       </c>
@@ -13494,7 +13493,7 @@
         <v>"IES2" As "¿Qué tanto impacta el enfoque del emprendimiento sostenible en tu proceso formativo?",</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>2021</v>
       </c>
@@ -13524,7 +13523,7 @@
         <v>"IES3" As "Innovación",</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>2021</v>
       </c>
@@ -13554,7 +13553,7 @@
         <v>"IES4" As "Emprendimiento",</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>2021</v>
       </c>
@@ -13584,7 +13583,7 @@
         <v>"IES5" As "Sostenibilidad",</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>2021</v>
       </c>
@@ -13614,7 +13613,7 @@
         <v>"IES6" As "Calidad",</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>2021</v>
       </c>
@@ -13644,7 +13643,7 @@
         <v>"IES7" As "Diversidad",</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>2021</v>
       </c>
@@ -13674,7 +13673,7 @@
         <v>"IES8" As "Ética y valores",</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>2021</v>
       </c>
@@ -13704,7 +13703,7 @@
         <v>"B1" As "¿Qué tan satisfecho(a) te encuentras con los servicios que presta la biblioteca de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>2021</v>
       </c>
@@ -13734,7 +13733,7 @@
         <v>"B2" As "¿Qué tan completas consideras las colecciones físicas y electrónicas en la biblioteca de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>2021</v>
       </c>
@@ -13764,7 +13763,7 @@
         <v>"B3" As "¿Qué tan fácil ha sido el acceso a las colecciones electrónicas en la biblioteca de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>2021</v>
       </c>
@@ -13794,7 +13793,7 @@
         <v>"B4" As "En general ¿Cómo percibes la atención y el servicio por parte de los colaboradores de la biblioteca?",</v>
       </c>
     </row>
-    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>2021</v>
       </c>
@@ -13824,7 +13823,7 @@
         <v>"INT1" As "Intercambios académicos",</v>
       </c>
     </row>
-    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>2021</v>
       </c>
@@ -13854,7 +13853,7 @@
         <v>"INT2" As "Buddy Program",</v>
       </c>
     </row>
-    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>2021</v>
       </c>
@@ -13884,7 +13883,7 @@
         <v>"INT3" As "Misiones académicas",</v>
       </c>
     </row>
-    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>2021</v>
       </c>
@@ -13914,7 +13913,7 @@
         <v>"INT4" As "Semana Ean Internacional",</v>
       </c>
     </row>
-    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>2021</v>
       </c>
@@ -13944,7 +13943,7 @@
         <v>"INT5" As "Sesiones Ean Internacional",</v>
       </c>
     </row>
-    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>2021</v>
       </c>
@@ -13974,7 +13973,7 @@
         <v>"INT6" As "Escuela Internacional de Verano/Invierno",</v>
       </c>
     </row>
-    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>2021</v>
       </c>
@@ -14004,7 +14003,7 @@
         <v>"INT7" As "Visión Global, con Brigitte Baptiste",</v>
       </c>
     </row>
-    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>2021</v>
       </c>
@@ -14034,7 +14033,7 @@
         <v>"INT8" As "Global Classroom",</v>
       </c>
     </row>
-    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>2021</v>
       </c>
@@ -14064,7 +14063,7 @@
         <v>"INT9" As "Doble Titulación",</v>
       </c>
     </row>
-    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>2021</v>
       </c>
@@ -14094,7 +14093,7 @@
         <v>"INT10" As "Consultoría de investigación internacional",</v>
       </c>
     </row>
-    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>2021</v>
       </c>
@@ -14124,7 +14123,7 @@
         <v>"INT11" As "Ean Filantropía",</v>
       </c>
     </row>
-    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>2021</v>
       </c>
@@ -14154,7 +14153,7 @@
         <v>"INT12" As "No conozco ninguno",</v>
       </c>
     </row>
-    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>2021</v>
       </c>
@@ -14184,7 +14183,7 @@
         <v>"INT13" As "¿Has participado en alguno de los programas mencionados anteriormente?",</v>
       </c>
     </row>
-    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>2021</v>
       </c>
@@ -14214,7 +14213,7 @@
         <v>"INT14" As "¿Te interesaría participar en el futuro en alguno de los programas mencionados anteriormente?",</v>
       </c>
     </row>
-    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>2021</v>
       </c>
@@ -14244,7 +14243,7 @@
         <v>"INT15" As "¿Conoces la oferta de convenios con universidades aliadas para hacer intercambios académicos?",</v>
       </c>
     </row>
-    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>2021</v>
       </c>
@@ -14274,7 +14273,7 @@
         <v>"INT16" As "¿Qué tan relevante es para tu desarrollo académico y profesional participar en uno de los programas de movilidad y proyección global?",</v>
       </c>
     </row>
-    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>2021</v>
       </c>
@@ -14304,7 +14303,7 @@
         <v>"INT17" As "¿Qué tan satisfecho te encuentras con la calidad de los servicios que brinda el equipo de Internacionalización?",</v>
       </c>
     </row>
-    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>2021</v>
       </c>
@@ -14334,7 +14333,7 @@
         <v>"PF1" As "¿Conoces los servicios, políticas y alcances de la oficina de Prácticas Profesionales?",</v>
       </c>
     </row>
-    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>2021</v>
       </c>
@@ -14364,7 +14363,7 @@
         <v>"PF2" As "¿Qué tan satisfecho te encuentras con el apoyo ofrecido desde Prácticas Profesionales de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>2021</v>
       </c>
@@ -14394,7 +14393,7 @@
         <v>"PF3" As "¿Qué tan satisfecho te encuentras con la calidad de los servicios que brinda el equipo de Prácticas Profesionales?",</v>
       </c>
     </row>
-    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>2021</v>
       </c>
@@ -14424,7 +14423,7 @@
         <v>"TIC1" As "¿Qué tan satisfecho te encuentras con la plataforma de Correo electrónico?",</v>
       </c>
     </row>
-    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>2021</v>
       </c>
@@ -14454,7 +14453,7 @@
         <v>"TIC2" As "¿Qué tan satisfecho te encuentras con la plataforma y la información que encuentras en SAP?",</v>
       </c>
     </row>
-    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>2021</v>
       </c>
@@ -14484,7 +14483,7 @@
         <v>"TIC3" As "¿Qué tan satisfecho te encuentras con el soporte técnico brindado para el Correo electrónico?",</v>
       </c>
     </row>
-    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>2021</v>
       </c>
@@ -14514,7 +14513,7 @@
         <v>"TIC4" As "¿Qué tan satisfecho te encuentras con el soporte técnico brindado para SAP?",</v>
       </c>
     </row>
-    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>2021</v>
       </c>
@@ -14544,7 +14543,7 @@
         <v>"MD1" As "¿Qué tan satisfecho te encuentras con la plataforma virtual Canvas?",</v>
       </c>
     </row>
-    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>2021</v>
       </c>
@@ -14574,7 +14573,7 @@
         <v>"MD2" As "¿Qué tan satisfecho te encuentras con Cisco Webex?",</v>
       </c>
     </row>
-    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>2021</v>
       </c>
@@ -14604,7 +14603,7 @@
         <v>"MD3" As "¿Qué tan satisfecho te encuentras con el soporte técnico brindado para la plataforma Canvas y Cisco Webex?",</v>
       </c>
     </row>
-    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>2021</v>
       </c>
@@ -14634,7 +14633,7 @@
         <v>"TIC5" As "Red (Internet)",</v>
       </c>
     </row>
-    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>2021</v>
       </c>
@@ -14664,7 +14663,7 @@
         <v>"TIC6" As "Correo electrónico",</v>
       </c>
     </row>
-    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>2021</v>
       </c>
@@ -14694,7 +14693,7 @@
         <v>"TIC7" As "Aplicación Móvil",</v>
       </c>
     </row>
-    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>2021</v>
       </c>
@@ -14724,7 +14723,7 @@
         <v>"TIC8" As "Control acceso",</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>2021</v>
       </c>
@@ -14754,7 +14753,7 @@
         <v>"MD4" As "¿Qué tan fácil ha sido el uso y acceso de Canvas y Cisco Webex?",</v>
       </c>
     </row>
-    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>2021</v>
       </c>
@@ -14784,7 +14783,7 @@
         <v>"RA1" As "¿Qué tan satisfecho te encuentras con los servicios ofrecidos por el área de registro académico de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>2021</v>
       </c>
@@ -14814,7 +14813,7 @@
         <v>"RA2" As "En relación con los tiempos de respuesta de registro académico ¿Qué tan satisfecho te encuentras?",</v>
       </c>
     </row>
-    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>2021</v>
       </c>
@@ -14844,7 +14843,7 @@
         <v>"RA3" As "¿Qué tan satisfecho te encuentras con la calidad de la atención que brinda el equipo de Registro Académico?",</v>
       </c>
     </row>
-    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>2021</v>
       </c>
@@ -14874,7 +14873,7 @@
         <v>"APF1" As "¿Conoces los convenios y opciones de financiación dispuestos por la Universidad para la financiación de matrícula?",</v>
       </c>
     </row>
-    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>2021</v>
       </c>
@@ -14904,7 +14903,7 @@
         <v>"APF2" As "Ean Respalda",</v>
       </c>
     </row>
-    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>2021</v>
       </c>
@@ -14934,7 +14933,7 @@
         <v>"APF3" As "Ean Fraccionamiento",</v>
       </c>
     </row>
-    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>2021</v>
       </c>
@@ -14964,7 +14963,7 @@
         <v>"APF4" As "Fundación Michelsen",</v>
       </c>
     </row>
-    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>2021</v>
       </c>
@@ -14994,7 +14993,7 @@
         <v>"APF5" As "Financiar",</v>
       </c>
     </row>
-    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>2021</v>
       </c>
@@ -15024,7 +15023,7 @@
         <v>"APF6" As "Lumni Respalda",</v>
       </c>
     </row>
-    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>2021</v>
       </c>
@@ -15054,7 +15053,7 @@
         <v>"APF7" As "Sufi Bancolombia",</v>
       </c>
     </row>
-    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>2021</v>
       </c>
@@ -15084,7 +15083,7 @@
         <v>"APF8" As "Somec",</v>
       </c>
     </row>
-    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>2021</v>
       </c>
@@ -15114,7 +15113,7 @@
         <v>"APF9" As "Lumni",</v>
       </c>
     </row>
-    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>2021</v>
       </c>
@@ -15144,7 +15143,7 @@
         <v>"APF10" As "Fincomercio – Fincoeducar",</v>
       </c>
     </row>
-    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>2021</v>
       </c>
@@ -15174,7 +15173,7 @@
         <v>"APF11" As "Banco Pichincha",</v>
       </c>
     </row>
-    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>2021</v>
       </c>
@@ -15204,7 +15203,7 @@
         <v>"APF12" As "Banco Av Villas",</v>
       </c>
     </row>
-    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>2021</v>
       </c>
@@ -15234,7 +15233,7 @@
         <v>"APF13" As "Icetex",</v>
       </c>
     </row>
-    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>2021</v>
       </c>
@@ -15264,7 +15263,7 @@
         <v>"APF14" As "No he utilizado ninguna",</v>
       </c>
     </row>
-    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>2021</v>
       </c>
@@ -15294,7 +15293,7 @@
         <v>"APF15" As "¿Qué tan satisfecho te encuentras con el servicio recibido de la entidad financiera?",</v>
       </c>
     </row>
-    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>2021</v>
       </c>
@@ -15324,7 +15323,7 @@
         <v>"APF16" As "¿Qué tan satisfecho te encuentras con la calidad de los servicios ofrecidos por el área de Apoyo Financiero y Recursos Financieros de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>2021</v>
       </c>
@@ -15354,7 +15353,7 @@
         <v>"APF17" As "¿Qué tan satisfecho te encuentras con los procedimientos y tiempos de respuesta para aplicación de descuentos?",</v>
       </c>
     </row>
-    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>2021</v>
       </c>
@@ -15384,7 +15383,7 @@
         <v>"APF18" As "¿Qué tan satisfecho te encuentras con los canales dispuestos para el pago de matrícula y otros servicios académicos?",</v>
       </c>
     </row>
-    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>2021</v>
       </c>
@@ -15414,7 +15413,7 @@
         <v>"APF19" As "¿Qué tan satisfecho te sientes con la atención brindada por los colaboradores del proceso de Apoyo Financiero y Recursos Financieros?",</v>
       </c>
     </row>
-    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>2021</v>
       </c>
@@ -15444,7 +15443,7 @@
         <v>"CC1" As "¿Qué tan satisfecho te encuentras con la atención telefónica cuando llamas al PBX de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>2021</v>
       </c>
@@ -15474,7 +15473,7 @@
         <v>"CC2" As "Facebook",</v>
       </c>
     </row>
-    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>2021</v>
       </c>
@@ -15504,7 +15503,7 @@
         <v>"CC3" As "Instagram",</v>
       </c>
     </row>
-    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>2021</v>
       </c>
@@ -15534,7 +15533,7 @@
         <v>"CC4" As "Twitter",</v>
       </c>
     </row>
-    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>2021</v>
       </c>
@@ -15564,7 +15563,7 @@
         <v>"CC5" As "LinKedIn",</v>
       </c>
     </row>
-    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>2021</v>
       </c>
@@ -15594,7 +15593,7 @@
         <v>"CC6" As "Todos los anteriores",</v>
       </c>
     </row>
-    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>2021</v>
       </c>
@@ -15624,7 +15623,7 @@
         <v>"CC07" As "Ninguno",</v>
       </c>
     </row>
-    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>2021</v>
       </c>
@@ -15654,7 +15653,7 @@
         <v>"CC8" As "¿Qué tan satisfecho te encuentras con el contenido que se encuentra en la página web de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>2021</v>
       </c>
@@ -15684,7 +15683,7 @@
         <v>"CC9" As "¿Qué tan satisfecho te encuentras con la App de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>2021</v>
       </c>
@@ -15714,7 +15713,7 @@
         <v>"CC10" As "¿Has interactuado con el Chat Bot E- Ann ubicado en la página web de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>2021</v>
       </c>
@@ -15744,7 +15743,7 @@
         <v>"CC11" As "¿Qué tan satisfecho te encuentras con la información que encuentras en el Bot?",</v>
       </c>
     </row>
-    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>2021</v>
       </c>
@@ -15774,7 +15773,7 @@
         <v>"INST1" As "¿Qué tan satisfecho te encuentras con el soporte brindado a través de las Salas Teams?",</v>
       </c>
     </row>
-    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>2021</v>
       </c>
@@ -15804,7 +15803,7 @@
         <v>"CC12" As "¿Qué tan satisfecho te encuentras con la información que recibes a través del Correo Electrónico de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>2021</v>
       </c>
@@ -15834,7 +15833,7 @@
         <v>"CC13" As "¿Con qué frecuencia te gustaría recibir correos electrónicos de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>2021</v>
       </c>
@@ -15864,7 +15863,7 @@
         <v>"CC14" As "¿Cuál de los siguientes canales consideras que es el más efectivo para resolver tus inquietudes o requerimientos?",</v>
       </c>
     </row>
-    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>2021</v>
       </c>
@@ -15894,7 +15893,7 @@
         <v>"PFSL5" As "Accesibilidad",</v>
       </c>
     </row>
-    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>2021</v>
       </c>
@@ -15924,7 +15923,7 @@
         <v>"PFSL6" As "Capacidad",</v>
       </c>
     </row>
-    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>2021</v>
       </c>
@@ -15954,7 +15953,7 @@
         <v>"PFSL7" As "Ventilación",</v>
       </c>
     </row>
-    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>2021</v>
       </c>
@@ -15984,7 +15983,7 @@
         <v>"PFSL8" As "Condiciones de Seguridad",</v>
       </c>
     </row>
-    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>2021</v>
       </c>
@@ -16014,7 +16013,7 @@
         <v>"PFSL9" As "Aseo",</v>
       </c>
     </row>
-    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>2021</v>
       </c>
@@ -16044,7 +16043,7 @@
         <v>"PFSL10" As "Disponibilidad",</v>
       </c>
     </row>
-    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>2021</v>
       </c>
@@ -16074,7 +16073,7 @@
         <v>"PFSL11" As "Acceso a Internet",</v>
       </c>
     </row>
-    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>2021</v>
       </c>
@@ -16104,7 +16103,7 @@
         <v>"TIC9" As "Tecnología",</v>
       </c>
     </row>
-    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>2021</v>
       </c>
@@ -16134,7 +16133,7 @@
         <v>"PFSL12" As "¿Qué tan satisfecho te encuentras con el espacio dispuesto para las cafeterías de la Universidad?",</v>
       </c>
     </row>
-    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>2021</v>
       </c>
@@ -16164,7 +16163,7 @@
         <v>"PFSL13" As "¿Qué tan satisfecho te encuentras con los productos ofrecidos en las cafeterías de la Universidad?",</v>
       </c>
     </row>
-    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>2021</v>
       </c>
@@ -16194,7 +16193,7 @@
         <v>"PFSL14" As "¿Qué tan satisfecho te encuentras con Frutiice?",</v>
       </c>
     </row>
-    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>2021</v>
       </c>
@@ -16224,7 +16223,7 @@
         <v>"PFSL15" As "¿Qué tan satisfecho te encuentras con los productos ofrecidos en Frutiice?",</v>
       </c>
     </row>
-    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>2021</v>
       </c>
@@ -16254,7 +16253,7 @@
         <v>"PFSL16" As "¡Estamos muy felices de nuestro Ean Legacy! Queremos saber ¿Cuál es el espacio que más te gusta?",</v>
       </c>
     </row>
-    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>2021</v>
       </c>
@@ -16284,7 +16283,7 @@
         <v>"PFSL17" As "¿Qué tan satisfecho te encuentras con la atención del personal de seguridad en la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>2021</v>
       </c>
@@ -16314,7 +16313,7 @@
         <v>"PFSL18" As "¿Qué tan satisfecho te encuentras con el servicio del personal de aseo en la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>2021</v>
       </c>
@@ -16344,7 +16343,7 @@
         <v>"PFSL19" As "¿Qué tan satisfecho te encuentras con el servicio de audiovisuales en la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>2021</v>
       </c>
@@ -16374,7 +16373,7 @@
         <v>"PFSL20" As "¿Qué tan satisfecho te encuentras con el servicio de parqueadero en la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>2021</v>
       </c>
@@ -16404,7 +16403,7 @@
         <v>"GEE01" As "Gimnasio",</v>
       </c>
     </row>
-    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>2021</v>
       </c>
@@ -16434,7 +16433,7 @@
         <v>"GEE02" As "Grupos Culturales",</v>
       </c>
     </row>
-    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>2021</v>
       </c>
@@ -16464,7 +16463,7 @@
         <v>"GEE03" As "Clases Deportivas (Fútbol, baloncesto, natación, etc.)",</v>
       </c>
     </row>
-    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>2021</v>
       </c>
@@ -16494,7 +16493,7 @@
         <v>"GEE04" As "Clases de habilidades humanas (inteligencia emocional, mindfulness, etc.)",</v>
       </c>
     </row>
-    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>2021</v>
       </c>
@@ -16524,7 +16523,7 @@
         <v>"GEE05" As "Café de la Diversidad, FrEands",</v>
       </c>
     </row>
-    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>2021</v>
       </c>
@@ -16554,7 +16553,7 @@
         <v>"GEE06" As "Servicio de salud (Consulta medicina general, enfermería, planificación familiar, etc)",</v>
       </c>
     </row>
-    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>2021</v>
       </c>
@@ -16584,7 +16583,7 @@
         <v>"GEE07" As "Atención Psicosocial",</v>
       </c>
     </row>
-    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>2021</v>
       </c>
@@ -16614,7 +16613,7 @@
         <v>"GEE08" As "Eventos (Jornadas de Bienvenida, Semana de la Salud, Semana de la Cultura y Semana Fitness Ean)",</v>
       </c>
     </row>
-    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>2021</v>
       </c>
@@ -16644,7 +16643,7 @@
         <v>"GEE09" As "Póliza de accidentes personales",</v>
       </c>
     </row>
-    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>2021</v>
       </c>
@@ -16674,7 +16673,7 @@
         <v>"GEE10_2" As "Utilización de Salón de juegos: préstamo de implementos deportivos, mesa de tenis de mesa",</v>
       </c>
     </row>
-    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>2021</v>
       </c>
@@ -16704,7 +16703,7 @@
         <v>"GEE11_2" As "Programa Pedaleando (Alquiler de Bicicletas)",</v>
       </c>
     </row>
-    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>2021</v>
       </c>
@@ -16734,7 +16733,7 @@
         <v>"CC7_2" As "Ninguno",</v>
       </c>
     </row>
-    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>2021</v>
       </c>
@@ -16764,7 +16763,7 @@
         <v>"GEE1" As "Gimnasio",</v>
       </c>
     </row>
-    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>2021</v>
       </c>
@@ -16794,7 +16793,7 @@
         <v>"GEE2" As "Grupos Culturales",</v>
       </c>
     </row>
-    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>2021</v>
       </c>
@@ -16824,7 +16823,7 @@
         <v>"GEE3" As "Clases Deportivas (Fútbol, baloncesto, natación, etc.)",</v>
       </c>
     </row>
-    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>2021</v>
       </c>
@@ -16854,7 +16853,7 @@
         <v>"GEE4" As "Clases de habilidades humanas (inteligencia emocional, mindfulness, etc.)",</v>
       </c>
     </row>
-    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>2021</v>
       </c>
@@ -16884,7 +16883,7 @@
         <v>"GEE5" As "Café de la Diversidad, FrEands",</v>
       </c>
     </row>
-    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>2021</v>
       </c>
@@ -16914,7 +16913,7 @@
         <v>"GEE6" As "Servicio de salud (Consulta medicina general, enfermería, planificación familiar, etc)",</v>
       </c>
     </row>
-    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>2021</v>
       </c>
@@ -16944,7 +16943,7 @@
         <v>"GEE7" As "Atención Psicosocial",</v>
       </c>
     </row>
-    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>2021</v>
       </c>
@@ -16974,7 +16973,7 @@
         <v>"GEE8" As "Eventos (Jornadas de Bienvenida, Semana de la Salud, Semana de la Cultura y Semana Fitness Ean)",</v>
       </c>
     </row>
-    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>2021</v>
       </c>
@@ -17004,7 +17003,7 @@
         <v>"GEE9" As "Póliza de accidentes personales",</v>
       </c>
     </row>
-    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>2021</v>
       </c>
@@ -17034,7 +17033,7 @@
         <v>"GEE10" As "Utilización de Salón de juegos: préstamo de implementos deportivos, mesa de tenis de mesa",</v>
       </c>
     </row>
-    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>2021</v>
       </c>
@@ -17064,7 +17063,7 @@
         <v>"GEE11" As "Programa Pedaleando (Alquiler de Bicicletas)",</v>
       </c>
     </row>
-    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>2021</v>
       </c>
@@ -17094,7 +17093,7 @@
         <v>"GEE24" As "Other",</v>
       </c>
     </row>
-    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>2021</v>
       </c>
@@ -17124,7 +17123,7 @@
         <v>"GEE25" As "¿Qué tan satisfecho te encuentras con la calidad de los servicios que brinda Bienestar Universitario?",</v>
       </c>
     </row>
-    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>2021</v>
       </c>
@@ -17154,7 +17153,7 @@
         <v>"GEE26" As "¿Conoces la App Fitness Ean?",</v>
       </c>
     </row>
-    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>2021</v>
       </c>
@@ -17184,7 +17183,7 @@
         <v>"GEE27" As "Acompañamiento en el proceso de renovación de matrícula",</v>
       </c>
     </row>
-    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>2021</v>
       </c>
@@ -17214,7 +17213,7 @@
         <v>"GEE28" As "Programa Ean Contigo",</v>
       </c>
     </row>
-    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>2021</v>
       </c>
@@ -17244,7 +17243,7 @@
         <v>"GEE29" As "Mentores Académicos",</v>
       </c>
     </row>
-    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>2021</v>
       </c>
@@ -17274,7 +17273,7 @@
         <v>"GEE30" As "Orientación Psicopedagógica",</v>
       </c>
     </row>
-    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>2021</v>
       </c>
@@ -17304,7 +17303,7 @@
         <v>"GEE31" As "Contacto para conocer el desarrollo de tu proceso académico",</v>
       </c>
     </row>
-    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>2021</v>
       </c>
@@ -17334,7 +17333,7 @@
         <v>"CC7_3" As "Ninguno",</v>
       </c>
     </row>
-    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>2021</v>
       </c>
@@ -17364,7 +17363,7 @@
         <v>"GEE33" As "¿Qué tan satisfecho te encuentras con la calidad de los servicios que brinda el equipo de Permanencia Estudiantil?",</v>
       </c>
     </row>
-    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>2021</v>
       </c>
@@ -17394,7 +17393,7 @@
         <v>"GEE34" As "Talleres de empleabilidad",</v>
       </c>
     </row>
-    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>2021</v>
       </c>
@@ -17424,7 +17423,7 @@
         <v>"GEE35" As "Asesoría en Hoja de Vida",</v>
       </c>
     </row>
-    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>2021</v>
       </c>
@@ -17454,7 +17453,7 @@
         <v>"GEE36" As "Bolsa de Empleo",</v>
       </c>
     </row>
-    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>2021</v>
       </c>
@@ -17484,7 +17483,7 @@
         <v>"GEE37" As "Seminario y talleres para el trabajo",</v>
       </c>
     </row>
-    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>2021</v>
       </c>
@@ -17514,7 +17513,7 @@
         <v>"CC7_4" As "Ninguno",</v>
       </c>
     </row>
-    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>2021</v>
       </c>
@@ -17544,7 +17543,7 @@
         <v>"GEE39" As "¿Qué tan satisfecho te encuentras con la calidad de los servicios que brinda el equipo del programa Empleabilidad?",</v>
       </c>
     </row>
-    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>2021</v>
       </c>
@@ -17574,7 +17573,7 @@
         <v>"GEE40" As "¿Conoces los servicios y el rol que desempeña la Defensoría Universitaria?",</v>
       </c>
     </row>
-    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>2021</v>
       </c>
@@ -17604,7 +17603,7 @@
         <v>"GEE41" As "¿Qué tan satisfecho te encuentras con el servicio brindado desde la Defensoría Universitaria?",</v>
       </c>
     </row>
-    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>2021</v>
       </c>
@@ -17634,7 +17633,7 @@
         <v>"INST2" As "¿Conoces la estrategia de la Universidad con la calificación de atención a través de QR?",</v>
       </c>
     </row>
-    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>2021</v>
       </c>
@@ -17664,7 +17663,7 @@
         <v>"PFSL21" As "Si has retornado a la presencialidad, ¿consideras que los protocolos de Bioseguridad son los adecuados para el retorno?",</v>
       </c>
     </row>
-    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>2021</v>
       </c>
@@ -17694,7 +17693,7 @@
         <v>"INST3" As "¿Qué tan satisfecho te encuentras con los horarios en los cuales las áreas de la Universidad atienden a sus estudiantes de manera remota-virtual?",</v>
       </c>
     </row>
-    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>2021</v>
       </c>
@@ -17724,7 +17723,7 @@
         <v>"INST4" As "¿Qué tan satisfecho te encuentras con los horarios en los cuales las áreas de la Universidad atienden a sus estudiantes de manera presencial?",</v>
       </c>
     </row>
-    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>2021</v>
       </c>
@@ -17754,7 +17753,7 @@
         <v>"INST5" As "¿Qué tan satisfecho te encuentras con el servicio que te brindamos al ingreso y recepción de la Universidad?",</v>
       </c>
     </row>
-    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>2021</v>
       </c>
@@ -17784,7 +17783,7 @@
         <v>"INST6" As "¿Quieres destacar algo positivo de la Universidad Ean? ¿Crees que podemos mejorar en algo más?",</v>
       </c>
     </row>
-    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>2021</v>
       </c>
@@ -17814,7 +17813,7 @@
         <v>"INST7" As "En una escala de 0 a 10 ¿Qué tan probable es que recomiendes los servicios y la atención que te brindamos en la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>2021</v>
       </c>
@@ -17844,7 +17843,7 @@
         <v>"Start Date (UTC)" As "Start Date (UTC)",</v>
       </c>
     </row>
-    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>2021</v>
       </c>
@@ -17874,7 +17873,7 @@
         <v>"Submit Date (UTC)" As "Submit Date (UTC)",</v>
       </c>
     </row>
-    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>2021</v>
       </c>
@@ -17904,7 +17903,7 @@
         <v>"Network ID" As "Network ID",</v>
       </c>
     </row>
-    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>2022</v>
       </c>
@@ -17934,7 +17933,7 @@
         <v>"Item" As "Item",</v>
       </c>
     </row>
-    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>2022</v>
       </c>
@@ -17964,7 +17963,7 @@
         <v>"Año" As "Año",</v>
       </c>
     </row>
-    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>2022</v>
       </c>
@@ -17994,7 +17993,7 @@
         <v>"Cedula" As "Cedula",</v>
       </c>
     </row>
-    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>2022</v>
       </c>
@@ -18024,7 +18023,7 @@
         <v>"Facultad" As "Facultad",</v>
       </c>
     </row>
-    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>2022</v>
       </c>
@@ -18054,7 +18053,7 @@
         <v>"Programa" As "Programa",</v>
       </c>
     </row>
-    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>2022</v>
       </c>
@@ -18084,7 +18083,7 @@
         <v>"Metododologia" As "Metododologia",</v>
       </c>
     </row>
-    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>2022</v>
       </c>
@@ -18114,7 +18113,7 @@
         <v>"AC1" As "Plan de estudios de tu programa",</v>
       </c>
     </row>
-    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>2022</v>
       </c>
@@ -18144,7 +18143,7 @@
         <v>"AC2" As "Las competencias propuestas en las unidades cursadas hasta el momento",</v>
       </c>
     </row>
-    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>2022</v>
       </c>
@@ -18174,7 +18173,7 @@
         <v>"AC3" As "¿Que tan cumplida ha sido la Universidad Ean respecto a la promesa de valor academica ofrecida por el programa que cursas actualmente",</v>
       </c>
     </row>
-    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>2022</v>
       </c>
@@ -18204,7 +18203,7 @@
         <v>"AC4" As "Conocimiento disciplinar",</v>
       </c>
     </row>
-    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>2022</v>
       </c>
@@ -18234,7 +18233,7 @@
         <v>"AC5" As "Competencias para la ensenanza y la formacion",</v>
       </c>
     </row>
-    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>2022</v>
       </c>
@@ -18264,7 +18263,7 @@
         <v>"AC6" As "Cumplimiento del Syllabus y plan de estudios del programa",</v>
       </c>
     </row>
-    <row r="457" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>2022</v>
       </c>
@@ -18294,7 +18293,7 @@
         <v>"AC7" As "Evaluacion y acompanamiento del proceso de aprendizaje",</v>
       </c>
     </row>
-    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>2022</v>
       </c>
@@ -18324,7 +18323,7 @@
         <v>"AC8" As "Entrega de calificaciones y feedback",</v>
       </c>
     </row>
-    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>2022</v>
       </c>
@@ -18354,7 +18353,7 @@
         <v>"MD1" As "Aulas Virtuales",</v>
       </c>
     </row>
-    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>2022</v>
       </c>
@@ -18384,7 +18383,7 @@
         <v>"AC9" As "Decano",</v>
       </c>
     </row>
-    <row r="461" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>2022</v>
       </c>
@@ -18414,7 +18413,7 @@
         <v>"AC10" As "Director de Programa",</v>
       </c>
     </row>
-    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>2022</v>
       </c>
@@ -18444,7 +18443,7 @@
         <v>"AC11" As "Coordinador Unidades de Estudio Transversales",</v>
       </c>
     </row>
-    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>2022</v>
       </c>
@@ -18474,7 +18473,7 @@
         <v>"AC12" As "En general ¿Que tan satisfecho te encuentras con la atencion y el servicio recibido de manera presencial y a traves de las salas teams por parte del equipo de la Unidad Academico Administrativa",</v>
       </c>
     </row>
-    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>2022</v>
       </c>
@@ -18504,7 +18503,7 @@
         <v>"AC13" As "En general ¿Que tan satisfecho te encuentras con la atencion y el servicio recibido por parte de los asistentes de tu Facultad",</v>
       </c>
     </row>
-    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>2022</v>
       </c>
@@ -18534,7 +18533,7 @@
         <v>"MD2" As "En general ¿Que tan satisfecho te encuentras con la atencion y el servicio recibido de manera presencial y a traves de las salas teams por parte del equipo de Mediaciones Didacticas",</v>
       </c>
     </row>
-    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>2022</v>
       </c>
@@ -18564,7 +18563,7 @@
         <v>"ASSMC1" As "En general ¿Que tan satisfecho te encuentras con la atencion y el servicio recibido de manera presencial y a traves de las salas teams por parte del equipo de Assessment Center",</v>
       </c>
     </row>
-    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>2022</v>
       </c>
@@ -18594,7 +18593,7 @@
         <v>"AC14" As "En general ¿Que tan satisfecho te encuentras con la atencion y el servicio recibido de manera presencial y a traves de las salas teams por parte del equipo de Investigacion y Trabajo de Grado",</v>
       </c>
     </row>
-    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>2022</v>
       </c>
@@ -18624,7 +18623,7 @@
         <v>"LAB1" As "Disponibilidad y funcionamiento de los equipos",</v>
       </c>
     </row>
-    <row r="469" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>2022</v>
       </c>
@@ -18654,7 +18653,7 @@
         <v>"LAB2" As "Disponibilidad de materiales y/o reactivos",</v>
       </c>
     </row>
-    <row r="470" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>2022</v>
       </c>
@@ -18684,7 +18683,7 @@
         <v>"LAB3" As "Instalaciones",</v>
       </c>
     </row>
-    <row r="471" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>2022</v>
       </c>
@@ -18714,7 +18713,7 @@
         <v>"LAB4" As "Higiene y limpieza las Instalaciones y Equipos",</v>
       </c>
     </row>
-    <row r="472" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>2022</v>
       </c>
@@ -18744,7 +18743,7 @@
         <v>"LAB5" As "Capacidad del Laboratorio",</v>
       </c>
     </row>
-    <row r="473" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>2022</v>
       </c>
@@ -18774,7 +18773,7 @@
         <v>"AC15" As "¿Que tan probable es que recomiendes tu programa academico con familiares y amigos",</v>
       </c>
     </row>
-    <row r="474" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>2022</v>
       </c>
@@ -18804,7 +18803,7 @@
         <v>"AC16" As "¿Que tan probable es que en el futuro vuelvas a estudiar un programa academico en la Universidad Ean",</v>
       </c>
     </row>
-    <row r="475" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>2022</v>
       </c>
@@ -18834,7 +18833,7 @@
         <v>"EANIMP1" As "¿Conoces los servicios y beneficios que dispone Ean Impacta para todos sus estudiantes",</v>
       </c>
     </row>
-    <row r="476" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>2022</v>
       </c>
@@ -18864,7 +18863,7 @@
         <v>"EANIMP2" As "¿Que tanto impacta el enfoque del emprendimiento sostenible en tu proceso formativo",</v>
       </c>
     </row>
-    <row r="477" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>2022</v>
       </c>
@@ -18894,7 +18893,7 @@
         <v>"EANIMP3" As "Innovacion",</v>
       </c>
     </row>
-    <row r="478" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>2022</v>
       </c>
@@ -18924,7 +18923,7 @@
         <v>"EANIMP4" As "Emprendimiento",</v>
       </c>
     </row>
-    <row r="479" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>2022</v>
       </c>
@@ -18954,7 +18953,7 @@
         <v>"EANIMP5" As "Sostenibilidad",</v>
       </c>
     </row>
-    <row r="480" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>2022</v>
       </c>
@@ -18984,7 +18983,7 @@
         <v>"EANIMP6" As "Calidad",</v>
       </c>
     </row>
-    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>2022</v>
       </c>
@@ -19014,7 +19013,7 @@
         <v>"EANIMP7" As "Diversidad",</v>
       </c>
     </row>
-    <row r="482" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>2022</v>
       </c>
@@ -19044,7 +19043,7 @@
         <v>"EANIMP8" As "Etica y valores",</v>
       </c>
     </row>
-    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>2022</v>
       </c>
@@ -19074,7 +19073,7 @@
         <v>"EANIMP9" As "Investigacion",</v>
       </c>
     </row>
-    <row r="484" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>2022</v>
       </c>
@@ -19104,7 +19103,7 @@
         <v>"EANIMP10" As "¿Que tan satisfecho te encuentras con la atencion y el servicio recibido por parte del equipo de Ean Impacta",</v>
       </c>
     </row>
-    <row r="485" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>2022</v>
       </c>
@@ -19134,7 +19133,7 @@
         <v>"B1" As "¿Que tan satisfechoa te encuentras con los servicios que presta la biblioteca de la Universidad Ean",</v>
       </c>
     </row>
-    <row r="486" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>2022</v>
       </c>
@@ -19164,7 +19163,7 @@
         <v>"B2" As "¿Que tan completas consideras las colecciones fisicas y electronicas en la biblioteca de la Universidad Ean",</v>
       </c>
     </row>
-    <row r="487" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>2022</v>
       </c>
@@ -19194,7 +19193,7 @@
         <v>"B3" As "¿Que tan facil ha sido el acceso a las colecciones electronicas en la biblioteca de la Universidad Ean",</v>
       </c>
     </row>
-    <row r="488" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>2022</v>
       </c>
@@ -19224,7 +19223,7 @@
         <v>"B4" As "En general ¿Que tan satisfecho te encuentras con la atencion y el servicio recibido de manera presencial y por sala teams por parte de los colaboradores de la Biblioteca",</v>
       </c>
     </row>
-    <row r="489" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>2022</v>
       </c>
@@ -19254,7 +19253,7 @@
         <v>"INT1" As "Intercambios academicos",</v>
       </c>
     </row>
-    <row r="490" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>2022</v>
       </c>
@@ -19284,7 +19283,7 @@
         <v>"INT2" As "Buddy Program",</v>
       </c>
     </row>
-    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>2022</v>
       </c>
@@ -19314,7 +19313,7 @@
         <v>"INT3" As "Misiones academicas",</v>
       </c>
     </row>
-    <row r="492" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>2022</v>
       </c>
@@ -19344,7 +19343,7 @@
         <v>"INT4" As "Semana Ean Internacional",</v>
       </c>
     </row>
-    <row r="493" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>2022</v>
       </c>
@@ -19374,7 +19373,7 @@
         <v>"INT5" As "Sesiones Ean Internacional",</v>
       </c>
     </row>
-    <row r="494" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>2022</v>
       </c>
@@ -19404,7 +19403,7 @@
         <v>"INT6" As "Escuela Internacional de Verano/Invierno",</v>
       </c>
     </row>
-    <row r="495" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>2022</v>
       </c>
@@ -19434,7 +19433,7 @@
         <v>"INT7" As "Vision Global con Brigitte Baptiste",</v>
       </c>
     </row>
-    <row r="496" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>2022</v>
       </c>
@@ -19464,7 +19463,7 @@
         <v>"INT8" As "Global Classroom",</v>
       </c>
     </row>
-    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>2022</v>
       </c>
@@ -19494,7 +19493,7 @@
         <v>"INT9" As "Doble Titulacion",</v>
       </c>
     </row>
-    <row r="498" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>2022</v>
       </c>
@@ -19524,7 +19523,7 @@
         <v>"INT10" As "Consultoria de investigacion internacional",</v>
       </c>
     </row>
-    <row r="499" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>2022</v>
       </c>
@@ -19554,7 +19553,7 @@
         <v>"INT11" As "No conozco ninguno",</v>
       </c>
     </row>
-    <row r="500" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>2022</v>
       </c>
@@ -19584,7 +19583,7 @@
         <v>"INT12" As "¿Has participado en alguno de los programas mencionados anteriormente",</v>
       </c>
     </row>
-    <row r="501" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>2022</v>
       </c>
@@ -19614,7 +19613,7 @@
         <v>"INT13" As "¿Conoces la oferta de convenios con universidades aliadas para hacer intercambios academicos",</v>
       </c>
     </row>
-    <row r="502" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>2022</v>
       </c>
@@ -19644,7 +19643,7 @@
         <v>"INT14" As "¿Que tan relevante es para tu desarrollo academico y profesional participar en uno de los programas de movilidad y proyeccion global",</v>
       </c>
     </row>
-    <row r="503" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>2022</v>
       </c>
@@ -19674,7 +19673,7 @@
         <v>"INT15" As "¿Conoces el programa Ean Filantropia",</v>
       </c>
     </row>
-    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>2022</v>
       </c>
@@ -19704,7 +19703,7 @@
         <v>"INT16" As "¿Que tan satisfecho te encuentras con la calidad de los servicios que brinda el equipo de Internacionalizacion",</v>
       </c>
     </row>
-    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>2022</v>
       </c>
@@ -19734,7 +19733,7 @@
         <v>"PF1" As "¿Conoces los servicios modalidades de practica y alcances de la oficina de Practicas Profesionales",</v>
       </c>
     </row>
-    <row r="506" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>2022</v>
       </c>
@@ -19764,7 +19763,7 @@
         <v>"PF2" As "¿Que tan satisfecho te encuentras con el apoyo ofrecido desde Practicas Profesionales para encontrar la empresa en donde realizaras la Practica Profesional",</v>
       </c>
     </row>
-    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>2022</v>
       </c>
@@ -19794,7 +19793,7 @@
         <v>"PF3" As "En general ¿Que tan satisfecho te encuentras con la atencion y el servicio recibido de manera presencial y por la sala teams por parte de los colaboradores de Practicas Profesionales",</v>
       </c>
     </row>
-    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>2022</v>
       </c>
@@ -19824,7 +19823,7 @@
         <v>"TIC1" As "¿Que tan satisfecho te encuentras con la plataforma de Correo electronico",</v>
       </c>
     </row>
-    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>2022</v>
       </c>
@@ -19854,7 +19853,7 @@
         <v>"TIC2" As "¿Que tan satisfecho te encuentras con la plataforma y la informacion que encuentras en SAP",</v>
       </c>
     </row>
-    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>2022</v>
       </c>
@@ -19884,7 +19883,7 @@
         <v>"MD3" As "¿Que tan satisfecho te encuentras con la plataforma virtual Canvas",</v>
       </c>
     </row>
-    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>2022</v>
       </c>
@@ -19914,7 +19913,7 @@
         <v>"TIC3" As "¿Que tan satisfecho te encuentras con Teams",</v>
       </c>
     </row>
-    <row r="512" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>2022</v>
       </c>
@@ -19944,7 +19943,7 @@
         <v>"TIC4" As "¿Que tan satisfecho te encuentras con Cisco Webex",</v>
       </c>
     </row>
-    <row r="513" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>2022</v>
       </c>
@@ -19974,7 +19973,7 @@
         <v>"TIC5" As "¿Que tan satisfecho te encuentras con la atencion y servicios recibidos de manera presencial y por sala teams en Soporte Officce por parte de los colaboradores del TIC",</v>
       </c>
     </row>
-    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>2022</v>
       </c>
@@ -20004,7 +20003,7 @@
         <v>"TIC6" As "Red Internet",</v>
       </c>
     </row>
-    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>2022</v>
       </c>
@@ -20034,7 +20033,7 @@
         <v>"TIC7" As "Correo electronico",</v>
       </c>
     </row>
-    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>2022</v>
       </c>
@@ -20064,7 +20063,7 @@
         <v>"TIC8" As "Aplicacion Movil",</v>
       </c>
     </row>
-    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>2022</v>
       </c>
@@ -20094,7 +20093,7 @@
         <v>"TIC9" As "Control acceso",</v>
       </c>
     </row>
-    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>2022</v>
       </c>
@@ -20124,7 +20123,7 @@
         <v>"TIC10" As "Equipos y software de las Salas de Computo",</v>
       </c>
     </row>
-    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>2022</v>
       </c>
@@ -20154,7 +20153,7 @@
         <v>"RA1" As "¿Que tan satisfecho te encuentras con los servicios ofrecidos por el area de registro academico de la Universidad Ean",</v>
       </c>
     </row>
-    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>2022</v>
       </c>
@@ -20184,7 +20183,7 @@
         <v>"RA2" As "En relacion con los tiempos de respuesta de registro academico ¿Que tan satisfecho te encuentras",</v>
       </c>
     </row>
-    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>2022</v>
       </c>
@@ -20214,7 +20213,7 @@
         <v>"RA3" As "¿Que tan satisfecho te encuentras con la atencion y servicios recibidos de manera presencial y por sala teams que brinda el equipo de Registro Academico",</v>
       </c>
     </row>
-    <row r="522" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>2022</v>
       </c>
@@ -20244,7 +20243,7 @@
         <v>"APF1" As "¿Conoces los convenios y opciones de financiacion dispuestos por la Universidad para la financiacion de matricula",</v>
       </c>
     </row>
-    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>2022</v>
       </c>
@@ -20274,7 +20273,7 @@
         <v>"APF2" As "Ean Respalda",</v>
       </c>
     </row>
-    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>2022</v>
       </c>
@@ -20304,7 +20303,7 @@
         <v>"APF3" As "Ean Fraccionamiento",</v>
       </c>
     </row>
-    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>2022</v>
       </c>
@@ -20334,7 +20333,7 @@
         <v>"APF4" As "Financiar",</v>
       </c>
     </row>
-    <row r="526" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>2022</v>
       </c>
@@ -20364,7 +20363,7 @@
         <v>"APF5" As "Lumni Respalda",</v>
       </c>
     </row>
-    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>2022</v>
       </c>
@@ -20394,7 +20393,7 @@
         <v>"APF6" As "Sufi Bancolombia",</v>
       </c>
     </row>
-    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>2022</v>
       </c>
@@ -20424,7 +20423,7 @@
         <v>"APF7" As "Fincomercio – Fincoeducar",</v>
       </c>
     </row>
-    <row r="529" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>2022</v>
       </c>
@@ -20454,7 +20453,7 @@
         <v>"APF8" As "Banco Av Villas",</v>
       </c>
     </row>
-    <row r="530" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>2022</v>
       </c>
@@ -20484,7 +20483,7 @@
         <v>"APF9" As "Icetex",</v>
       </c>
     </row>
-    <row r="531" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>2022</v>
       </c>
@@ -20514,7 +20513,7 @@
         <v>"APF10" As "No he utilizado ninguna",</v>
       </c>
     </row>
-    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>2022</v>
       </c>
@@ -20544,7 +20543,7 @@
         <v>"APF11" As "¿Que tan satisfecho te encuentras con el servicio recibido",</v>
       </c>
     </row>
-    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>2022</v>
       </c>
@@ -20574,7 +20573,7 @@
         <v>"APF12" As "¿Queremos conocer por que te encuentras insatisfecho",</v>
       </c>
     </row>
-    <row r="534" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>2022</v>
       </c>
@@ -20604,7 +20603,7 @@
         <v>"APF13" As "¿Que tan satisfecho te encuentras con los procedimientos y tiempos de respuesta para aplicacion de descuentos",</v>
       </c>
     </row>
-    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>2022</v>
       </c>
@@ -20634,7 +20633,7 @@
         <v>"APF14" As "¿Que tan satisfecho te encuentras con los canales dispuestos para el pago de matricula y otros servicios financieros",</v>
       </c>
     </row>
-    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>2022</v>
       </c>
@@ -20664,7 +20663,7 @@
         <v>"APF15" As "En general ¿Que tan satisfecho te encuentras con la atencion y servicios recibidos de manera presencial y por sala teams que brinda el equipo del area de Recursos Financieros",</v>
       </c>
     </row>
-    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>2022</v>
       </c>
@@ -20694,7 +20693,7 @@
         <v>"MC1" As "¿Que tan satisfecho te encuentras con la atencion telefonica cuando llamas al PBX de la Universidad Ean",</v>
       </c>
     </row>
-    <row r="538" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>2022</v>
       </c>
@@ -20724,7 +20723,7 @@
         <v>"MC2" As "Facebook",</v>
       </c>
     </row>
-    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>2022</v>
       </c>
@@ -20754,7 +20753,7 @@
         <v>"MC3" As "Instagram",</v>
       </c>
     </row>
-    <row r="540" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>2022</v>
       </c>
@@ -20784,7 +20783,7 @@
         <v>"MC4" As "Twitter",</v>
       </c>
     </row>
-    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>2022</v>
       </c>
@@ -20814,7 +20813,7 @@
         <v>"MC5" As "LinKedIn",</v>
       </c>
     </row>
-    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>2022</v>
       </c>
@@ -20844,7 +20843,7 @@
         <v>"MC6" As "TikTok",</v>
       </c>
     </row>
-    <row r="543" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>2022</v>
       </c>
@@ -20874,7 +20873,7 @@
         <v>"GEE21_2" As "Todos los anteriores",</v>
       </c>
     </row>
-    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>2022</v>
       </c>
@@ -20904,7 +20903,7 @@
         <v>"GEE12_2" As "Ninguno",</v>
       </c>
     </row>
-    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>2022</v>
       </c>
@@ -20934,7 +20933,7 @@
         <v>"MC9" As "¿Utilizas la App de la Universidad Ean",</v>
       </c>
     </row>
-    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>2022</v>
       </c>
@@ -20964,7 +20963,7 @@
         <v>"MC10" As "¿Has interactuado con el Chat Bot E Ann ubicado en la pagina web de la Universidad Ean",</v>
       </c>
     </row>
-    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>2022</v>
       </c>
@@ -20994,7 +20993,7 @@
         <v>"MC11" As "¿Que tan satisfecho te encuentras con la informacion que encuentras en el Chat Bot E Ann",</v>
       </c>
     </row>
-    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>2022</v>
       </c>
@@ -21024,7 +21023,7 @@
         <v>"MC12" As "¿Que tan satisfecho te encuentras con la informacion que recibes a traves del Correo Electronico de la Universidad Ean",</v>
       </c>
     </row>
-    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>2022</v>
       </c>
@@ -21054,7 +21053,7 @@
         <v>"MC13" As "¿Con que frecuencia te gustaria recibir correos electronicos de la Universidad Ean",</v>
       </c>
     </row>
-    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>2022</v>
       </c>
@@ -21084,7 +21083,7 @@
         <v>"MC14" As "¿Cual de los siguientes canales consideras que es el mas efectivo para resolver tus inquietudes o requerimientos",</v>
       </c>
     </row>
-    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>2022</v>
       </c>
@@ -21114,7 +21113,7 @@
         <v>"PFSL1" As "Accesibilidad",</v>
       </c>
     </row>
-    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>2022</v>
       </c>
@@ -21144,7 +21143,7 @@
         <v>"PFSL2" As "Capacidad",</v>
       </c>
     </row>
-    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>2022</v>
       </c>
@@ -21174,7 +21173,7 @@
         <v>"PFSL3" As "Ventilacion",</v>
       </c>
     </row>
-    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>2022</v>
       </c>
@@ -21204,7 +21203,7 @@
         <v>"PFSL4" As "Condiciones de Seguridad",</v>
       </c>
     </row>
-    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>2022</v>
       </c>
@@ -21234,7 +21233,7 @@
         <v>"PFSL5" As "Aseo",</v>
       </c>
     </row>
-    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>2022</v>
       </c>
@@ -21264,7 +21263,7 @@
         <v>"PFSL6" As "Disponibilidad",</v>
       </c>
     </row>
-    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>2022</v>
       </c>
@@ -21294,7 +21293,7 @@
         <v>"PFSL7" As "Acceso a Internet",</v>
       </c>
     </row>
-    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>2022</v>
       </c>
@@ -21324,7 +21323,7 @@
         <v>"TIC11" As "Tecnologia",</v>
       </c>
     </row>
-    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>2022</v>
       </c>
@@ -21354,7 +21353,7 @@
         <v>"PFSL8" As "Equipos audiovisuales",</v>
       </c>
     </row>
-    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>2022</v>
       </c>
@@ -21384,7 +21383,7 @@
         <v>"PFSL9" As "¿Que tan satisfecho te encuentras con los espacios dispuestos para la zona de alimentacion en la Universidad",</v>
       </c>
     </row>
-    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>2022</v>
       </c>
@@ -21414,7 +21413,7 @@
         <v>"PFSL10" As "¿Que tan satisfecho te encuentras con los productos ofrecidos en la cafeteria Delicaffe Ubicada en piso 1 Ean legacy",</v>
       </c>
     </row>
-    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>2022</v>
       </c>
@@ -21444,7 +21443,7 @@
         <v>"PFSL11" As "¿Que tan satisfecho te encuentras con el menu ofrecido por la cafeteria Delicaffe Ubicada en piso 1 Ean legacy",</v>
       </c>
     </row>
-    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>2022</v>
       </c>
@@ -21474,7 +21473,7 @@
         <v>"PFSL12" As "¿Que tan satisfecho te encuentras con los productos ofrecidos en Frutiice Ubicado en piso 4 Legacy y piso 4 Fundadores",</v>
       </c>
     </row>
-    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>2022</v>
       </c>
@@ -21504,7 +21503,7 @@
         <v>"PFSL13" As "Personal de Seguridad",</v>
       </c>
     </row>
-    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>2022</v>
       </c>
@@ -21534,7 +21533,7 @@
         <v>"PFSL14" As "Personal de aseo",</v>
       </c>
     </row>
-    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>2022</v>
       </c>
@@ -21564,7 +21563,7 @@
         <v>"PFSL15" As "Servicio de Parqueadero “City Parking”",</v>
       </c>
     </row>
-    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>2022</v>
       </c>
@@ -21594,7 +21593,7 @@
         <v>"PFSL16_2" As "Frutiice",</v>
       </c>
     </row>
-    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>2022</v>
       </c>
@@ -21624,7 +21623,7 @@
         <v>"PFSL17" As "Delicaffe",</v>
       </c>
     </row>
-    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>2022</v>
       </c>
@@ -21654,7 +21653,7 @@
         <v>"PFSL18" As "Servicio Auros Centro de copiado",</v>
       </c>
     </row>
-    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>2022</v>
       </c>
@@ -21684,7 +21683,7 @@
         <v>"PFSL16" As "Frutiice",</v>
       </c>
     </row>
-    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>2022</v>
       </c>
@@ -21714,7 +21713,7 @@
         <v>"PFSL20" As "Cafeteria Delicaffe",</v>
       </c>
     </row>
-    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>2022</v>
       </c>
@@ -21744,7 +21743,7 @@
         <v>"PFSL21" As "Centro de copiado",</v>
       </c>
     </row>
-    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>2022</v>
       </c>
@@ -21774,7 +21773,7 @@
         <v>"PFSL22" As "Parqueadero",</v>
       </c>
     </row>
-    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>2022</v>
       </c>
@@ -21804,7 +21803,7 @@
         <v>"GEE1" As "Gimnasio",</v>
       </c>
     </row>
-    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>2022</v>
       </c>
@@ -21834,7 +21833,7 @@
         <v>"GEE2" As "Grupos Culturales",</v>
       </c>
     </row>
-    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>2022</v>
       </c>
@@ -21864,7 +21863,7 @@
         <v>"GEE3" As "Clases Deportivas Futbol baloncesto natacion etc",</v>
       </c>
     </row>
-    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>2022</v>
       </c>
@@ -21894,7 +21893,7 @@
         <v>"GEE4" As "Clases de habilidades humanas inteligencia emocional mindfulness etc",</v>
       </c>
     </row>
-    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>2022</v>
       </c>
@@ -21924,7 +21923,7 @@
         <v>"GEE5" As "Servicio de salud Consulta medicina general enfermeria planificacion familiar etc",</v>
       </c>
     </row>
-    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>2022</v>
       </c>
@@ -21954,7 +21953,7 @@
         <v>"GEE6" As "Atencion Psicologica",</v>
       </c>
     </row>
-    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>2022</v>
       </c>
@@ -21984,7 +21983,7 @@
         <v>"GEE7" As "Eventos Jornadas de Bienvenida Semana de la Salud Semana de la Cultura y Semana Fitness Ean",</v>
       </c>
     </row>
-    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>2022</v>
       </c>
@@ -22014,7 +22013,7 @@
         <v>"GEE8" As "Poliza de accidentes personales",</v>
       </c>
     </row>
-    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>2022</v>
       </c>
@@ -22044,7 +22043,7 @@
         <v>"GEE9" As "Utilizacion de Salon de juegos: prestamo de implementos deportivos mesa de tenis de mesa",</v>
       </c>
     </row>
-    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>2022</v>
       </c>
@@ -22074,7 +22073,7 @@
         <v>"GEE10" As "Programa Pedaleando Alquiler de Bicicletas",</v>
       </c>
     </row>
-    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>2022</v>
       </c>
@@ -22104,7 +22103,7 @@
         <v>"GEE11" As "Todos",</v>
       </c>
     </row>
-    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>2022</v>
       </c>
@@ -22134,7 +22133,7 @@
         <v>"GEE12" As "Ninguno",</v>
       </c>
     </row>
-    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>2022</v>
       </c>
@@ -22164,7 +22163,7 @@
         <v>"GEE13" As "¿Que tan completo consideras el portafolio de programas y servicios que brinda Bienestar Universitario",</v>
       </c>
     </row>
-    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>2022</v>
       </c>
@@ -22194,7 +22193,7 @@
         <v>"GEE14" As "En general ¿Que tan satisfecho te encuentras con la atencion y el servicio ofrecido por Bienestar Universitario",</v>
       </c>
     </row>
-    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>2022</v>
       </c>
@@ -22224,7 +22223,7 @@
         <v>"GEE15" As "¿Conoces o has sido usuario de alguno de los apoyos o servicios de permanencia estudiantil",</v>
       </c>
     </row>
-    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>2022</v>
       </c>
@@ -22254,7 +22253,7 @@
         <v>"GEE16_2" As "Acompanamiento en el proceso de renovacion de matricula",</v>
       </c>
     </row>
-    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>2022</v>
       </c>
@@ -22284,7 +22283,7 @@
         <v>"GEE17_2" As "Programa Ean Contigo",</v>
       </c>
     </row>
-    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>2022</v>
       </c>
@@ -22314,7 +22313,7 @@
         <v>"GEE18_2" As "Mentores Academicos",</v>
       </c>
     </row>
-    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>2022</v>
       </c>
@@ -22344,7 +22343,7 @@
         <v>"GEE19_2" As "Orientacion Psicopedagogica",</v>
       </c>
     </row>
-    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>2022</v>
       </c>
@@ -22374,7 +22373,7 @@
         <v>"GEE20_2" As "Contacto para conocer el desarrollo de tu proceso academico",</v>
       </c>
     </row>
-    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>2022</v>
       </c>
@@ -22404,7 +22403,7 @@
         <v>"GEE21_3" As "Todos los anteriores",</v>
       </c>
     </row>
-    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>2022</v>
       </c>
@@ -22434,7 +22433,7 @@
         <v>"GEE16" As "Acompanamiento en el proceso de renovacion de matricula",</v>
       </c>
     </row>
-    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>2022</v>
       </c>
@@ -22464,7 +22463,7 @@
         <v>"GEE17" As "Programa Ean Contigo",</v>
       </c>
     </row>
-    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>2022</v>
       </c>
@@ -22494,7 +22493,7 @@
         <v>"GEE18" As "Mentores Academicos",</v>
       </c>
     </row>
-    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A598">
         <v>2022</v>
       </c>
@@ -22524,7 +22523,7 @@
         <v>"GEE19" As "Orientacion Psicopedagogica",</v>
       </c>
     </row>
-    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>2022</v>
       </c>
@@ -22554,7 +22553,7 @@
         <v>"GEE20" As "Contacto para conocer el desarrollo de tu proceso academico",</v>
       </c>
     </row>
-    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>2022</v>
       </c>
@@ -22584,7 +22583,7 @@
         <v>"GEE21" As "Todos los anteriores",</v>
       </c>
     </row>
-    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>2022</v>
       </c>
@@ -22614,7 +22613,7 @@
         <v>"GEE28" As "¿Conoces o has usado la bolsa de empleo o el programa de formacion para la empleabilidad que tiene la Universidad Ean para estudiantes y graduados",</v>
       </c>
     </row>
-    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>2022</v>
       </c>
@@ -22644,7 +22643,7 @@
         <v>"GEE29" As "No has necesitado estos servicios",</v>
       </c>
     </row>
-    <row r="603" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A603">
         <v>2022</v>
       </c>
@@ -22674,7 +22673,7 @@
         <v>"GEE30" As "Buscas oportunidades laborales en otras bolsas de empleo",</v>
       </c>
     </row>
-    <row r="604" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>2022</v>
       </c>
@@ -22704,7 +22703,7 @@
         <v>"GEE31" As "Other",</v>
       </c>
     </row>
-    <row r="605" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>2022</v>
       </c>
@@ -22734,7 +22733,7 @@
         <v>"GEE32" As "¿Conoces los servicios ofrecidos desde la Defensoria Universitaria",</v>
       </c>
     </row>
-    <row r="606" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A606">
         <v>2022</v>
       </c>
@@ -22764,7 +22763,7 @@
         <v>"GEE33" As "En general ¿Que tan satisfecho te encuentras con la atencion y el servicio ofrecido por la Oficina de Servicios al Estudiante de manera presencial y a traves de la sala teams",</v>
       </c>
     </row>
-    <row r="607" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A607">
         <v>2022</v>
       </c>
@@ -22794,7 +22793,7 @@
         <v>"HORA1" As "¿Que tan satisfecho te encuentras con el horario ofrecido por la Universidad para atencion de estudiantes de lunes a viernes de 07:00 am a 07:00 pm y sabado de 08:00 am a 01:00 pm",</v>
       </c>
     </row>
-    <row r="608" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A608">
         <v>2022</v>
       </c>
@@ -22824,7 +22823,7 @@
         <v>"GEE34" As "¿Que tan satisfecho te encuentras con el servicio que te brindamos al ingreso y recepcion de la Universidad",</v>
       </c>
     </row>
-    <row r="609" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A609">
         <v>2022</v>
       </c>
@@ -22854,7 +22853,7 @@
         <v>"COMENT1" As "¿Quieres destacar algo positivo de la Universidad Ean ¿Crees que podemos mejorar en algo mas",</v>
       </c>
     </row>
-    <row r="610" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A610">
         <v>2022</v>
       </c>
@@ -22884,7 +22883,7 @@
         <v>"INST1" As "En una escala de 0 a 10 ¿Que tan probable es que recomiendes los servicios y la atencion que te brindamos en la Universidad Ean",</v>
       </c>
     </row>
-    <row r="611" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611">
         <v>2022</v>
       </c>
@@ -22914,7 +22913,7 @@
         <v>"Start Date UTC" As "Start Date UTC",</v>
       </c>
     </row>
-    <row r="612" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A612">
         <v>2022</v>
       </c>
@@ -22944,7 +22943,7 @@
         <v>"Submit Date UTC" As "Submit Date UTC",</v>
       </c>
     </row>
-    <row r="613" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A613">
         <v>2022</v>
       </c>
@@ -22974,7 +22973,7 @@
         <v>"Network ID" As "Network ID",</v>
       </c>
     </row>
-    <row r="614" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A614">
         <v>2023</v>
       </c>
@@ -23004,7 +23003,7 @@
         <v>"Id_2023" As "Id_2023",</v>
       </c>
     </row>
-    <row r="615" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A615">
         <v>2023</v>
       </c>
@@ -23034,7 +23033,7 @@
         <v>"Para iniciar, por favor indícanos el número de tu documento de identidad:" As "Para iniciar, por favor indícanos el número de tu documento de identidad:",</v>
       </c>
     </row>
-    <row r="616" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A616">
         <v>2023</v>
       </c>
@@ -23064,7 +23063,7 @@
         <v>"Modalidad" As "Modalidad",</v>
       </c>
     </row>
-    <row r="617" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A617">
         <v>2023</v>
       </c>
@@ -23094,7 +23093,7 @@
         <v>"Programa" As "Programa",</v>
       </c>
     </row>
-    <row r="618" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618">
         <v>2023</v>
       </c>
@@ -23124,7 +23123,7 @@
         <v>"ACA1" As "Plan de estudios de tu programa",</v>
       </c>
     </row>
-    <row r="619" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>2023</v>
       </c>
@@ -23154,7 +23153,7 @@
         <v>"ACA2" As "Pertinencia de los conocimientos adquiridos en las clases",</v>
       </c>
     </row>
-    <row r="620" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620">
         <v>2023</v>
       </c>
@@ -23184,7 +23183,7 @@
         <v>"ACA3" As "Contribución del programa en tu proceso formativo",</v>
       </c>
     </row>
-    <row r="621" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>2023</v>
       </c>
@@ -23214,7 +23213,7 @@
         <v>"ACA4" As "¿Qué tan cumplida ha sido la Universidad Ean respecto a la promesa de valor académica ofrecida por el programa que cursas actualmente?",</v>
       </c>
     </row>
-    <row r="622" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622">
         <v>2023</v>
       </c>
@@ -23244,7 +23243,7 @@
         <v>"ACA5" As "Conforme al avance de tu programa académico:",</v>
       </c>
     </row>
-    <row r="623" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623">
         <v>2023</v>
       </c>
@@ -23274,7 +23273,7 @@
         <v>"ACA6" As "Conocimiento disciplinar",</v>
       </c>
     </row>
-    <row r="624" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624">
         <v>2023</v>
       </c>
@@ -23304,7 +23303,7 @@
         <v>"ACA7" As "Competencias para la enseñanza y la formación",</v>
       </c>
     </row>
-    <row r="625" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>2023</v>
       </c>
@@ -23334,7 +23333,7 @@
         <v>"ACA8" As "Cumplimiento del syllabus y plan de estudios del programa",</v>
       </c>
     </row>
-    <row r="626" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A626">
         <v>2023</v>
       </c>
@@ -23364,7 +23363,7 @@
         <v>"ACA9" As "Evaluación y acompañamiento del proceso de aprendizaje",</v>
       </c>
     </row>
-    <row r="627" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A627">
         <v>2023</v>
       </c>
@@ -23394,7 +23393,7 @@
         <v>"ACA10" As "Entrega de calificaciones y retroalimentación",</v>
       </c>
     </row>
-    <row r="628" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A628">
         <v>2023</v>
       </c>
@@ -23424,7 +23423,7 @@
         <v>"ACA11" As "Calidad humana",</v>
       </c>
     </row>
-    <row r="629" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>2023</v>
       </c>
@@ -23454,7 +23453,7 @@
         <v>"ACA12" As "Compromiso",</v>
       </c>
     </row>
-    <row r="630" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A630">
         <v>2023</v>
       </c>
@@ -23484,7 +23483,7 @@
         <v>"ACA13" As "Manejo tecnológico",</v>
       </c>
     </row>
-    <row r="631" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>2023</v>
       </c>
@@ -23514,7 +23513,7 @@
         <v>"ACA14" As "Decano(a)",</v>
       </c>
     </row>
-    <row r="632" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632">
         <v>2023</v>
       </c>
@@ -23544,7 +23543,7 @@
         <v>"ACA15" As "Director(a) de Programa o Coordinador",</v>
       </c>
     </row>
-    <row r="633" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A633">
         <v>2023</v>
       </c>
@@ -23574,7 +23573,7 @@
         <v>"ACA16" As "Sala Teams unidad academica",</v>
       </c>
     </row>
-    <row r="634" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A634">
         <v>2023</v>
       </c>
@@ -23604,7 +23603,7 @@
         <v>"ACA17" As "Atención presencial",</v>
       </c>
     </row>
-    <row r="635" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A635">
         <v>2023</v>
       </c>
@@ -23634,7 +23633,7 @@
         <v>"ACA18" As "En general, ¿qué tan satisfecho(a) te encuentras con la atención y el servicio brindado por parte de las *asistentes de tu facultad*?",</v>
       </c>
     </row>
-    <row r="636" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A636">
         <v>2023</v>
       </c>
@@ -23664,7 +23663,7 @@
         <v>"ACA19_2" As "Sala Teams",</v>
       </c>
     </row>
-    <row r="637" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A637">
         <v>2023</v>
       </c>
@@ -23694,7 +23693,7 @@
         <v>"ACA20" As "Atención presencial",</v>
       </c>
     </row>
-    <row r="638" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A638">
         <v>2023</v>
       </c>
@@ -23724,7 +23723,7 @@
         <v>"ACA21" As "Atención por correo electrónico",</v>
       </c>
     </row>
-    <row r="639" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639">
         <v>2023</v>
       </c>
@@ -23754,7 +23753,7 @@
         <v>"ACA22" As "Atención presencial",</v>
       </c>
     </row>
-    <row r="640" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A640">
         <v>2023</v>
       </c>
@@ -23784,7 +23783,7 @@
         <v>"ACA23" As "Atención por correo electrónico",</v>
       </c>
     </row>
-    <row r="641" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A641">
         <v>2023</v>
       </c>
@@ -23814,7 +23813,7 @@
         <v>"ACA24" As "Atención presencial",</v>
       </c>
     </row>
-    <row r="642" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A642">
         <v>2023</v>
       </c>
@@ -23844,7 +23843,7 @@
         <v>"ACA25" As "Disponibilidad y funcionamiento de los equipos",</v>
       </c>
     </row>
-    <row r="643" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A643">
         <v>2023</v>
       </c>
@@ -23874,7 +23873,7 @@
         <v>"ACA26" As "Disponibilidad de materiales y/o reactivos",</v>
       </c>
     </row>
-    <row r="644" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A644">
         <v>2023</v>
       </c>
@@ -23904,7 +23903,7 @@
         <v>"ACA27" As "Instalaciones",</v>
       </c>
     </row>
-    <row r="645" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A645">
         <v>2023</v>
       </c>
@@ -23934,7 +23933,7 @@
         <v>"ACA28" As "Higiene y limpieza las Instalaciones y Equipos",</v>
       </c>
     </row>
-    <row r="646" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A646">
         <v>2023</v>
       </c>
@@ -23964,7 +23963,7 @@
         <v>"ACA29" As "¿Qué tan probable es que recomiendes tu *programa académico* con familiares y amigos?",</v>
       </c>
     </row>
-    <row r="647" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A647">
         <v>2023</v>
       </c>
@@ -23994,7 +23993,7 @@
         <v>"ACA30" As "¿Qué tan probable es que en el futuro, vuelvas a estudiar un programa académico en la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="648" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A648">
         <v>2023</v>
       </c>
@@ -24024,7 +24023,7 @@
         <v>"IMP1" As "¿Conoces los servicios y beneficios que dispone *Ean Impacta* para todos sus estudiantes?",</v>
       </c>
     </row>
-    <row r="649" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A649">
         <v>2023</v>
       </c>
@@ -24054,7 +24053,7 @@
         <v>"IMP2" As "¿Qué tanto te ha influenciado la filosofía del emprendimiento sostenible de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="650" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A650">
         <v>2023</v>
       </c>
@@ -24084,7 +24083,7 @@
         <v>"IMP3" As "Calidad académica",</v>
       </c>
     </row>
-    <row r="651" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A651">
         <v>2023</v>
       </c>
@@ -24114,7 +24113,7 @@
         <v>"IMP4" As "Calidad docente",</v>
       </c>
     </row>
-    <row r="652" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A652">
         <v>2023</v>
       </c>
@@ -24144,7 +24143,7 @@
         <v>"IMP5" As "Diversidad e inclusión",</v>
       </c>
     </row>
-    <row r="653" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A653">
         <v>2023</v>
       </c>
@@ -24174,7 +24173,7 @@
         <v>"IMP6" As "Emprendimiento",</v>
       </c>
     </row>
-    <row r="654" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A654">
         <v>2023</v>
       </c>
@@ -24204,7 +24203,7 @@
         <v>"IMP7" As "Ética y valores",</v>
       </c>
     </row>
-    <row r="655" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A655">
         <v>2023</v>
       </c>
@@ -24234,7 +24233,7 @@
         <v>"IMP8" As "Innovación en la formación",</v>
       </c>
     </row>
-    <row r="656" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A656">
         <v>2023</v>
       </c>
@@ -24264,7 +24263,7 @@
         <v>"IMP9" As "Investigación",</v>
       </c>
     </row>
-    <row r="657" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A657">
         <v>2023</v>
       </c>
@@ -24294,7 +24293,7 @@
         <v>"IMP10" As "Sostenibilidad",</v>
       </c>
     </row>
-    <row r="658" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A658">
         <v>2023</v>
       </c>
@@ -24324,7 +24323,7 @@
         <v>"IMP11" As "Other",</v>
       </c>
     </row>
-    <row r="659" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A659">
         <v>2023</v>
       </c>
@@ -24354,7 +24353,7 @@
         <v>"IMP12" As "¿Qué tan satisfecho(a) te encuentras con la atención y el servicio recibido por parte del equipo de *Ean Impacta*?",</v>
       </c>
     </row>
-    <row r="660" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A660">
         <v>2023</v>
       </c>
@@ -24384,7 +24383,7 @@
         <v>"SOS1" As "¿Conoces los aportes y avances de la Universidad Ean en términos de sostenibilidad (dentro y fuera de la institución)?",</v>
       </c>
     </row>
-    <row r="661" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A661">
         <v>2023</v>
       </c>
@@ -24414,7 +24413,7 @@
         <v>"SOS2" As "¿En qué tipo de acciones te gustaría participar junto a Ean Sostenibilidad?",</v>
       </c>
     </row>
-    <row r="662" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A662">
         <v>2023</v>
       </c>
@@ -24444,7 +24443,7 @@
         <v>"SOS3" As "Other",</v>
       </c>
     </row>
-    <row r="663" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A663">
         <v>2023</v>
       </c>
@@ -24474,7 +24473,7 @@
         <v>"BIB1" As "Asesoría en referencias, normas APA y trabajos de grado",</v>
       </c>
     </row>
-    <row r="664" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A664">
         <v>2023</v>
       </c>
@@ -24504,7 +24503,7 @@
         <v>"BIB2" As "Búsqueda de información",</v>
       </c>
     </row>
-    <row r="665" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A665">
         <v>2023</v>
       </c>
@@ -24534,7 +24533,7 @@
         <v>"BIB3" As "Préstamo de libros",</v>
       </c>
     </row>
-    <row r="666" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A666">
         <v>2023</v>
       </c>
@@ -24564,7 +24563,7 @@
         <v>"BIB4" As "Tutoriales",</v>
       </c>
     </row>
-    <row r="667" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A667">
         <v>2023</v>
       </c>
@@ -24594,7 +24593,7 @@
         <v>"BIB5" As "Reserva de salas",</v>
       </c>
     </row>
-    <row r="668" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A668">
         <v>2023</v>
       </c>
@@ -24624,7 +24623,7 @@
         <v>"BIB6" As "Préstamo interbibliotecario",</v>
       </c>
     </row>
-    <row r="669" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A669">
         <v>2023</v>
       </c>
@@ -24654,7 +24653,7 @@
         <v>"BIB7" As "Pago de multas",</v>
       </c>
     </row>
-    <row r="670" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A670">
         <v>2023</v>
       </c>
@@ -24684,7 +24683,7 @@
         <v>"BIB8" As "¿Qué tan completas consideras las colecciones físicas y electrónicas en la *Biblioteca* de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="671" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671">
         <v>2023</v>
       </c>
@@ -24714,7 +24713,7 @@
         <v>"BIB9" As "¿Qué tan fácil ha sido el acceso a las colecciones electrónicas en la *biblioteca* de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="672" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A672">
         <v>2023</v>
       </c>
@@ -24744,7 +24743,7 @@
         <v>"BIB10" As "Sala Teams",</v>
       </c>
     </row>
-    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A673">
         <v>2023</v>
       </c>
@@ -24774,7 +24773,7 @@
         <v>"BIB11" As "Atención presencial",</v>
       </c>
     </row>
-    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A674">
         <v>2023</v>
       </c>
@@ -24804,7 +24803,7 @@
         <v>"BIB12" As "Whatsapp",</v>
       </c>
     </row>
-    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A675">
         <v>2023</v>
       </c>
@@ -24834,7 +24833,7 @@
         <v>"BIB13" As "En general, ¿qué tan satisfecho(a) te encuentras con los espacios físicos ofrecidos por la *Biblioteca*?",</v>
       </c>
     </row>
-    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A676">
         <v>2023</v>
       </c>
@@ -24864,7 +24863,7 @@
         <v>"INT1" As "Buddy Program",</v>
       </c>
     </row>
-    <row r="677" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A677">
         <v>2023</v>
       </c>
@@ -24894,7 +24893,7 @@
         <v>"INT2" As "Doble Titulación",</v>
       </c>
     </row>
-    <row r="678" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A678">
         <v>2023</v>
       </c>
@@ -24924,7 +24923,7 @@
         <v>"INT3" As "Escuela Internacional de Verano/Invierno",</v>
       </c>
     </row>
-    <row r="679" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A679">
         <v>2023</v>
       </c>
@@ -24954,7 +24953,7 @@
         <v>"INT4" As "Intercambios académicos presenciales",</v>
       </c>
     </row>
-    <row r="680" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A680">
         <v>2023</v>
       </c>
@@ -24984,7 +24983,7 @@
         <v>"INT5" As "Intercambio académicos virtuales",</v>
       </c>
     </row>
-    <row r="681" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A681">
         <v>2023</v>
       </c>
@@ -25014,7 +25013,7 @@
         <v>"INT6" As "Misiones académicas",</v>
       </c>
     </row>
-    <row r="682" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A682">
         <v>2023</v>
       </c>
@@ -25044,7 +25043,7 @@
         <v>"INT7" As "Semana Ean Internacional",</v>
       </c>
     </row>
-    <row r="683" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A683">
         <v>2023</v>
       </c>
@@ -25074,7 +25073,7 @@
         <v>"INT8" As "No conozco ninguno",</v>
       </c>
     </row>
-    <row r="684" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A684">
         <v>2023</v>
       </c>
@@ -25104,7 +25103,7 @@
         <v>"INT9" As "¿Has participado en alguno de los programas mencionados anteriormente?",</v>
       </c>
     </row>
-    <row r="685" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A685">
         <v>2023</v>
       </c>
@@ -25134,7 +25133,7 @@
         <v>"INT10" As "¿Cuáles son los principales obstáculos para que puedas participar?",</v>
       </c>
     </row>
-    <row r="686" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A686">
         <v>2023</v>
       </c>
@@ -25164,7 +25163,7 @@
         <v>"INT11" As "¿Conoces la oferta de convenios con universidades aliadas para hacer intercambios académicos?",</v>
       </c>
     </row>
-    <row r="687" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A687">
         <v>2023</v>
       </c>
@@ -25194,7 +25193,7 @@
         <v>"INT12" As "¿Qué tan relevante es para tu desarrollo académico y profesional participar en uno de los programas de movilidad y proyección global?",</v>
       </c>
     </row>
-    <row r="688" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A688">
         <v>2023</v>
       </c>
@@ -25224,7 +25223,7 @@
         <v>"INT13" As "Apiario Ean",</v>
       </c>
     </row>
-    <row r="689" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689">
         <v>2023</v>
       </c>
@@ -25254,7 +25253,7 @@
         <v>"INT14" As "Ean Investigaciones",</v>
       </c>
     </row>
-    <row r="690" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A690">
         <v>2023</v>
       </c>
@@ -25284,7 +25283,7 @@
         <v>"INT15" As "Ean Siempre Contigo",</v>
       </c>
     </row>
-    <row r="691" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691">
         <v>2023</v>
       </c>
@@ -25314,7 +25313,7 @@
         <v>"INT16" As "Ean Social",</v>
       </c>
     </row>
-    <row r="692" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A692">
         <v>2023</v>
       </c>
@@ -25344,7 +25343,7 @@
         <v>"INT17" As "Fondo Diversidades",</v>
       </c>
     </row>
-    <row r="693" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A693">
         <v>2023</v>
       </c>
@@ -25374,7 +25373,7 @@
         <v>"INT18" As "Ningunas de las anteriores",</v>
       </c>
     </row>
-    <row r="694" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A694">
         <v>2023</v>
       </c>
@@ -25404,7 +25403,7 @@
         <v>"INT19" As "Atención por correo electrónico",</v>
       </c>
     </row>
-    <row r="695" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695">
         <v>2023</v>
       </c>
@@ -25434,7 +25433,7 @@
         <v>"INT20" As "Atención presencial",</v>
       </c>
     </row>
-    <row r="696" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A696">
         <v>2023</v>
       </c>
@@ -25464,7 +25463,7 @@
         <v>"PRA1" As "¿Conoces los servicios de la oficina de *Prácticas Profesionales*?",</v>
       </c>
     </row>
-    <row r="697" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697">
         <v>2023</v>
       </c>
@@ -25494,7 +25493,7 @@
         <v>"PRA2" As "Atención por correo electrónico",</v>
       </c>
     </row>
-    <row r="698" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A698">
         <v>2023</v>
       </c>
@@ -25524,7 +25523,7 @@
         <v>"PRA3" As "Atención presencial",</v>
       </c>
     </row>
-    <row r="699" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A699">
         <v>2023</v>
       </c>
@@ -25554,7 +25553,7 @@
         <v>"PRA4" As "Déjanos saber qué te gustaría que mejorara en el área de *Prácticas Profesionales*.",</v>
       </c>
     </row>
-    <row r="700" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A700">
         <v>2023</v>
       </c>
@@ -25584,7 +25583,7 @@
         <v>"PLA1" As "Plataforma de correo electrónico",</v>
       </c>
     </row>
-    <row r="701" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A701">
         <v>2023</v>
       </c>
@@ -25614,7 +25613,7 @@
         <v>"PLA2" As "Aplicaciones de Office",</v>
       </c>
     </row>
-    <row r="702" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A702">
         <v>2023</v>
       </c>
@@ -25644,7 +25643,7 @@
         <v>"PLA3" As "Plataforma Teams",</v>
       </c>
     </row>
-    <row r="703" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A703">
         <v>2023</v>
       </c>
@@ -25674,7 +25673,7 @@
         <v>"PLA4" As "Plataforma Cisco Webex",</v>
       </c>
     </row>
-    <row r="704" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704">
         <v>2023</v>
       </c>
@@ -25704,7 +25703,7 @@
         <v>"PLA5" As "Plataforma Canvas",</v>
       </c>
     </row>
-    <row r="705" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705">
         <v>2023</v>
       </c>
@@ -25734,7 +25733,7 @@
         <v>"PLA6" As "App Ean",</v>
       </c>
     </row>
-    <row r="706" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A706">
         <v>2023</v>
       </c>
@@ -25764,7 +25763,7 @@
         <v>"PLA7" As "Mesa de servicios",</v>
       </c>
     </row>
-    <row r="707" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A707">
         <v>2023</v>
       </c>
@@ -25794,7 +25793,7 @@
         <v>"PLA8" As "Plataforma de pagos",</v>
       </c>
     </row>
-    <row r="708" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A708">
         <v>2023</v>
       </c>
@@ -25824,7 +25823,7 @@
         <v>"PLA9" As "Velocidad de conexión WiFi",</v>
       </c>
     </row>
-    <row r="709" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A709">
         <v>2023</v>
       </c>
@@ -25854,7 +25853,7 @@
         <v>"PLA10" As "Estabilidad de conexión WiFi",</v>
       </c>
     </row>
-    <row r="710" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A710">
         <v>2023</v>
       </c>
@@ -25884,7 +25883,7 @@
         <v>"PLA11" As "Cobertura de red WiFi",</v>
       </c>
     </row>
-    <row r="711" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A711">
         <v>2023</v>
       </c>
@@ -25914,7 +25913,7 @@
         <v>"PLA12" As "Dispositivo de reconocimiento facial al ingreso",</v>
       </c>
     </row>
-    <row r="712" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A712">
         <v>2023</v>
       </c>
@@ -25944,7 +25943,7 @@
         <v>"PLA13" As "Estado de los equipos de las salas de cómputo",</v>
       </c>
     </row>
-    <row r="713" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A713">
         <v>2023</v>
       </c>
@@ -25974,7 +25973,7 @@
         <v>"PLA14" As "Disponibilidad de los equipos de las salas de cómputo",</v>
       </c>
     </row>
-    <row r="714" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A714">
         <v>2023</v>
       </c>
@@ -26004,7 +26003,7 @@
         <v>"PLA15" As "Sala Teams",</v>
       </c>
     </row>
-    <row r="715" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A715">
         <v>2023</v>
       </c>
@@ -26034,7 +26033,7 @@
         <v>"PLA16" As "Atención presencial",</v>
       </c>
     </row>
-    <row r="716" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A716">
         <v>2023</v>
       </c>
@@ -26064,7 +26063,7 @@
         <v>"REG1" As "Emisión de certificados académicos",</v>
       </c>
     </row>
-    <row r="717" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A717">
         <v>2023</v>
       </c>
@@ -26094,7 +26093,7 @@
         <v>"REG2" As "Retiro de unidades de estudio",</v>
       </c>
     </row>
-    <row r="718" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A718">
         <v>2023</v>
       </c>
@@ -26124,7 +26123,7 @@
         <v>"REG3" As "Abonos",</v>
       </c>
     </row>
-    <row r="719" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A719">
         <v>2023</v>
       </c>
@@ -26154,7 +26153,7 @@
         <v>"REG4" As "Gestión relacionada con cursos libres",</v>
       </c>
     </row>
-    <row r="720" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A720">
         <v>2023</v>
       </c>
@@ -26184,7 +26183,7 @@
         <v>"REG5" As "Gestión relacionada con validaciones",</v>
       </c>
     </row>
-    <row r="721" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A721">
         <v>2023</v>
       </c>
@@ -26214,7 +26213,7 @@
         <v>"REG6" As "Distinciones e incentivos",</v>
       </c>
     </row>
-    <row r="722" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A722">
         <v>2023</v>
       </c>
@@ -26244,7 +26243,7 @@
         <v>"REG7" As "Presentación Examen Saber Pro",</v>
       </c>
     </row>
-    <row r="723" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A723">
         <v>2023</v>
       </c>
@@ -26274,7 +26273,7 @@
         <v>"REG8" As "Actualización de datos y proceso grado",</v>
       </c>
     </row>
-    <row r="724" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A724">
         <v>2023</v>
       </c>
@@ -26304,7 +26303,7 @@
         <v>"REG9" As "Sala Teams",</v>
       </c>
     </row>
-    <row r="725" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A725">
         <v>2023</v>
       </c>
@@ -26334,7 +26333,7 @@
         <v>"REG10" As "Atención presencial",</v>
       </c>
     </row>
-    <row r="726" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A726">
         <v>2023</v>
       </c>
@@ -26364,7 +26363,7 @@
         <v>"FIN1" As "¿Conoces los *convenios y opciones dispuestos* por la universidad para la financiación de matrícula?",</v>
       </c>
     </row>
-    <row r="727" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A727">
         <v>2023</v>
       </c>
@@ -26394,7 +26393,7 @@
         <v>"FIN02" As "Banco Av Villas",</v>
       </c>
     </row>
-    <row r="728" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A728">
         <v>2023</v>
       </c>
@@ -26424,7 +26423,7 @@
         <v>"FIN3" As "Ean Fraccionamiento",</v>
       </c>
     </row>
-    <row r="729" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A729">
         <v>2023</v>
       </c>
@@ -26454,7 +26453,7 @@
         <v>"FIN4" As "Ean Respalda",</v>
       </c>
     </row>
-    <row r="730" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A730">
         <v>2023</v>
       </c>
@@ -26484,7 +26483,7 @@
         <v>"FIN5" As "Financiar",</v>
       </c>
     </row>
-    <row r="731" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A731">
         <v>2023</v>
       </c>
@@ -26514,7 +26513,7 @@
         <v>"FIN6" As "Fincomercio – Fincoeducar",</v>
       </c>
     </row>
-    <row r="732" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A732">
         <v>2023</v>
       </c>
@@ -26544,7 +26543,7 @@
         <v>"FIN7" As "FLEVO Financiación",</v>
       </c>
     </row>
-    <row r="733" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A733">
         <v>2023</v>
       </c>
@@ -26574,7 +26573,7 @@
         <v>"FIN8" As "Icetex",</v>
       </c>
     </row>
-    <row r="734" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A734">
         <v>2023</v>
       </c>
@@ -26604,7 +26603,7 @@
         <v>"FIN9" As "Lumni Respalda",</v>
       </c>
     </row>
-    <row r="735" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A735">
         <v>2023</v>
       </c>
@@ -26634,7 +26633,7 @@
         <v>"FIN10" As "Sufi Bancolombia",</v>
       </c>
     </row>
-    <row r="736" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A736">
         <v>2023</v>
       </c>
@@ -26664,7 +26663,7 @@
         <v>"FIN11" As "No he utilizado ninguna",</v>
       </c>
     </row>
-    <row r="737" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A737">
         <v>2023</v>
       </c>
@@ -26694,7 +26693,7 @@
         <v>"FIN12" As "¿Qué tan satisfecho(a) te encuentras con los procedimientos y tiempos de respuesta para aplicación de descuentos?",</v>
       </c>
     </row>
-    <row r="738" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A738">
         <v>2023</v>
       </c>
@@ -26724,7 +26723,7 @@
         <v>"FIN13" As "¿Qué tan satisfecho te encuentras con los canales dispuestos para el pago de matrícula y otros servicios financieros?",</v>
       </c>
     </row>
-    <row r="739" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A739">
         <v>2023</v>
       </c>
@@ -26754,7 +26753,7 @@
         <v>"FIN14" As "Sala Teams",</v>
       </c>
     </row>
-    <row r="740" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A740">
         <v>2023</v>
       </c>
@@ -26784,7 +26783,7 @@
         <v>"FIN15" As "Atención presencial",</v>
       </c>
     </row>
-    <row r="741" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A741">
         <v>2023</v>
       </c>
@@ -26814,7 +26813,7 @@
         <v>"COM1" As "¿Qué tan satisfecho(a) te encuentras con la *atención telefónica* cuando llamas al *PBX* de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="742" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A742">
         <v>2023</v>
       </c>
@@ -26844,7 +26843,7 @@
         <v>"COM2" As "Facebook",</v>
       </c>
     </row>
-    <row r="743" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A743">
         <v>2023</v>
       </c>
@@ -26874,7 +26873,7 @@
         <v>"COM3" As "Instagram",</v>
       </c>
     </row>
-    <row r="744" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A744">
         <v>2023</v>
       </c>
@@ -26904,7 +26903,7 @@
         <v>"COM4" As "LinKedIn",</v>
       </c>
     </row>
-    <row r="745" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A745">
         <v>2023</v>
       </c>
@@ -26934,7 +26933,7 @@
         <v>"COM5" As "Threads",</v>
       </c>
     </row>
-    <row r="746" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A746">
         <v>2023</v>
       </c>
@@ -26964,7 +26963,7 @@
         <v>"COM6" As "TikTok",</v>
       </c>
     </row>
-    <row r="747" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A747">
         <v>2023</v>
       </c>
@@ -26994,7 +26993,7 @@
         <v>"COM7" As "Twitter",</v>
       </c>
     </row>
-    <row r="748" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A748">
         <v>2023</v>
       </c>
@@ -27024,7 +27023,7 @@
         <v>"COM8" As "Todas los anteriores",</v>
       </c>
     </row>
-    <row r="749" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A749">
         <v>2023</v>
       </c>
@@ -27054,7 +27053,7 @@
         <v>"COM9" As "Ninguna",</v>
       </c>
     </row>
-    <row r="750" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A750">
         <v>2023</v>
       </c>
@@ -27084,7 +27083,7 @@
         <v>"COM10" As "¿Utilizas la *App* de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="751" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A751">
         <v>2023</v>
       </c>
@@ -27114,7 +27113,7 @@
         <v>"COM11" As "¿Has interactuado con el *Chat Bot E- Ann* en la página web de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="752" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A752">
         <v>2023</v>
       </c>
@@ -27144,7 +27143,7 @@
         <v>"COM12" As "¿Qué tan satisfecho(a) te encuentras con la información que encuentras en el *Chat Bot E- Ann*?",</v>
       </c>
     </row>
-    <row r="753" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A753">
         <v>2023</v>
       </c>
@@ -27174,7 +27173,7 @@
         <v>"COM13" As "¿Qué tan satisfecho(a) te encuentras con la información que recibes a través del correo electrónico de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="754" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A754">
         <v>2023</v>
       </c>
@@ -27204,7 +27203,7 @@
         <v>"COM14" As "¿Con qué *frecuencia* te gustaría recibir correos electrónicos de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="755" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A755">
         <v>2023</v>
       </c>
@@ -27234,7 +27233,7 @@
         <v>"COM15" As ""¿Cuáles de los siguientes canales consideras que es el más efectivo para resolver tus inquietudes o requerimientos? Ordénalos según tu preferencia."",</v>
       </c>
     </row>
-    <row r="756" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A756">
         <v>2023</v>
       </c>
@@ -27264,7 +27263,7 @@
         <v>"PLF1" As "Accesibilidad",</v>
       </c>
     </row>
-    <row r="757" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A757">
         <v>2023</v>
       </c>
@@ -27294,7 +27293,7 @@
         <v>"PLF2" As "Capacidad",</v>
       </c>
     </row>
-    <row r="758" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A758">
         <v>2023</v>
       </c>
@@ -27324,7 +27323,7 @@
         <v>"PLF3" As "Ventilación",</v>
       </c>
     </row>
-    <row r="759" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A759">
         <v>2023</v>
       </c>
@@ -27354,7 +27353,7 @@
         <v>"PLF4" As "Condiciones de Seguridad",</v>
       </c>
     </row>
-    <row r="760" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A760">
         <v>2023</v>
       </c>
@@ -27384,7 +27383,7 @@
         <v>"PLF5_2" As "Aseo",</v>
       </c>
     </row>
-    <row r="761" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A761">
         <v>2023</v>
       </c>
@@ -27414,7 +27413,7 @@
         <v>"PLF6" As "Disponibilidad",</v>
       </c>
     </row>
-    <row r="762" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A762">
         <v>2023</v>
       </c>
@@ -27444,7 +27443,7 @@
         <v>"PLF7" As "Equipos audiovisuales",</v>
       </c>
     </row>
-    <row r="763" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A763">
         <v>2023</v>
       </c>
@@ -27474,7 +27473,7 @@
         <v>"PLF8" As "¿Qué tan satisfecho(a) te encuentras con los espacios dispuestos para la zona de alimentación en la Universidad?",</v>
       </c>
     </row>
-    <row r="764" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A764">
         <v>2023</v>
       </c>
@@ -27504,7 +27503,7 @@
         <v>"PLF9" As "Cafetería DoEat (ubicada en piso 6 - Ean Legacy)",</v>
       </c>
     </row>
-    <row r="765" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A765">
         <v>2023</v>
       </c>
@@ -27534,7 +27533,7 @@
         <v>"PLF10" As "Frutiice (ubicada en 4 piso de Legacy y Fundadores)",</v>
       </c>
     </row>
-    <row r="766" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A766">
         <v>2023</v>
       </c>
@@ -27564,7 +27563,7 @@
         <v>"PLF11" As "La regional (ubicada en piso 1 - Ean Legacy)",</v>
       </c>
     </row>
-    <row r="767" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A767">
         <v>2023</v>
       </c>
@@ -27594,7 +27593,7 @@
         <v>"PLF12" As "Frutiice",</v>
       </c>
     </row>
-    <row r="768" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A768">
         <v>2023</v>
       </c>
@@ -27624,7 +27623,7 @@
         <v>"PLF13" As "DoEat",</v>
       </c>
     </row>
-    <row r="769" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A769">
         <v>2023</v>
       </c>
@@ -27654,7 +27653,7 @@
         <v>"PLF14" As "La Regional",</v>
       </c>
     </row>
-    <row r="770" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A770">
         <v>2023</v>
       </c>
@@ -27684,7 +27683,7 @@
         <v>"PLF15" As "Seguridad",</v>
       </c>
     </row>
-    <row r="771" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A771">
         <v>2023</v>
       </c>
@@ -27714,7 +27713,7 @@
         <v>"PLF5" As "Aseo",</v>
       </c>
     </row>
-    <row r="772" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A772">
         <v>2023</v>
       </c>
@@ -27744,7 +27743,7 @@
         <v>"PLF17" As "Parqueadero “City Parking”",</v>
       </c>
     </row>
-    <row r="773" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A773">
         <v>2023</v>
       </c>
@@ -27774,7 +27773,7 @@
         <v>"FIN2" As "Banco Av Villas",</v>
       </c>
     </row>
-    <row r="774" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A774">
         <v>2023</v>
       </c>
@@ -27804,7 +27803,7 @@
         <v>"PLF19" As "Servicios de impresión",</v>
       </c>
     </row>
-    <row r="775" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A775">
         <v>2023</v>
       </c>
@@ -27834,7 +27833,7 @@
         <v>"EXP1" As "App Bienestar Ean",</v>
       </c>
     </row>
-    <row r="776" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A776">
         <v>2023</v>
       </c>
@@ -27864,7 +27863,7 @@
         <v>"EXP2" As "Gimnasio fitness (planes de entrenamiento, nutrición y medicina deportiva).",</v>
       </c>
     </row>
-    <row r="777" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A777">
         <v>2023</v>
       </c>
@@ -27894,7 +27893,7 @@
         <v>"EXP3" As "Clases y grupos culturales (teatro, danzas, instrumentos, canto, grupos musicales).",</v>
       </c>
     </row>
-    <row r="778" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A778">
         <v>2023</v>
       </c>
@@ -27924,7 +27923,7 @@
         <v>"EXP4" As "Clases y grupos deportivos (futbol, voley, baloncesto)",</v>
       </c>
     </row>
-    <row r="779" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A779">
         <v>2023</v>
       </c>
@@ -27954,7 +27953,7 @@
         <v>"EXP5" As "Orquesta filarmónica",</v>
       </c>
     </row>
-    <row r="780" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A780">
         <v>2023</v>
       </c>
@@ -27984,7 +27983,7 @@
         <v>"EXP6" As "Actividad física (GAP, Zumba, Grit)",</v>
       </c>
     </row>
-    <row r="781" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A781">
         <v>2023</v>
       </c>
@@ -28014,7 +28013,7 @@
         <v>"EXP7" As "Clases y talleres de habilidades humanas (inteligencia emocional, mindfulness, fotografía).",</v>
       </c>
     </row>
-    <row r="782" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A782">
         <v>2023</v>
       </c>
@@ -28044,7 +28043,7 @@
         <v>"EXP8" As "Servicio de salud (Consulta medicina general, enfermería, planificación familiar).",</v>
       </c>
     </row>
-    <row r="783" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A783">
         <v>2023</v>
       </c>
@@ -28074,7 +28073,7 @@
         <v>"EXP9" As "Servicio de acompañamiento psicológico.",</v>
       </c>
     </row>
-    <row r="784" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A784">
         <v>2023</v>
       </c>
@@ -28104,7 +28103,7 @@
         <v>"EXP10" As "Póliza de accidentes personales",</v>
       </c>
     </row>
-    <row r="785" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A785">
         <v>2023</v>
       </c>
@@ -28134,7 +28133,7 @@
         <v>"EXP11" As "Salón de juegos.",</v>
       </c>
     </row>
-    <row r="786" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A786">
         <v>2023</v>
       </c>
@@ -28164,7 +28163,7 @@
         <v>"EXP12" As "Préstamo de elementos de juegos o instrumentos musicales.",</v>
       </c>
     </row>
-    <row r="787" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A787">
         <v>2023</v>
       </c>
@@ -28194,7 +28193,7 @@
         <v>"EXP13" As "Programa pedaleando (alquiler de bicicletas)",</v>
       </c>
     </row>
-    <row r="788" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A788">
         <v>2023</v>
       </c>
@@ -28224,7 +28223,7 @@
         <v>"EXP14" As "Voluntariado Ean",</v>
       </c>
     </row>
-    <row r="789" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A789">
         <v>2023</v>
       </c>
@@ -28254,7 +28253,7 @@
         <v>"EXP15" As "Programa vendedor emprendedor",</v>
       </c>
     </row>
-    <row r="790" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A790">
         <v>2023</v>
       </c>
@@ -28284,7 +28283,7 @@
         <v>"EXP16" As "Polideportivo Ean Arena",</v>
       </c>
     </row>
-    <row r="791" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A791">
         <v>2023</v>
       </c>
@@ -28314,7 +28313,7 @@
         <v>"EXP17" As "Gimnasio fitness Ean.",</v>
       </c>
     </row>
-    <row r="792" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A792">
         <v>2023</v>
       </c>
@@ -28344,7 +28343,7 @@
         <v>"EXP18" As "Zona de tenis de mesa piso 4 Legacy",</v>
       </c>
     </row>
-    <row r="793" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A793">
         <v>2023</v>
       </c>
@@ -28374,7 +28373,7 @@
         <v>"EXP19" As "Ball pit Piso 1 Edificio fundadores",</v>
       </c>
     </row>
-    <row r="794" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A794">
         <v>2023</v>
       </c>
@@ -28404,7 +28403,7 @@
         <v>"EXP20" As "Sala Neutro Piso 1 Legacy",</v>
       </c>
     </row>
-    <row r="795" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A795">
         <v>2023</v>
       </c>
@@ -28434,7 +28433,7 @@
         <v>"EXP21" As "Salones de Expresiones piso 4 Legacy",</v>
       </c>
     </row>
-    <row r="796" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A796">
         <v>2023</v>
       </c>
@@ -28464,7 +28463,7 @@
         <v>"EXP22" As "Salones de música piso 4 edificio Fundadores.",</v>
       </c>
     </row>
-    <row r="797" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A797">
         <v>2023</v>
       </c>
@@ -28494,7 +28493,7 @@
         <v>"EXP23" As "Canchas futbol y tenis de campo en Club El Carmel",</v>
       </c>
     </row>
-    <row r="798" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A798">
         <v>2023</v>
       </c>
@@ -28524,7 +28523,7 @@
         <v>"EXP24" As "Sala de lactancia",</v>
       </c>
     </row>
-    <row r="799" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A799">
         <v>2023</v>
       </c>
@@ -28554,7 +28553,7 @@
         <v>"EXP25" As "En general, ¿qué tan satisfecho(a) te encuentras con la atención y el servicio ofrecido por el equipo de *Bienestar Universitario*?",</v>
       </c>
     </row>
-    <row r="800" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A800">
         <v>2023</v>
       </c>
@@ -28584,7 +28583,7 @@
         <v>"EXP26_2" As "Acompañamiento en el proceso de renovación de matrícula",</v>
       </c>
     </row>
-    <row r="801" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A801">
         <v>2023</v>
       </c>
@@ -28614,7 +28613,7 @@
         <v>"EXP27" As "Programa Ean Contigo.",</v>
       </c>
     </row>
-    <row r="802" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A802">
         <v>2023</v>
       </c>
@@ -28644,7 +28643,7 @@
         <v>"EXP28_2" As "Mentores Académicos",</v>
       </c>
     </row>
-    <row r="803" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A803">
         <v>2023</v>
       </c>
@@ -28674,7 +28673,7 @@
         <v>"EXP29_2" As "Orientación Psicopedagógica",</v>
       </c>
     </row>
-    <row r="804" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A804">
         <v>2023</v>
       </c>
@@ -28704,7 +28703,7 @@
         <v>"EXP30" As "Acompañamiento y asesoría para solicitar cursos de refuerzo y/o tutorías",</v>
       </c>
     </row>
-    <row r="805" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A805">
         <v>2023</v>
       </c>
@@ -28734,7 +28733,7 @@
         <v>"EXP26" As "Acompañamiento en el proceso de renovación de matrícula",</v>
       </c>
     </row>
-    <row r="806" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A806">
         <v>2023</v>
       </c>
@@ -28764,7 +28763,7 @@
         <v>"EXP32" As "Programa Ean Contigo",</v>
       </c>
     </row>
-    <row r="807" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A807">
         <v>2023</v>
       </c>
@@ -28794,7 +28793,7 @@
         <v>"EXP28" As "Mentores Académicos",</v>
       </c>
     </row>
-    <row r="808" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A808">
         <v>2023</v>
       </c>
@@ -28824,7 +28823,7 @@
         <v>"EXP29" As "Orientación Psicopedagógica",</v>
       </c>
     </row>
-    <row r="809" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A809">
         <v>2023</v>
       </c>
@@ -28854,7 +28853,7 @@
         <v>"EXP35" As "Apoyos académicos para tu proceso académico",</v>
       </c>
     </row>
-    <row r="810" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A810">
         <v>2023</v>
       </c>
@@ -28884,7 +28883,7 @@
         <v>"EXP36" As "¿Has interactuado o requerido los servicios de la *Defensoría Universitaria*?",</v>
       </c>
     </row>
-    <row r="811" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A811">
         <v>2023</v>
       </c>
@@ -28914,7 +28913,7 @@
         <v>"EXP37" As "¿Qué tan satisfecho(a) te encuentras con la atención y el servicio brindada por la *Defensoría Universitaria*?",</v>
       </c>
     </row>
-    <row r="812" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A812">
         <v>2023</v>
       </c>
@@ -28944,7 +28943,7 @@
         <v>"EXP38" As "Orientación sobre asuntos y normativa institucional",</v>
       </c>
     </row>
-    <row r="813" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A813">
         <v>2023</v>
       </c>
@@ -28974,7 +28973,7 @@
         <v>"EXP39" As "Mediación en asuntos académicos",</v>
       </c>
     </row>
-    <row r="814" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A814">
         <v>2023</v>
       </c>
@@ -29004,7 +29003,7 @@
         <v>"EXP40" As "Intervención en asuntos administrativos",</v>
       </c>
     </row>
-    <row r="815" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A815">
         <v>2023</v>
       </c>
@@ -29034,7 +29033,7 @@
         <v>"EXP41" As "Respuesta a solicitudes /peticiones",</v>
       </c>
     </row>
-    <row r="816" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A816">
         <v>2023</v>
       </c>
@@ -29064,7 +29063,7 @@
         <v>"EXP42" As "Atención presencial en EAN A TU LADO Piso 2 Legacy",</v>
       </c>
     </row>
-    <row r="817" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A817">
         <v>2023</v>
       </c>
@@ -29094,7 +29093,7 @@
         <v>"EXP43" As "Mesa de servicio",</v>
       </c>
     </row>
-    <row r="818" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A818">
         <v>2023</v>
       </c>
@@ -29124,7 +29123,7 @@
         <v>"EXP44" As "Canal PQRS",</v>
       </c>
     </row>
-    <row r="819" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A819">
         <v>2023</v>
       </c>
@@ -29154,7 +29153,7 @@
         <v>"ACA19" As "Sala Teams",</v>
       </c>
     </row>
-    <row r="820" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A820">
         <v>2023</v>
       </c>
@@ -29184,7 +29183,7 @@
         <v>"EXP46" As "¿Qué tan satisfecho(a) te encuentras con el servicio y atención que te brinda el *equipo de recepción* de la universidad?",</v>
       </c>
     </row>
-    <row r="821" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A821">
         <v>2023</v>
       </c>
@@ -29214,7 +29213,7 @@
         <v>"EVC1" As "Tienda Ean",</v>
       </c>
     </row>
-    <row r="822" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A822">
         <v>2023</v>
       </c>
@@ -29244,7 +29243,7 @@
         <v>"EVC2" As "Galería de arte",</v>
       </c>
     </row>
-    <row r="823" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A823">
         <v>2023</v>
       </c>
@@ -29274,7 +29273,7 @@
         <v>"EVC3" As "Eventos externos",</v>
       </c>
     </row>
-    <row r="824" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A824">
         <v>2023</v>
       </c>
@@ -29304,7 +29303,7 @@
         <v>"EVC4" As "Eventos internos",</v>
       </c>
     </row>
-    <row r="825" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A825">
         <v>2023</v>
       </c>
@@ -29334,7 +29333,7 @@
         <v>"EVC5" As "¿Has tenido alguna experiencia utilizando nuestros servicios de eventos, producción audiovisual o productos, como transmisiones en vivo, fotografías, videos para redes sociales o productos de la tienda de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="826" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A826">
         <v>2023</v>
       </c>
@@ -29364,7 +29363,7 @@
         <v>"EVC6" As "En tu opinión, ¿qué mejoras crees que podríamos hacer para que nuestros servicios de producción audiovisual sean aún más beneficiosos para la comunidad universitaria? ¿Hay algún tipo de contenido o producto específico que te gustaría ver en el futuro?",</v>
       </c>
     </row>
-    <row r="827" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A827">
         <v>2023</v>
       </c>
@@ -29394,7 +29393,7 @@
         <v>"FAB1" As "¿Conoces los servicios que presta el *FabLab*?",</v>
       </c>
     </row>
-    <row r="828" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A828">
         <v>2023</v>
       </c>
@@ -29424,7 +29423,7 @@
         <v>"EMP1" As "Bolsa de empleo Universia",</v>
       </c>
     </row>
-    <row r="829" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A829">
         <v>2023</v>
       </c>
@@ -29454,7 +29453,7 @@
         <v>"EMP2" As "Entrenamientos de desarrollo de habilidades para la vida profesional",</v>
       </c>
     </row>
-    <row r="830" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A830">
         <v>2023</v>
       </c>
@@ -29484,7 +29483,7 @@
         <v>"EMP3" As "Orientación vocacional",</v>
       </c>
     </row>
-    <row r="831" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A831">
         <v>2023</v>
       </c>
@@ -29514,7 +29513,7 @@
         <v>"EMP4" As "Ferias de oportunidades laborales",</v>
       </c>
     </row>
-    <row r="832" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A832">
         <v>2023</v>
       </c>
@@ -29544,7 +29543,7 @@
         <v>"EMP5" As "Prueba ESIC",</v>
       </c>
     </row>
-    <row r="833" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A833">
         <v>2023</v>
       </c>
@@ -29574,7 +29573,7 @@
         <v>"INSTI1" As "¿Qué tan satisfecho(a) te sientes con el carácter incluyente y diverso de la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="834" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A834">
         <v>2023</v>
       </c>
@@ -29604,7 +29603,7 @@
         <v>"INSTI2" As ""¿Quieres destacar algo positivo de la Universidad Ean? ¿Tienes alguna sugerencia en la que podríamos mejorar?"",</v>
       </c>
     </row>
-    <row r="835" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A835">
         <v>2023</v>
       </c>
@@ -29634,7 +29633,7 @@
         <v>"INSTI3" As "En una escala de 0 a 10 ¿Qué tan probable es que recomiendes los servicios y la atención que te brindamos en la Universidad Ean?",</v>
       </c>
     </row>
-    <row r="836" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A836">
         <v>2023</v>
       </c>
@@ -29664,7 +29663,7 @@
         <v>"Start Date (UTC)" As "Start Date (UTC)",</v>
       </c>
     </row>
-    <row r="837" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A837">
         <v>2023</v>
       </c>
@@ -29694,7 +29693,7 @@
         <v>"Submit Date (UTC)" As "Submit Date (UTC)",</v>
       </c>
     </row>
-    <row r="838" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A838">
         <v>2023</v>
       </c>
@@ -29724,7 +29723,7 @@
         <v>"Network ID" As "Network ID",</v>
       </c>
     </row>
-    <row r="839" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A839">
         <v>2023</v>
       </c>
@@ -29754,7 +29753,7 @@
         <v>"Tags" As "Tags",</v>
       </c>
     </row>
-    <row r="840" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A840">
         <v>2024</v>
       </c>
@@ -29784,7 +29783,7 @@
         <v>"Año" As "Año",</v>
       </c>
     </row>
-    <row r="841" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A841">
         <v>2024</v>
       </c>
@@ -29814,7 +29813,7 @@
         <v>"Para iniciar, por favor, indícanos el número de tu documento de identidad:" As "Para iniciar, por favor, indícanos el número de tu documento de identidad:",</v>
       </c>
     </row>
-    <row r="842" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A842">
         <v>2024</v>
       </c>
@@ -29844,7 +29843,7 @@
         <v>"Modalidad" As "Modalidad",</v>
       </c>
     </row>
-    <row r="843" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A843">
         <v>2024</v>
       </c>
@@ -29874,7 +29873,7 @@
         <v>"Facultad" As "Facultad",</v>
       </c>
     </row>
-    <row r="844" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A844">
         <v>2024</v>
       </c>
@@ -29904,7 +29903,7 @@
         <v>"Tipo de Formación " As "Tipo de Formación ",</v>
       </c>
     </row>
-    <row r="845" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A845">
         <v>2024</v>
       </c>
@@ -29934,7 +29933,7 @@
         <v>"Programa" As "Programa",</v>
       </c>
     </row>
-    <row r="846" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A846">
         <v>2024</v>
       </c>
@@ -29964,7 +29963,7 @@
         <v>"ACA1" As "Plan de estudios de tu programa",</v>
       </c>
     </row>
-    <row r="847" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A847">
         <v>2024</v>
       </c>
@@ -29994,7 +29993,7 @@
         <v>"ACA2" As "Pertinencia de los conocimientos adquiridos en las clases",</v>
       </c>
     </row>
-    <row r="848" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A848">
         <v>2024</v>
       </c>
@@ -30024,7 +30023,7 @@
         <v>"ACA3" As "Contribución del programa en tu proceso formativo",</v>
       </c>
     </row>
-    <row r="849" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A849">
         <v>2024</v>
       </c>
@@ -30054,7 +30053,7 @@
         <v>"ACA4" As "¿Qué tan cumplida ha sido la Universidad Ean respecto a la promesa de valor académica ofrecida por el programa que cursas actualmente?",</v>
       </c>
     </row>
-    <row r="850" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A850">
         <v>2024</v>
       </c>
@@ -30084,7 +30083,7 @@
         <v>"ACA5" As "Conforme al avance de tu programa académico:",</v>
       </c>
     </row>
-    <row r="851" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A851">
         <v>2024</v>
       </c>
@@ -30114,7 +30113,7 @@
         <v>"ACA6" As "Conocimiento disciplinar",</v>
       </c>
     </row>
-    <row r="852" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A852">
         <v>2024</v>
       </c>
@@ -30144,7 +30143,7 @@
         <v>"ACA7" As "Competencias para la enseñanza y la formación",</v>
       </c>
     </row>
-    <row r="853" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A853">
         <v>2024</v>
       </c>
@@ -30174,7 +30173,7 @@
         <v>"ACA8" As "Cumplimiento del syllabus y plan de estudios del programa",</v>
       </c>
     </row>
-    <row r="854" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A854">
         <v>2024</v>
       </c>
@@ -30204,7 +30203,7 @@
         <v>"ACA9" As "Evaluación y acompañamiento del proceso de aprendizaje",</v>
       </c>
     </row>
-    <row r="855" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A855">
         <v>2024</v>
       </c>
@@ -30234,7 +30233,7 @@
         <v>"ACA10" As "Entrega de calificaciones y retroalimentación",</v>
       </c>
     </row>
-    <row r="856" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A856">
         <v>2024</v>
       </c>
@@ -30264,7 +30263,7 @@
         <v>"ACA11" As "Calidad humana",</v>
       </c>
     </row>
-    <row r="857" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A857">
         <v>2024</v>
       </c>
@@ -30294,7 +30293,7 @@
         <v>"ACA12" As "Compromiso",</v>
       </c>
     </row>
-    <row r="858" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A858">
         <v>2024</v>
       </c>
@@ -30324,7 +30323,7 @@
         <v>"ACA13" As "Manejo tecnológico",</v>
       </c>
     </row>
-    <row r="859" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A859">
         <v>2024</v>
       </c>
@@ -30354,7 +30353,7 @@
         <v>"ACA14" As "Decano(a)",</v>
       </c>
     </row>
-    <row r="860" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A860">
         <v>2024</v>
       </c>
@@ -30384,7 +30383,7 @@
         <v>"ACA15" As "Director(a) de Programa o Coordinador",</v>
       </c>
     </row>
-    <row r="861" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A861">
         <v>2024</v>
       </c>
@@ -30414,7 +30413,7 @@
         <v>"EXP1_2" As "Meli Turno (Virtual)",</v>
       </c>
     </row>
-    <row r="862" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A862">
         <v>2024</v>
       </c>
@@ -30444,7 +30443,7 @@
         <v>"EXP2_2" As "Atención Ean a tu lado (Presencial)",</v>
       </c>
     </row>
-    <row r="863" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A863">
         <v>2024</v>
       </c>
@@ -30474,7 +30473,7 @@
         <v>"EXP3_2" As "Mesa de Servicio",</v>
       </c>
     </row>
-    <row r="864" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A864">
         <v>2024</v>
       </c>
@@ -30504,7 +30503,7 @@
         <v>"ACA16" As "Satisfacción entrega material VAC",</v>
       </c>
     </row>
-    <row r="865" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A865">
         <v>2024</v>
       </c>
@@ -30534,7 +30533,7 @@
         <v>"ACA17" As "Satisfacción asistentes facultad",</v>
       </c>
     </row>
-    <row r="866" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A866">
         <v>2024</v>
       </c>
@@ -30564,7 +30563,7 @@
         <v>"EXP1_3" As "Meli Turno (Virtual)",</v>
       </c>
     </row>
-    <row r="867" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A867">
         <v>2024</v>
       </c>
@@ -30594,7 +30593,7 @@
         <v>"EXP2" As "Atención Ean a tu lado (Presencial)",</v>
       </c>
     </row>
-    <row r="868" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A868">
         <v>2024</v>
       </c>
@@ -30624,7 +30623,7 @@
         <v>"EXP3_3" As "Mesa de Servicio",</v>
       </c>
     </row>
-    <row r="869" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A869">
         <v>2024</v>
       </c>
@@ -30654,7 +30653,7 @@
         <v>"COM1_2" As "Atención por correo electrónico",</v>
       </c>
     </row>
-    <row r="870" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A870">
         <v>2024</v>
       </c>
@@ -30684,7 +30683,7 @@
         <v>"COM2" As "Atención presencial (Tercer Piso Legacy)",</v>
       </c>
     </row>
-    <row r="871" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A871">
         <v>2024</v>
       </c>
@@ -30714,7 +30713,7 @@
         <v>"COM1" As "Atención por correo electrónico",</v>
       </c>
     </row>
-    <row r="872" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A872">
         <v>2024</v>
       </c>
@@ -30744,7 +30743,7 @@
         <v>"COM4" As "Atención presencial (Tercer Piso Legacy)",</v>
       </c>
     </row>
-    <row r="873" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A873">
         <v>2024</v>
       </c>
@@ -30774,7 +30773,7 @@
         <v>"FAB1" As "Disponibilidad y funcionamiento de los equipos",</v>
       </c>
     </row>
-    <row r="874" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A874">
         <v>2024</v>
       </c>
@@ -30804,7 +30803,7 @@
         <v>"FAB2" As "Disponibilidad de materiales y/o reactivos",</v>
       </c>
     </row>
-    <row r="875" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875">
         <v>2024</v>
       </c>
@@ -30834,7 +30833,7 @@
         <v>"PLF1" As "Instalaciones",</v>
       </c>
     </row>
-    <row r="876" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A876">
         <v>2024</v>
       </c>
@@ -30864,7 +30863,7 @@
         <v>"PLF2" As "Higiene y limpieza instalaciones y equipos",</v>
       </c>
     </row>
-    <row r="877" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877">
         <v>2024</v>
       </c>
@@ -30894,7 +30893,7 @@
         <v>"ACA18" As "Probabilidad recomendar programa académico",</v>
       </c>
     </row>
-    <row r="878" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A878">
         <v>2024</v>
       </c>
@@ -30924,7 +30923,7 @@
         <v>"ACA19" As "Probabilidad volver a estudiar en EAN",</v>
       </c>
     </row>
-    <row r="879" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879">
         <v>2024</v>
       </c>
@@ -30954,7 +30953,7 @@
         <v>"IMP1" As "Conocimiento servicios Ean Impacta",</v>
       </c>
     </row>
-    <row r="880" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880">
         <v>2024</v>
       </c>
@@ -30984,7 +30983,7 @@
         <v>"SOS1" As "Influencia emprendimiento sostenible",</v>
       </c>
     </row>
-    <row r="881" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A881">
         <v>2024</v>
       </c>
@@ -31014,7 +31013,7 @@
         <v>"IMP2" As "Enfoque en el emprendimiento",</v>
       </c>
     </row>
-    <row r="882" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A882">
         <v>2024</v>
       </c>
@@ -31044,7 +31043,7 @@
         <v>"EMP1" As "Fuerte conexión con sector empresarial",</v>
       </c>
     </row>
-    <row r="883" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A883">
         <v>2024</v>
       </c>
@@ -31074,7 +31073,7 @@
         <v>"EMP2" As "Programas académicos con alta demanda laboral",</v>
       </c>
     </row>
-    <row r="884" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A884">
         <v>2024</v>
       </c>
@@ -31104,7 +31103,7 @@
         <v>"EXP7" As "Comunidad estudiantil diversa e inclusiva",</v>
       </c>
     </row>
-    <row r="885" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A885">
         <v>2024</v>
       </c>
@@ -31134,7 +31133,7 @@
         <v>"SOS2" As "Compromiso con la sostenibilidad",</v>
       </c>
     </row>
-    <row r="886" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A886">
         <v>2024</v>
       </c>
@@ -31164,7 +31163,7 @@
         <v>"PLF3" As "Infraestructura y espacios de bienestar",</v>
       </c>
     </row>
-    <row r="887" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A887">
         <v>2024</v>
       </c>
@@ -31194,7 +31193,7 @@
         <v>"ACA20" As "Cuerpo docente con experiencia profesional",</v>
       </c>
     </row>
-    <row r="888" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A888">
         <v>2024</v>
       </c>
@@ -31224,7 +31223,7 @@
         <v>"INT1" As "Oportunidades movilidad internacional",</v>
       </c>
     </row>
-    <row r="889" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A889">
         <v>2024</v>
       </c>
@@ -31254,7 +31253,7 @@
         <v>"EMP3" As "Red de graduados y conexiones profesionales",</v>
       </c>
     </row>
-    <row r="890" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A890">
         <v>2024</v>
       </c>
@@ -31284,7 +31283,7 @@
         <v>"INSTI1" As "Qué haría falta para que EAN sea única",</v>
       </c>
     </row>
-    <row r="891" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A891">
         <v>2024</v>
       </c>
@@ -31314,7 +31313,7 @@
         <v>"IMP3" As "Satisfacción atención Ean Impacta",</v>
       </c>
     </row>
-    <row r="892" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A892">
         <v>2024</v>
       </c>
@@ -31344,7 +31343,7 @@
         <v>"SOS3" As "Conocimiento avances sostenibilidad",</v>
       </c>
     </row>
-    <row r="893" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A893">
         <v>2024</v>
       </c>
@@ -31374,7 +31373,7 @@
         <v>"SOS4" As "Acciones junto a Ean Sostenibilidad",</v>
       </c>
     </row>
-    <row r="894" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A894">
         <v>2024</v>
       </c>
@@ -31404,7 +31403,7 @@
         <v>"INSTI2" As "Other",</v>
       </c>
     </row>
-    <row r="895" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A895">
         <v>2024</v>
       </c>
@@ -31434,7 +31433,7 @@
         <v>"SOS5" As "Visión sostenibilidad EAN",</v>
       </c>
     </row>
-    <row r="896" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A896">
         <v>2024</v>
       </c>
@@ -31464,7 +31463,7 @@
         <v>"BIB1" As "Asesoría referencias APA",</v>
       </c>
     </row>
-    <row r="897" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A897">
         <v>2024</v>
       </c>
@@ -31494,7 +31493,7 @@
         <v>"BIB2" As "Búsqueda de información",</v>
       </c>
     </row>
-    <row r="898" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A898">
         <v>2024</v>
       </c>
@@ -31524,7 +31523,7 @@
         <v>"BIB3" As "Pago de multas biblioteca",</v>
       </c>
     </row>
-    <row r="899" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A899">
         <v>2024</v>
       </c>
@@ -31554,7 +31553,7 @@
         <v>"BIB4" As "Préstamo de libros",</v>
       </c>
     </row>
-    <row r="900" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A900">
         <v>2024</v>
       </c>
@@ -31584,7 +31583,7 @@
         <v>"BIB5" As "Préstamo interbibliotecario",</v>
       </c>
     </row>
-    <row r="901" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A901">
         <v>2024</v>
       </c>
@@ -31614,7 +31613,7 @@
         <v>"BIB6" As "Reserva de salas",</v>
       </c>
     </row>
-    <row r="902" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A902">
         <v>2024</v>
       </c>
@@ -31644,7 +31643,7 @@
         <v>"BIB7" As "Tutoriales biblioteca",</v>
       </c>
     </row>
-    <row r="903" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A903">
         <v>2024</v>
       </c>
@@ -31674,7 +31673,7 @@
         <v>"BIB8" As "Completitud colecciones biblioteca",</v>
       </c>
     </row>
-    <row r="904" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A904">
         <v>2024</v>
       </c>
@@ -31704,7 +31703,7 @@
         <v>"BIB10" As "Acceso colecciones electrónicas",</v>
       </c>
     </row>
-    <row r="905" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A905">
         <v>2024</v>
       </c>
@@ -31734,7 +31733,7 @@
         <v>"EXP1_4" As "Meli Turno (Virtual)",</v>
       </c>
     </row>
-    <row r="906" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A906">
         <v>2024</v>
       </c>
@@ -31764,7 +31763,7 @@
         <v>"BIB12" As "Atención presencial biblioteca",</v>
       </c>
     </row>
-    <row r="907" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A907">
         <v>2024</v>
       </c>
@@ -31794,7 +31793,7 @@
         <v>"BIB13" As "Whatsapp biblioteca",</v>
       </c>
     </row>
-    <row r="908" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A908">
         <v>2024</v>
       </c>
@@ -31824,7 +31823,7 @@
         <v>"BIB14" As "Satisfacción espacios físicos biblioteca",</v>
       </c>
     </row>
-    <row r="909" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A909">
         <v>2024</v>
       </c>
@@ -31854,7 +31853,7 @@
         <v>"INT2" As "Buddy Program",</v>
       </c>
     </row>
-    <row r="910" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A910">
         <v>2024</v>
       </c>
@@ -31884,7 +31883,7 @@
         <v>"INT3" As "Doble titulación",</v>
       </c>
     </row>
-    <row r="911" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A911">
         <v>2024</v>
       </c>
@@ -31914,7 +31913,7 @@
         <v>"INT4" As "Escuela internacional verano invierno",</v>
       </c>
     </row>
-    <row r="912" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A912">
         <v>2024</v>
       </c>
@@ -31944,7 +31943,7 @@
         <v>"INT5" As "Intercambios académicos presenciales",</v>
       </c>
     </row>
-    <row r="913" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A913">
         <v>2024</v>
       </c>
@@ -31974,7 +31973,7 @@
         <v>"INT6" As "Intercambios académicos virtuales",</v>
       </c>
     </row>
-    <row r="914" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A914">
         <v>2024</v>
       </c>
@@ -32004,7 +32003,7 @@
         <v>"INT7" As "Misiones académicas",</v>
       </c>
     </row>
-    <row r="915" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A915">
         <v>2024</v>
       </c>
@@ -32034,7 +32033,7 @@
         <v>"INT8" As "Semana Ean Internacional",</v>
       </c>
     </row>
-    <row r="916" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A916">
         <v>2024</v>
       </c>
@@ -32064,7 +32063,7 @@
         <v>"INT9" As "No conozco ninguno",</v>
       </c>
     </row>
-    <row r="917" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A917">
         <v>2024</v>
       </c>
@@ -32094,7 +32093,7 @@
         <v>"INT10" As "Participación programas internacionales",</v>
       </c>
     </row>
-    <row r="918" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A918">
         <v>2024</v>
       </c>
@@ -32124,7 +32123,7 @@
         <v>"INT11" As "Obstáculos movilidad internacional",</v>
       </c>
     </row>
-    <row r="919" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A919">
         <v>2024</v>
       </c>
@@ -32154,7 +32153,7 @@
         <v>"INT12" As "Conocimiento convenios internacionales",</v>
       </c>
     </row>
-    <row r="920" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A920">
         <v>2024</v>
       </c>
@@ -32184,7 +32183,7 @@
         <v>"INT13" As "Relevancia movilidad internacional",</v>
       </c>
     </row>
-    <row r="921" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A921">
         <v>2024</v>
       </c>
@@ -32214,7 +32213,7 @@
         <v>"FIN1" As "Fondo Nutramos Talentos",</v>
       </c>
     </row>
-    <row r="922" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A922">
         <v>2024</v>
       </c>
@@ -32244,7 +32243,7 @@
         <v>"FIN2" As "Fondo Becas Ean Siempre Contigo",</v>
       </c>
     </row>
-    <row r="923" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A923">
         <v>2024</v>
       </c>
@@ -32274,7 +32273,7 @@
         <v>"FIN3" As "Fondo Diversidades",</v>
       </c>
     </row>
-    <row r="924" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A924">
         <v>2024</v>
       </c>
@@ -32304,7 +32303,7 @@
         <v>"FIN4" As "Fondo Sostenibilidad",</v>
       </c>
     </row>
-    <row r="925" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A925">
         <v>2024</v>
       </c>
@@ -32334,7 +32333,7 @@
         <v>"FIN5" As "Ninguna financiación",</v>
       </c>
     </row>
-    <row r="926" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A926">
         <v>2024</v>
       </c>
@@ -32364,7 +32363,7 @@
         <v>"EXP3_4" As "Mesa de Servicio",</v>
       </c>
     </row>
-    <row r="927" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A927">
         <v>2024</v>
       </c>
@@ -32394,7 +32393,7 @@
         <v>"PRA2_2" As "Atención presencial prácticas",</v>
       </c>
     </row>
-    <row r="928" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A928">
         <v>2024</v>
       </c>
@@ -32424,7 +32423,7 @@
         <v>"PRA3" As "Correo electrónico prácticas",</v>
       </c>
     </row>
-    <row r="929" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A929">
         <v>2024</v>
       </c>
@@ -32454,7 +32453,7 @@
         <v>"PRA4" As "Conocimiento prácticas profesionales",</v>
       </c>
     </row>
-    <row r="930" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A930">
         <v>2024</v>
       </c>
@@ -32484,7 +32483,7 @@
         <v>"PRA5" As "Meli turno prácticas",</v>
       </c>
     </row>
-    <row r="931" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A931">
         <v>2024</v>
       </c>
@@ -32514,7 +32513,7 @@
         <v>"PRA2" As "Atención presencial prácticas",</v>
       </c>
     </row>
-    <row r="932" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A932">
         <v>2024</v>
       </c>
@@ -32544,7 +32543,7 @@
         <v>"EXP3_5" As "Mesa de Servicio",</v>
       </c>
     </row>
-    <row r="933" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A933">
         <v>2024</v>
       </c>
@@ -32574,7 +32573,7 @@
         <v>"PRA8" As "Oportunidades mejora prácticas",</v>
       </c>
     </row>
-    <row r="934" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A934">
         <v>2024</v>
       </c>
@@ -32604,7 +32603,7 @@
         <v>"PLA1" As "Plataforma correo electrónico",</v>
       </c>
     </row>
-    <row r="935" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A935">
         <v>2024</v>
       </c>
@@ -32634,7 +32633,7 @@
         <v>"PLA2" As "Aplicaciones Office",</v>
       </c>
     </row>
-    <row r="936" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A936">
         <v>2024</v>
       </c>
@@ -32664,7 +32663,7 @@
         <v>"PLA3" As "Plataforma Teams",</v>
       </c>
     </row>
-    <row r="937" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A937">
         <v>2024</v>
       </c>
@@ -32694,7 +32693,7 @@
         <v>"PLA4" As "Plataforma Cisco Webex",</v>
       </c>
     </row>
-    <row r="938" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A938">
         <v>2024</v>
       </c>
@@ -32724,7 +32723,7 @@
         <v>"PLA5" As "Plataforma Canvas",</v>
       </c>
     </row>
-    <row r="939" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A939">
         <v>2024</v>
       </c>
@@ -32754,7 +32753,7 @@
         <v>"PLA6" As "App Ean",</v>
       </c>
     </row>
-    <row r="940" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A940">
         <v>2024</v>
       </c>
@@ -32784,7 +32783,7 @@
         <v>"PLA7" As "Mesa de servicios TI",</v>
       </c>
     </row>
-    <row r="941" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A941">
         <v>2024</v>
       </c>
@@ -32814,7 +32813,7 @@
         <v>"PLA8" As "Plataforma pagos",</v>
       </c>
     </row>
-    <row r="942" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A942">
         <v>2024</v>
       </c>
@@ -32844,7 +32843,7 @@
         <v>"PLA9" As "Velocidad conexión WiFi",</v>
       </c>
     </row>
-    <row r="943" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A943">
         <v>2024</v>
       </c>
@@ -32874,7 +32873,7 @@
         <v>"PLA10" As "Estabilidad conexión WiFi",</v>
       </c>
     </row>
-    <row r="944" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A944">
         <v>2024</v>
       </c>
@@ -32904,7 +32903,7 @@
         <v>"PLA11" As "Cobertura red WiFi",</v>
       </c>
     </row>
-    <row r="945" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A945">
         <v>2024</v>
       </c>
@@ -32934,7 +32933,7 @@
         <v>"PLA12" As "Reconocimiento facial ingreso",</v>
       </c>
     </row>
-    <row r="946" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A946">
         <v>2024</v>
       </c>
@@ -32964,7 +32963,7 @@
         <v>"PLA13" As "Estado equipos salas cómputo",</v>
       </c>
     </row>
-    <row r="947" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A947">
         <v>2024</v>
       </c>
@@ -32994,7 +32993,7 @@
         <v>"PLA14" As "Disponibilidad equipos salas cómputo",</v>
       </c>
     </row>
-    <row r="948" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A948">
         <v>2024</v>
       </c>
@@ -33024,7 +33023,7 @@
         <v>"PLA15" As "Razones baja calificación servicios tecnológicos",</v>
       </c>
     </row>
-    <row r="949" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A949">
         <v>2024</v>
       </c>
@@ -33054,7 +33053,7 @@
         <v>"EXP1_5" As "Meli Turno (Virtual)",</v>
       </c>
     </row>
-    <row r="950" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A950">
         <v>2024</v>
       </c>
@@ -33084,7 +33083,7 @@
         <v>"REG2_2" As "Atención Ean a tu lado registro",</v>
       </c>
     </row>
-    <row r="951" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A951">
         <v>2024</v>
       </c>
@@ -33114,7 +33113,7 @@
         <v>"EXP3_6" As "Mesa de Servicio",</v>
       </c>
     </row>
-    <row r="952" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A952">
         <v>2024</v>
       </c>
@@ -33144,7 +33143,7 @@
         <v>"REG4" As "Emisión certificados académicos",</v>
       </c>
     </row>
-    <row r="953" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A953">
         <v>2024</v>
       </c>
@@ -33174,7 +33173,7 @@
         <v>"REG5" As "Retiro unidades estudio",</v>
       </c>
     </row>
-    <row r="954" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A954">
         <v>2024</v>
       </c>
@@ -33204,7 +33203,7 @@
         <v>"REG6" As "Abonos",</v>
       </c>
     </row>
-    <row r="955" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A955">
         <v>2024</v>
       </c>
@@ -33234,7 +33233,7 @@
         <v>"REG7" As "Gestion cursos libres",</v>
       </c>
     </row>
-    <row r="956" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A956">
         <v>2024</v>
       </c>
@@ -33264,7 +33263,7 @@
         <v>"REG8" As "Gestion validaciones",</v>
       </c>
     </row>
-    <row r="957" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A957">
         <v>2024</v>
       </c>
@@ -33294,7 +33293,7 @@
         <v>"REG9" As "Distinciones incentivos",</v>
       </c>
     </row>
-    <row r="958" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A958">
         <v>2024</v>
       </c>
@@ -33324,7 +33323,7 @@
         <v>"REG10" As "Examen Saber Pro",</v>
       </c>
     </row>
-    <row r="959" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A959">
         <v>2024</v>
       </c>
@@ -33354,7 +33353,7 @@
         <v>"REG11" As "Proceso grado",</v>
       </c>
     </row>
-    <row r="960" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A960">
         <v>2024</v>
       </c>
@@ -33384,7 +33383,7 @@
         <v>"REG12" As "Actualización documentos",</v>
       </c>
     </row>
-    <row r="961" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A961">
         <v>2024</v>
       </c>
@@ -33414,7 +33413,7 @@
         <v>"EXP1_6" As "Meli Turno (Virtual)",</v>
       </c>
     </row>
-    <row r="962" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A962">
         <v>2024</v>
       </c>
@@ -33444,7 +33443,7 @@
         <v>"REG2_3" As "Atención Ean a tu lado registro",</v>
       </c>
     </row>
-    <row r="963" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A963">
         <v>2024</v>
       </c>
@@ -33474,7 +33473,7 @@
         <v>"EXP3_7" As "Mesa de Servicio",</v>
       </c>
     </row>
-    <row r="964" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A964">
         <v>2024</v>
       </c>
@@ -33504,7 +33503,7 @@
         <v>"FIN6" As "Conocimiento financiación matrícula",</v>
       </c>
     </row>
-    <row r="965" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A965">
         <v>2024</v>
       </c>
@@ -33534,7 +33533,7 @@
         <v>"FIN7" As "Banco AV Villas",</v>
       </c>
     </row>
-    <row r="966" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A966">
         <v>2024</v>
       </c>
@@ -33564,7 +33563,7 @@
         <v>"FIN8" As "Ean Fraccionamiento",</v>
       </c>
     </row>
-    <row r="967" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A967">
         <v>2024</v>
       </c>
@@ -33594,7 +33593,7 @@
         <v>"FIN9" As "Ean Respalda",</v>
       </c>
     </row>
-    <row r="968" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A968">
         <v>2024</v>
       </c>
@@ -33624,7 +33623,7 @@
         <v>"FIN10" As "Financiar",</v>
       </c>
     </row>
-    <row r="969" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A969">
         <v>2024</v>
       </c>
@@ -33654,7 +33653,7 @@
         <v>"FIN11" As "Fincomercio Fincoeducar",</v>
       </c>
     </row>
-    <row r="970" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A970">
         <v>2024</v>
       </c>
@@ -33684,7 +33683,7 @@
         <v>"FIN12" As "FLEVO financiación",</v>
       </c>
     </row>
-    <row r="971" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A971">
         <v>2024</v>
       </c>
@@ -33714,7 +33713,7 @@
         <v>"FIN13" As "Icetex",</v>
       </c>
     </row>
-    <row r="972" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A972">
         <v>2024</v>
       </c>
@@ -33744,7 +33743,7 @@
         <v>"FIN14" As "Lumni Respalda",</v>
       </c>
     </row>
-    <row r="973" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A973">
         <v>2024</v>
       </c>
@@ -33774,7 +33773,7 @@
         <v>"FIN15" As "Sufi Bancolombia",</v>
       </c>
     </row>
-    <row r="974" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A974">
         <v>2024</v>
       </c>
@@ -33804,7 +33803,7 @@
         <v>"FIN16" As "No he utilizado financiación",</v>
       </c>
     </row>
-    <row r="975" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A975">
         <v>2024</v>
       </c>
@@ -33834,7 +33833,7 @@
         <v>"FIN17" As "Satisfacción tiempos descuentos",</v>
       </c>
     </row>
-    <row r="976" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A976">
         <v>2024</v>
       </c>
@@ -33864,7 +33863,7 @@
         <v>"FIN18" As "Satisfacción canales pago matrícula",</v>
       </c>
     </row>
-    <row r="977" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A977">
         <v>2024</v>
       </c>
@@ -33894,7 +33893,7 @@
         <v>"EXP1_7" As "Meli Turno (Virtual)",</v>
       </c>
     </row>
-    <row r="978" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A978">
         <v>2024</v>
       </c>
@@ -33924,7 +33923,7 @@
         <v>"REG2_4" As "Atención Ean a tu lado registro",</v>
       </c>
     </row>
-    <row r="979" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A979">
         <v>2024</v>
       </c>
@@ -33954,7 +33953,7 @@
         <v>"EXP3_8" As "Mesa de Servicio",</v>
       </c>
     </row>
-    <row r="980" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A980">
         <v>2024</v>
       </c>
@@ -33984,7 +33983,7 @@
         <v>"COM8" As "Satisfacción atención Meli turno",</v>
       </c>
     </row>
-    <row r="981" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A981">
         <v>2024</v>
       </c>
@@ -34014,7 +34013,7 @@
         <v>"COM9" As "Satisfacción atención presencial",</v>
       </c>
     </row>
-    <row r="982" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A982">
         <v>2024</v>
       </c>
@@ -34044,7 +34043,7 @@
         <v>"COM10" As "Satisfacción mesa atención",</v>
       </c>
     </row>
-    <row r="983" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A983">
         <v>2024</v>
       </c>
@@ -34074,7 +34073,7 @@
         <v>"COM11" As "Utilidad canal PQRSF",</v>
       </c>
     </row>
-    <row r="984" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A984">
         <v>2024</v>
       </c>
@@ -34104,7 +34103,7 @@
         <v>"COM12" As "Comentarios canales atención",</v>
       </c>
     </row>
-    <row r="985" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A985">
         <v>2024</v>
       </c>
@@ -34134,7 +34133,7 @@
         <v>"COM13" As "Uso PBX universidad",</v>
       </c>
     </row>
-    <row r="986" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A986">
         <v>2024</v>
       </c>
@@ -34164,7 +34163,7 @@
         <v>"COM14" As "Recomendación atención PBX",</v>
       </c>
     </row>
-    <row r="987" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A987">
         <v>2024</v>
       </c>
@@ -34194,7 +34193,7 @@
         <v>"COM15" As "Facebook",</v>
       </c>
     </row>
-    <row r="988" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A988">
         <v>2024</v>
       </c>
@@ -34224,7 +34223,7 @@
         <v>"COM16" As "Instagram",</v>
       </c>
     </row>
-    <row r="989" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A989">
         <v>2024</v>
       </c>
@@ -34254,7 +34253,7 @@
         <v>"COM17" As "LinkedIn",</v>
       </c>
     </row>
-    <row r="990" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A990">
         <v>2024</v>
       </c>
@@ -34284,7 +34283,7 @@
         <v>"COM18" As "Threads",</v>
       </c>
     </row>
-    <row r="991" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A991">
         <v>2024</v>
       </c>
@@ -34314,7 +34313,7 @@
         <v>"COM19" As "TikTok",</v>
       </c>
     </row>
-    <row r="992" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A992">
         <v>2024</v>
       </c>
@@ -34344,7 +34343,7 @@
         <v>"COM20" As "Twitter",</v>
       </c>
     </row>
-    <row r="993" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A993">
         <v>2024</v>
       </c>
@@ -34374,7 +34373,7 @@
         <v>"COM21" As "Todos los anteriores redes",</v>
       </c>
     </row>
-    <row r="994" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A994">
         <v>2024</v>
       </c>
@@ -34404,7 +34403,7 @@
         <v>"COM22" As "Ninguna red",</v>
       </c>
     </row>
-    <row r="995" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A995">
         <v>2024</v>
       </c>
@@ -34434,7 +34433,7 @@
         <v>"PLA16" As "Uso App Universidad Ean",</v>
       </c>
     </row>
-    <row r="996" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A996">
         <v>2024</v>
       </c>
@@ -34464,7 +34463,7 @@
         <v>"EXP8" As "Uso App Bienestar",</v>
       </c>
     </row>
-    <row r="997" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A997">
         <v>2024</v>
       </c>
@@ -34494,7 +34493,7 @@
         <v>"COM23" As "Interacción Chatbot E Ann",</v>
       </c>
     </row>
-    <row r="998" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A998">
         <v>2024</v>
       </c>
@@ -34524,7 +34523,7 @@
         <v>"COM24" As "Satisfacción información chatbot",</v>
       </c>
     </row>
-    <row r="999" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A999">
         <v>2024</v>
       </c>
@@ -34554,7 +34553,7 @@
         <v>"COM25" As "Satisfacción información correo institucional",</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1000">
         <v>2024</v>
       </c>
@@ -34584,7 +34583,7 @@
         <v>"COM26" As "Frecuencia correos institucionales",</v>
       </c>
     </row>
-    <row r="1001" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1001">
         <v>2024</v>
       </c>
@@ -34614,7 +34613,7 @@
         <v>"COM27" As "Canales preferidos atención",</v>
       </c>
     </row>
-    <row r="1002" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1002">
         <v>2024</v>
       </c>
@@ -34644,7 +34643,7 @@
         <v>"PLF4" As "Accesibilidad espacios",</v>
       </c>
     </row>
-    <row r="1003" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1003">
         <v>2024</v>
       </c>
@@ -34674,7 +34673,7 @@
         <v>"PLF5" As "Capacidad espacios",</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1004">
         <v>2024</v>
       </c>
@@ -34704,7 +34703,7 @@
         <v>"PLF6" As "Ventilación espacios",</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1005">
         <v>2024</v>
       </c>
@@ -34734,7 +34733,7 @@
         <v>"PLF7" As "Condiciones seguridad espacios",</v>
       </c>
     </row>
-    <row r="1006" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1006">
         <v>2024</v>
       </c>
@@ -34764,7 +34763,7 @@
         <v>"PLF8_2" As "Aseo espacios",</v>
       </c>
     </row>
-    <row r="1007" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1007">
         <v>2024</v>
       </c>
@@ -34794,7 +34793,7 @@
         <v>"PLF9" As "Disponibilidad espacios",</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1008">
         <v>2024</v>
       </c>
@@ -34824,7 +34823,7 @@
         <v>"PLF10" As "Equipos audiovisuales espacios",</v>
       </c>
     </row>
-    <row r="1009" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1009">
         <v>2024</v>
       </c>
@@ -34854,7 +34853,7 @@
         <v>"PLF11" As "Satisfacción zona alimentación",</v>
       </c>
     </row>
-    <row r="1010" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1010">
         <v>2024</v>
       </c>
@@ -34884,7 +34883,7 @@
         <v>"PLF12" As "Cafetería DoEat",</v>
       </c>
     </row>
-    <row r="1011" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1011">
         <v>2024</v>
       </c>
@@ -34914,7 +34913,7 @@
         <v>"PLF13" As "Frutiice",</v>
       </c>
     </row>
-    <row r="1012" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1012">
         <v>2024</v>
       </c>
@@ -34944,7 +34943,7 @@
         <v>"PLF14" As "La Regional",</v>
       </c>
     </row>
-    <row r="1013" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1013">
         <v>2024</v>
       </c>
@@ -34974,7 +34973,7 @@
         <v>"PLF15" As "Frutiice",</v>
       </c>
     </row>
-    <row r="1014" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1014">
         <v>2024</v>
       </c>
@@ -35004,7 +35003,7 @@
         <v>"PLF16" As "DoEat",</v>
       </c>
     </row>
-    <row r="1015" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1015">
         <v>2024</v>
       </c>
@@ -35034,7 +35033,7 @@
         <v>"PLF17" As "La Regional",</v>
       </c>
     </row>
-    <row r="1016" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1016">
         <v>2024</v>
       </c>
@@ -35064,7 +35063,7 @@
         <v>"PLF18" As "Seguridad campus",</v>
       </c>
     </row>
-    <row r="1017" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1017">
         <v>2024</v>
       </c>
@@ -35094,7 +35093,7 @@
         <v>"PLF8" As "Aseo espacios",</v>
       </c>
     </row>
-    <row r="1018" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1018">
         <v>2024</v>
       </c>
@@ -35124,7 +35123,7 @@
         <v>"PLF20" As "Parqueadero City Parking",</v>
       </c>
     </row>
-    <row r="1019" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1019">
         <v>2024</v>
       </c>
@@ -35154,7 +35153,7 @@
         <v>"FIN7_2" As "Banco AV Villas",</v>
       </c>
     </row>
-    <row r="1020" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1020">
         <v>2024</v>
       </c>
@@ -35184,7 +35183,7 @@
         <v>"PLF22" As "Servicios impresión",</v>
       </c>
     </row>
-    <row r="1021" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1021">
         <v>2024</v>
       </c>
@@ -35214,7 +35213,7 @@
         <v>"EXP9" As "App Bienestar Ean",</v>
       </c>
     </row>
-    <row r="1022" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1022">
         <v>2024</v>
       </c>
@@ -35244,7 +35243,7 @@
         <v>"EXP10" As "Gimnasio fitness",</v>
       </c>
     </row>
-    <row r="1023" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1023">
         <v>2024</v>
       </c>
@@ -35274,7 +35273,7 @@
         <v>"EVC1" As "Clases grupos culturales",</v>
       </c>
     </row>
-    <row r="1024" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1024">
         <v>2024</v>
       </c>
@@ -35304,7 +35303,7 @@
         <v>"EVC2" As "Clases grupos deportivos",</v>
       </c>
     </row>
-    <row r="1025" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1025">
         <v>2024</v>
       </c>
@@ -35334,7 +35333,7 @@
         <v>"EVC3" As "Orquesta filarmónica",</v>
       </c>
     </row>
-    <row r="1026" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1026">
         <v>2024</v>
       </c>
@@ -35364,7 +35363,7 @@
         <v>"EVC4" As "Clases habilidades humanas",</v>
       </c>
     </row>
-    <row r="1027" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1027">
         <v>2024</v>
       </c>
@@ -35394,7 +35393,7 @@
         <v>"EXP11" As "Servicio salud",</v>
       </c>
     </row>
-    <row r="1028" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1028">
         <v>2024</v>
       </c>
@@ -35424,7 +35423,7 @@
         <v>"EXP12" As "Acompañamiento psicológico",</v>
       </c>
     </row>
-    <row r="1029" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1029">
         <v>2024</v>
       </c>
@@ -35454,7 +35453,7 @@
         <v>"EXP13" As "Póliza accidentes personales",</v>
       </c>
     </row>
-    <row r="1030" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1030">
         <v>2024</v>
       </c>
@@ -35484,7 +35483,7 @@
         <v>"EXP14" As "Salón de juegos",</v>
       </c>
     </row>
-    <row r="1031" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1031">
         <v>2024</v>
       </c>
@@ -35514,7 +35513,7 @@
         <v>"EXP15" As "Préstamo juegos instrumentos",</v>
       </c>
     </row>
-    <row r="1032" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1032">
         <v>2024</v>
       </c>
@@ -35544,7 +35543,7 @@
         <v>"EXP16" As "Programa pedaleando bicicletas",</v>
       </c>
     </row>
-    <row r="1033" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1033">
         <v>2024</v>
       </c>
@@ -35574,7 +35573,7 @@
         <v>"EXP17" As "Voluntariado Ean",</v>
       </c>
     </row>
-    <row r="1034" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1034">
         <v>2024</v>
       </c>
@@ -35604,7 +35603,7 @@
         <v>"EMP4" As "Programa vendedor emprendedor",</v>
       </c>
     </row>
-    <row r="1035" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1035">
         <v>2024</v>
       </c>
@@ -35634,7 +35633,7 @@
         <v>"EVC5" As "Eventos promoción prevención salud",</v>
       </c>
     </row>
-    <row r="1036" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1036">
         <v>2024</v>
       </c>
@@ -35664,7 +35663,7 @@
         <v>"EVC6" As "Actividades bienestar integral",</v>
       </c>
     </row>
-    <row r="1037" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1037">
         <v>2024</v>
       </c>
@@ -35694,7 +35693,7 @@
         <v>"EXP18" As "Polideportivo Ean Arena",</v>
       </c>
     </row>
-    <row r="1038" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1038">
         <v>2024</v>
       </c>
@@ -35724,7 +35723,7 @@
         <v>"EXP19" As "Gimnasio fitness Ean",</v>
       </c>
     </row>
-    <row r="1039" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1039">
         <v>2024</v>
       </c>
@@ -35754,7 +35753,7 @@
         <v>"EXP20" As "Zona tenis mesa",</v>
       </c>
     </row>
-    <row r="1040" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1040">
         <v>2024</v>
       </c>
@@ -35784,7 +35783,7 @@
         <v>"EXP21" As "Ball pit Fundadores",</v>
       </c>
     </row>
-    <row r="1041" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1041">
         <v>2024</v>
       </c>
@@ -35814,7 +35813,7 @@
         <v>"EXP22" As "Sala Neutro Legacy",</v>
       </c>
     </row>
-    <row r="1042" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1042">
         <v>2024</v>
       </c>
@@ -35844,7 +35843,7 @@
         <v>"EXP23" As "Salones expresiones",</v>
       </c>
     </row>
-    <row r="1043" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1043">
         <v>2024</v>
       </c>
@@ -35874,7 +35873,7 @@
         <v>"EXP24" As "Salones música Fundadores",</v>
       </c>
     </row>
-    <row r="1044" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1044">
         <v>2024</v>
       </c>
@@ -35904,7 +35903,7 @@
         <v>"EXP25" As "Canchas club Carmel",</v>
       </c>
     </row>
-    <row r="1045" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1045">
         <v>2024</v>
       </c>
@@ -35934,7 +35933,7 @@
         <v>"EXP26" As "Sala lactancia",</v>
       </c>
     </row>
-    <row r="1046" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1046">
         <v>2024</v>
       </c>
@@ -35964,7 +35963,7 @@
         <v>"EXP27" As "Participación bienestar virtual",</v>
       </c>
     </row>
-    <row r="1047" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1047">
         <v>2024</v>
       </c>
@@ -35994,7 +35993,7 @@
         <v>"EXP28" As "Satisfacción bienestar universitario",</v>
       </c>
     </row>
-    <row r="1048" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1048">
         <v>2024</v>
       </c>
@@ -36024,7 +36023,7 @@
         <v>"EXP29" As "Acompañamiento renovación matrícula",</v>
       </c>
     </row>
-    <row r="1049" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1049">
         <v>2024</v>
       </c>
@@ -36054,7 +36053,7 @@
         <v>"EXP30" As "Programa Ean Contigo",</v>
       </c>
     </row>
-    <row r="1050" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1050">
         <v>2024</v>
       </c>
@@ -36084,7 +36083,7 @@
         <v>"EXP31" As "Mentores académicos",</v>
       </c>
     </row>
-    <row r="1051" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1051">
         <v>2024</v>
       </c>
@@ -36114,7 +36113,7 @@
         <v>"EXP32" As "Apoyo psicopedagógico",</v>
       </c>
     </row>
-    <row r="1052" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1052">
         <v>2024</v>
       </c>
@@ -36144,7 +36143,7 @@
         <v>"EXP33" As "Seguimiento proceso académico",</v>
       </c>
     </row>
-    <row r="1053" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1053">
         <v>2024</v>
       </c>
@@ -36174,7 +36173,7 @@
         <v>"EXP34" As "Cursos refuerzo tutorías",</v>
       </c>
     </row>
-    <row r="1054" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1054">
         <v>2024</v>
       </c>
@@ -36204,7 +36203,7 @@
         <v>"EXP35" As "Uso Defensoría universitaria",</v>
       </c>
     </row>
-    <row r="1055" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1055">
         <v>2024</v>
       </c>
@@ -36234,7 +36233,7 @@
         <v>"EXP36" As "Orientación normativa institucional",</v>
       </c>
     </row>
-    <row r="1056" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1056">
         <v>2024</v>
       </c>
@@ -36264,7 +36263,7 @@
         <v>"EXP37" As "Mediación asuntos académicos",</v>
       </c>
     </row>
-    <row r="1057" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1057">
         <v>2024</v>
       </c>
@@ -36294,7 +36293,7 @@
         <v>"EXP38" As "Intervención asuntos administrativos",</v>
       </c>
     </row>
-    <row r="1058" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1058">
         <v>2024</v>
       </c>
@@ -36324,7 +36323,7 @@
         <v>"EXP39" As "Respuesta solicitudes defensoría",</v>
       </c>
     </row>
-    <row r="1059" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1059">
         <v>2024</v>
       </c>
@@ -36354,7 +36353,7 @@
         <v>"EVC7" As "Tienda Ean",</v>
       </c>
     </row>
-    <row r="1060" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1060">
         <v>2024</v>
       </c>
@@ -36384,7 +36383,7 @@
         <v>"EVC8" As "Galería de arte",</v>
       </c>
     </row>
-    <row r="1061" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1061">
         <v>2024</v>
       </c>
@@ -36414,7 +36413,7 @@
         <v>"EVC9" As "Mejoras eventos universidad",</v>
       </c>
     </row>
-    <row r="1062" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1062">
         <v>2024</v>
       </c>
@@ -36444,7 +36443,7 @@
         <v>"FAB3" As "Conocimiento FabLab",</v>
       </c>
     </row>
-    <row r="1063" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1063">
         <v>2024</v>
       </c>
@@ -36474,7 +36473,7 @@
         <v>"EMP5" As "Bolsa empleo universidad",</v>
       </c>
     </row>
-    <row r="1064" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1064" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1064">
         <v>2024</v>
       </c>
@@ -36504,7 +36503,7 @@
         <v>"EMP6" As "Entrenamientos habilidades profesionales",</v>
       </c>
     </row>
-    <row r="1065" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1065" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1065">
         <v>2024</v>
       </c>
@@ -36534,7 +36533,7 @@
         <v>"EMP7" As "Orientación vocacional",</v>
       </c>
     </row>
-    <row r="1066" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1066" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1066">
         <v>2024</v>
       </c>
@@ -36564,7 +36563,7 @@
         <v>"EMP8" As "Ferias oportunidades laborales",</v>
       </c>
     </row>
-    <row r="1067" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1067" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1067">
         <v>2024</v>
       </c>
@@ -36594,7 +36593,7 @@
         <v>"EMP9" As "Prueba ESIC",</v>
       </c>
     </row>
-    <row r="1068" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1068" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1068">
         <v>2024</v>
       </c>
@@ -36624,7 +36623,7 @@
         <v>"INSTI3" As "¿Tienes hijos?",</v>
       </c>
     </row>
-    <row r="1069" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1069" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1069">
         <v>2024</v>
       </c>
@@ -36654,7 +36653,7 @@
         <v>"INSTI4" As "Servicio cuidado infantil",</v>
       </c>
     </row>
-    <row r="1070" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1070" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1070">
         <v>2024</v>
       </c>
@@ -36684,7 +36683,7 @@
         <v>"EXP40" As "Satisfacción inclusión universidad",</v>
       </c>
     </row>
-    <row r="1071" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1071" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1071">
         <v>2024</v>
       </c>
@@ -36714,7 +36713,7 @@
         <v>"EXP41" As "Satisfacción atención recepción",</v>
       </c>
     </row>
-    <row r="1072" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1072" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1072">
         <v>2024</v>
       </c>
@@ -36744,7 +36743,7 @@
         <v>"INSTI5" As "Aspecto positivo universidad",</v>
       </c>
     </row>
-    <row r="1073" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1073" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1073">
         <v>2024</v>
       </c>
@@ -36774,7 +36773,7 @@
         <v>"INSTI6" As "Sugerencias mejora universidad",</v>
       </c>
     </row>
-    <row r="1074" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1074" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1074">
         <v>2024</v>
       </c>
@@ -36804,7 +36803,7 @@
         <v>"INSTI7" As "Recomendación servicios universidad",</v>
       </c>
     </row>
-    <row r="1075" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1075" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1075">
         <v>2024</v>
       </c>
@@ -36834,7 +36833,7 @@
         <v>"Response Type" As "Response Type",</v>
       </c>
     </row>
-    <row r="1076" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1076" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1076">
         <v>2024</v>
       </c>
@@ -36864,7 +36863,7 @@
         <v>"Start Date (UTC)" As "Start Date (UTC)",</v>
       </c>
     </row>
-    <row r="1077" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1077" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1077">
         <v>2024</v>
       </c>
@@ -36894,7 +36893,7 @@
         <v>"Stage Date (UTC)" As "Stage Date (UTC)",</v>
       </c>
     </row>
-    <row r="1078" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1078" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1078">
         <v>2024</v>
       </c>
@@ -36924,7 +36923,7 @@
         <v>"Submit Date (UTC)" As "Submit Date (UTC)",</v>
       </c>
     </row>
-    <row r="1079" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1079" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1079">
         <v>2024</v>
       </c>
@@ -36954,7 +36953,7 @@
         <v>"Network ID" As "Network ID",</v>
       </c>
     </row>
-    <row r="1080" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1080" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1080">
         <v>2024</v>
       </c>
@@ -36985,20 +36984,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1080" xr:uid="{CD622777-2061-4107-94CD-CCCFB7DE918A}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="2019"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Academia"/>
-        <filter val="Datos Estudiante"/>
-        <filter val="Datos Programa"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I1080" xr:uid="{CD622777-2061-4107-94CD-CCCFB7DE918A}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
